--- a/docs/참고/인허가/사운드1/[04] SUVC-FW-SND1 소프트웨어 유닛 검증 기준서.xlsx
+++ b/docs/참고/인허가/사운드1/[04] SUVC-FW-SND1 소프트웨어 유닛 검증 기준서.xlsx
@@ -637,16 +637,16 @@
   <dimension ref="B2:K350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="27" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="38" customWidth="1" min="9" max="9"/>
+    <col width="44" customWidth="1" min="10" max="10"/>
+    <col width="62" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="2" ht="34" customHeight="1">
@@ -865,7 +865,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="37.5" customHeight="1">
       <c r="B26" s="8" t="inlineStr">
         <is>
           <t>CFX</t>
@@ -919,7 +919,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="12.5" customHeight="1">
       <c r="B27" s="8" t="inlineStr"/>
       <c r="C27" s="8" t="inlineStr"/>
       <c r="D27" s="9" t="inlineStr">
@@ -963,7 +963,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="12.5" customHeight="1">
       <c r="B28" s="8" t="inlineStr"/>
       <c r="C28" s="8" t="inlineStr"/>
       <c r="D28" s="9" t="inlineStr">
@@ -1007,7 +1007,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="12.5" customHeight="1">
       <c r="B29" s="8" t="inlineStr"/>
       <c r="C29" s="8" t="inlineStr"/>
       <c r="D29" s="9" t="inlineStr">
@@ -1051,7 +1051,7 @@
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="12.5" customHeight="1">
       <c r="B30" s="8" t="inlineStr"/>
       <c r="C30" s="8" t="inlineStr"/>
       <c r="D30" s="9" t="inlineStr">
@@ -1095,7 +1095,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="12.5" customHeight="1">
       <c r="B31" s="8" t="inlineStr"/>
       <c r="C31" s="8" t="inlineStr"/>
       <c r="D31" s="9" t="inlineStr">
@@ -1139,7 +1139,7 @@
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="12.5" customHeight="1">
       <c r="B32" s="8" t="inlineStr"/>
       <c r="C32" s="8" t="inlineStr"/>
       <c r="D32" s="9" t="inlineStr">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="12.5" customHeight="1">
       <c r="B33" s="8" t="inlineStr"/>
       <c r="C33" s="8" t="inlineStr"/>
       <c r="D33" s="9" t="inlineStr">
@@ -1227,7 +1227,7 @@
         </is>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="12.5" customHeight="1">
       <c r="B34" s="8" t="inlineStr"/>
       <c r="C34" s="8" t="inlineStr"/>
       <c r="D34" s="9" t="inlineStr">
@@ -1271,7 +1271,7 @@
         </is>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="12.5" customHeight="1">
       <c r="B35" s="8" t="inlineStr"/>
       <c r="C35" s="8" t="inlineStr"/>
       <c r="D35" s="9" t="inlineStr">
@@ -1315,7 +1315,7 @@
         </is>
       </c>
     </row>
-    <row r="36">
+    <row r="36" ht="12.5" customHeight="1">
       <c r="B36" s="8" t="inlineStr"/>
       <c r="C36" s="8" t="inlineStr"/>
       <c r="D36" s="9" t="inlineStr">
@@ -1359,7 +1359,7 @@
         </is>
       </c>
     </row>
-    <row r="37">
+    <row r="37" ht="12.5" customHeight="1">
       <c r="B37" s="8" t="inlineStr"/>
       <c r="C37" s="8" t="inlineStr"/>
       <c r="D37" s="9" t="inlineStr">
@@ -1403,7 +1403,7 @@
         </is>
       </c>
     </row>
-    <row r="38">
+    <row r="38" ht="12.5" customHeight="1">
       <c r="B38" s="8" t="inlineStr"/>
       <c r="C38" s="8" t="inlineStr"/>
       <c r="D38" s="9" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="12.5" customHeight="1">
       <c r="B39" s="8" t="inlineStr"/>
       <c r="C39" s="8" t="inlineStr"/>
       <c r="D39" s="9" t="inlineStr">
@@ -1491,7 +1491,7 @@
         </is>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="12.5" customHeight="1">
       <c r="B40" s="8" t="inlineStr"/>
       <c r="C40" s="8" t="inlineStr"/>
       <c r="D40" s="9" t="inlineStr">
@@ -1535,7 +1535,7 @@
         </is>
       </c>
     </row>
-    <row r="41">
+    <row r="41" ht="12.5" customHeight="1">
       <c r="B41" s="8" t="inlineStr"/>
       <c r="C41" s="8" t="inlineStr"/>
       <c r="D41" s="9" t="inlineStr">
@@ -1579,7 +1579,7 @@
         </is>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="12.5" customHeight="1">
       <c r="B42" s="8" t="inlineStr"/>
       <c r="C42" s="8" t="inlineStr"/>
       <c r="D42" s="9" t="inlineStr">
@@ -1623,7 +1623,7 @@
         </is>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="12.5" customHeight="1">
       <c r="B43" s="8" t="inlineStr"/>
       <c r="C43" s="8" t="inlineStr"/>
       <c r="D43" s="9" t="inlineStr">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="12.5" customHeight="1">
       <c r="B44" s="8" t="inlineStr"/>
       <c r="C44" s="8" t="inlineStr"/>
       <c r="D44" s="9" t="inlineStr">
@@ -1711,7 +1711,7 @@
         </is>
       </c>
     </row>
-    <row r="45">
+    <row r="45" ht="12.5" customHeight="1">
       <c r="B45" s="8" t="inlineStr"/>
       <c r="C45" s="8" t="inlineStr"/>
       <c r="D45" s="9" t="inlineStr">
@@ -1755,7 +1755,7 @@
         </is>
       </c>
     </row>
-    <row r="46">
+    <row r="46" ht="12.5" customHeight="1">
       <c r="B46" s="8" t="inlineStr"/>
       <c r="C46" s="8" t="inlineStr"/>
       <c r="D46" s="9" t="inlineStr">
@@ -1799,7 +1799,7 @@
         </is>
       </c>
     </row>
-    <row r="47">
+    <row r="47" ht="12.5" customHeight="1">
       <c r="B47" s="8" t="inlineStr"/>
       <c r="C47" s="8" t="inlineStr"/>
       <c r="D47" s="9" t="inlineStr">
@@ -1843,7 +1843,7 @@
         </is>
       </c>
     </row>
-    <row r="48">
+    <row r="48" ht="12.5" customHeight="1">
       <c r="B48" s="8" t="inlineStr"/>
       <c r="C48" s="8" t="inlineStr"/>
       <c r="D48" s="9" t="inlineStr">
@@ -1887,7 +1887,7 @@
         </is>
       </c>
     </row>
-    <row r="49">
+    <row r="49" ht="12.5" customHeight="1">
       <c r="B49" s="8" t="inlineStr"/>
       <c r="C49" s="8" t="inlineStr"/>
       <c r="D49" s="9" t="inlineStr">
@@ -1931,7 +1931,7 @@
         </is>
       </c>
     </row>
-    <row r="50">
+    <row r="50" ht="12.5" customHeight="1">
       <c r="B50" s="8" t="inlineStr"/>
       <c r="C50" s="8" t="inlineStr"/>
       <c r="D50" s="9" t="inlineStr">
@@ -1975,7 +1975,7 @@
         </is>
       </c>
     </row>
-    <row r="51">
+    <row r="51" ht="12.5" customHeight="1">
       <c r="B51" s="8" t="inlineStr"/>
       <c r="C51" s="8" t="inlineStr"/>
       <c r="D51" s="9" t="inlineStr">
@@ -2019,7 +2019,7 @@
         </is>
       </c>
     </row>
-    <row r="52">
+    <row r="52" ht="12.5" customHeight="1">
       <c r="B52" s="8" t="inlineStr"/>
       <c r="C52" s="8" t="inlineStr"/>
       <c r="D52" s="9" t="inlineStr">
@@ -2063,7 +2063,7 @@
         </is>
       </c>
     </row>
-    <row r="53">
+    <row r="53" ht="12.5" customHeight="1">
       <c r="B53" s="8" t="inlineStr"/>
       <c r="C53" s="8" t="inlineStr"/>
       <c r="D53" s="9" t="inlineStr">
@@ -2107,7 +2107,7 @@
         </is>
       </c>
     </row>
-    <row r="54">
+    <row r="54" ht="12.5" customHeight="1">
       <c r="B54" s="8" t="inlineStr"/>
       <c r="C54" s="8" t="inlineStr"/>
       <c r="D54" s="9" t="inlineStr">
@@ -2151,7 +2151,7 @@
         </is>
       </c>
     </row>
-    <row r="55">
+    <row r="55" ht="12.5" customHeight="1">
       <c r="B55" s="8" t="inlineStr"/>
       <c r="C55" s="8" t="inlineStr"/>
       <c r="D55" s="9" t="inlineStr">
@@ -2195,7 +2195,7 @@
         </is>
       </c>
     </row>
-    <row r="56">
+    <row r="56" ht="12.5" customHeight="1">
       <c r="B56" s="8" t="inlineStr"/>
       <c r="C56" s="8" t="inlineStr"/>
       <c r="D56" s="9" t="inlineStr">
@@ -2239,7 +2239,7 @@
         </is>
       </c>
     </row>
-    <row r="57">
+    <row r="57" ht="12.5" customHeight="1">
       <c r="B57" s="8" t="inlineStr"/>
       <c r="C57" s="8" t="inlineStr"/>
       <c r="D57" s="9" t="inlineStr">
@@ -2283,7 +2283,7 @@
         </is>
       </c>
     </row>
-    <row r="58">
+    <row r="58" ht="12.5" customHeight="1">
       <c r="B58" s="8" t="inlineStr"/>
       <c r="C58" s="8" t="inlineStr"/>
       <c r="D58" s="9" t="inlineStr">
@@ -2327,7 +2327,7 @@
         </is>
       </c>
     </row>
-    <row r="59">
+    <row r="59" ht="12.5" customHeight="1">
       <c r="B59" s="8" t="inlineStr"/>
       <c r="C59" s="8" t="inlineStr"/>
       <c r="D59" s="9" t="inlineStr">
@@ -2371,7 +2371,7 @@
         </is>
       </c>
     </row>
-    <row r="60">
+    <row r="60" ht="12.5" customHeight="1">
       <c r="B60" s="8" t="inlineStr"/>
       <c r="C60" s="8" t="inlineStr"/>
       <c r="D60" s="9" t="inlineStr">
@@ -2415,7 +2415,7 @@
         </is>
       </c>
     </row>
-    <row r="61">
+    <row r="61" ht="12.5" customHeight="1">
       <c r="B61" s="8" t="inlineStr"/>
       <c r="C61" s="8" t="inlineStr"/>
       <c r="D61" s="9" t="inlineStr">
@@ -2459,7 +2459,7 @@
         </is>
       </c>
     </row>
-    <row r="62">
+    <row r="62" ht="12.5" customHeight="1">
       <c r="B62" s="8" t="inlineStr"/>
       <c r="C62" s="8" t="inlineStr"/>
       <c r="D62" s="9" t="inlineStr">
@@ -2503,7 +2503,7 @@
         </is>
       </c>
     </row>
-    <row r="63">
+    <row r="63" ht="12.5" customHeight="1">
       <c r="B63" s="8" t="inlineStr"/>
       <c r="C63" s="8" t="inlineStr"/>
       <c r="D63" s="9" t="inlineStr">
@@ -2547,7 +2547,7 @@
         </is>
       </c>
     </row>
-    <row r="64">
+    <row r="64" ht="12.5" customHeight="1">
       <c r="B64" s="8" t="inlineStr"/>
       <c r="C64" s="8" t="inlineStr"/>
       <c r="D64" s="9" t="inlineStr">
@@ -2591,7 +2591,7 @@
         </is>
       </c>
     </row>
-    <row r="65">
+    <row r="65" ht="12.5" customHeight="1">
       <c r="B65" s="8" t="inlineStr"/>
       <c r="C65" s="8" t="inlineStr"/>
       <c r="D65" s="9" t="inlineStr">
@@ -2635,7 +2635,7 @@
         </is>
       </c>
     </row>
-    <row r="66">
+    <row r="66" ht="12.5" customHeight="1">
       <c r="B66" s="8" t="inlineStr"/>
       <c r="C66" s="8" t="inlineStr"/>
       <c r="D66" s="9" t="inlineStr">
@@ -2679,7 +2679,7 @@
         </is>
       </c>
     </row>
-    <row r="67">
+    <row r="67" ht="12.5" customHeight="1">
       <c r="B67" s="8" t="inlineStr"/>
       <c r="C67" s="8" t="inlineStr"/>
       <c r="D67" s="9" t="inlineStr">
@@ -2723,7 +2723,7 @@
         </is>
       </c>
     </row>
-    <row r="68">
+    <row r="68" ht="12.5" customHeight="1">
       <c r="B68" s="8" t="inlineStr"/>
       <c r="C68" s="8" t="inlineStr"/>
       <c r="D68" s="9" t="inlineStr">
@@ -2767,7 +2767,7 @@
         </is>
       </c>
     </row>
-    <row r="69">
+    <row r="69" ht="12.5" customHeight="1">
       <c r="B69" s="8" t="inlineStr"/>
       <c r="C69" s="8" t="inlineStr"/>
       <c r="D69" s="9" t="inlineStr">
@@ -2811,7 +2811,7 @@
         </is>
       </c>
     </row>
-    <row r="70">
+    <row r="70" ht="12.5" customHeight="1">
       <c r="B70" s="8" t="inlineStr"/>
       <c r="C70" s="8" t="inlineStr"/>
       <c r="D70" s="9" t="inlineStr">
@@ -2855,7 +2855,7 @@
         </is>
       </c>
     </row>
-    <row r="71">
+    <row r="71" ht="12.5" customHeight="1">
       <c r="B71" s="8" t="inlineStr"/>
       <c r="C71" s="8" t="inlineStr"/>
       <c r="D71" s="9" t="inlineStr">
@@ -2899,7 +2899,7 @@
         </is>
       </c>
     </row>
-    <row r="72">
+    <row r="72" ht="12.5" customHeight="1">
       <c r="B72" s="8" t="inlineStr"/>
       <c r="C72" s="8" t="inlineStr"/>
       <c r="D72" s="9" t="inlineStr">
@@ -2943,7 +2943,7 @@
         </is>
       </c>
     </row>
-    <row r="73">
+    <row r="73" ht="12.5" customHeight="1">
       <c r="B73" s="8" t="inlineStr"/>
       <c r="C73" s="8" t="inlineStr"/>
       <c r="D73" s="9" t="inlineStr">
@@ -2987,7 +2987,7 @@
         </is>
       </c>
     </row>
-    <row r="74">
+    <row r="74" ht="12.5" customHeight="1">
       <c r="B74" s="8" t="inlineStr"/>
       <c r="C74" s="8" t="inlineStr"/>
       <c r="D74" s="9" t="inlineStr">
@@ -3031,7 +3031,7 @@
         </is>
       </c>
     </row>
-    <row r="75">
+    <row r="75" ht="12.5" customHeight="1">
       <c r="B75" s="8" t="inlineStr"/>
       <c r="C75" s="8" t="inlineStr"/>
       <c r="D75" s="9" t="inlineStr">
@@ -3075,7 +3075,7 @@
         </is>
       </c>
     </row>
-    <row r="76">
+    <row r="76" ht="12.5" customHeight="1">
       <c r="B76" s="8" t="inlineStr"/>
       <c r="C76" s="8" t="inlineStr"/>
       <c r="D76" s="9" t="inlineStr">
@@ -3119,7 +3119,7 @@
         </is>
       </c>
     </row>
-    <row r="77">
+    <row r="77" ht="12.5" customHeight="1">
       <c r="B77" s="8" t="inlineStr"/>
       <c r="C77" s="8" t="inlineStr"/>
       <c r="D77" s="9" t="inlineStr">
@@ -3163,7 +3163,7 @@
         </is>
       </c>
     </row>
-    <row r="78">
+    <row r="78" ht="12.5" customHeight="1">
       <c r="B78" s="8" t="inlineStr"/>
       <c r="C78" s="8" t="inlineStr"/>
       <c r="D78" s="9" t="inlineStr">
@@ -3207,7 +3207,7 @@
         </is>
       </c>
     </row>
-    <row r="79">
+    <row r="79" ht="12.5" customHeight="1">
       <c r="B79" s="8" t="inlineStr"/>
       <c r="C79" s="8" t="inlineStr"/>
       <c r="D79" s="9" t="inlineStr">
@@ -3251,7 +3251,7 @@
         </is>
       </c>
     </row>
-    <row r="80">
+    <row r="80" ht="12.5" customHeight="1">
       <c r="B80" s="8" t="inlineStr"/>
       <c r="C80" s="8" t="inlineStr"/>
       <c r="D80" s="9" t="inlineStr">
@@ -3295,7 +3295,7 @@
         </is>
       </c>
     </row>
-    <row r="81">
+    <row r="81" ht="12.5" customHeight="1">
       <c r="B81" s="8" t="inlineStr"/>
       <c r="C81" s="8" t="inlineStr"/>
       <c r="D81" s="9" t="inlineStr">
@@ -3339,7 +3339,7 @@
         </is>
       </c>
     </row>
-    <row r="82">
+    <row r="82" ht="12.5" customHeight="1">
       <c r="B82" s="8" t="inlineStr"/>
       <c r="C82" s="8" t="inlineStr"/>
       <c r="D82" s="9" t="inlineStr">
@@ -3383,7 +3383,7 @@
         </is>
       </c>
     </row>
-    <row r="83">
+    <row r="83" ht="12.5" customHeight="1">
       <c r="B83" s="8" t="inlineStr"/>
       <c r="C83" s="8" t="inlineStr"/>
       <c r="D83" s="9" t="inlineStr">
@@ -3427,7 +3427,7 @@
         </is>
       </c>
     </row>
-    <row r="84">
+    <row r="84" ht="12.5" customHeight="1">
       <c r="B84" s="8" t="inlineStr"/>
       <c r="C84" s="8" t="inlineStr"/>
       <c r="D84" s="9" t="inlineStr">
@@ -3471,7 +3471,7 @@
         </is>
       </c>
     </row>
-    <row r="85">
+    <row r="85" ht="12.5" customHeight="1">
       <c r="B85" s="8" t="inlineStr"/>
       <c r="C85" s="8" t="inlineStr"/>
       <c r="D85" s="9" t="inlineStr">
@@ -3515,7 +3515,7 @@
         </is>
       </c>
     </row>
-    <row r="86">
+    <row r="86" ht="12.5" customHeight="1">
       <c r="B86" s="8" t="inlineStr"/>
       <c r="C86" s="8" t="inlineStr"/>
       <c r="D86" s="9" t="inlineStr">
@@ -3559,7 +3559,7 @@
         </is>
       </c>
     </row>
-    <row r="87">
+    <row r="87" ht="12.5" customHeight="1">
       <c r="B87" s="8" t="inlineStr"/>
       <c r="C87" s="8" t="inlineStr"/>
       <c r="D87" s="9" t="inlineStr">
@@ -3603,7 +3603,7 @@
         </is>
       </c>
     </row>
-    <row r="88">
+    <row r="88" ht="12.5" customHeight="1">
       <c r="B88" s="8" t="inlineStr"/>
       <c r="C88" s="8" t="inlineStr"/>
       <c r="D88" s="9" t="inlineStr">
@@ -3647,7 +3647,7 @@
         </is>
       </c>
     </row>
-    <row r="89">
+    <row r="89" ht="12.5" customHeight="1">
       <c r="B89" s="8" t="inlineStr"/>
       <c r="C89" s="8" t="inlineStr"/>
       <c r="D89" s="9" t="inlineStr">
@@ -3691,7 +3691,7 @@
         </is>
       </c>
     </row>
-    <row r="90">
+    <row r="90" ht="12.5" customHeight="1">
       <c r="B90" s="8" t="inlineStr"/>
       <c r="C90" s="8" t="inlineStr"/>
       <c r="D90" s="9" t="inlineStr">
@@ -3735,7 +3735,7 @@
         </is>
       </c>
     </row>
-    <row r="91">
+    <row r="91" ht="12.5" customHeight="1">
       <c r="B91" s="8" t="inlineStr"/>
       <c r="C91" s="8" t="inlineStr"/>
       <c r="D91" s="9" t="inlineStr">
@@ -3779,7 +3779,7 @@
         </is>
       </c>
     </row>
-    <row r="92">
+    <row r="92" ht="37.5" customHeight="1">
       <c r="B92" s="8" t="inlineStr"/>
       <c r="C92" s="8" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         </is>
       </c>
     </row>
-    <row r="93">
+    <row r="93" ht="12.5" customHeight="1">
       <c r="B93" s="8" t="inlineStr"/>
       <c r="C93" s="8" t="inlineStr"/>
       <c r="D93" s="9" t="inlineStr">
@@ -3873,7 +3873,7 @@
         </is>
       </c>
     </row>
-    <row r="94">
+    <row r="94" ht="112.5" customHeight="1">
       <c r="B94" s="8" t="inlineStr"/>
       <c r="C94" s="8" t="inlineStr">
         <is>
@@ -3904,30 +3904,35 @@
       </c>
       <c r="H94" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 대상 유닛이 호출되는 지점에 디버깅용 중단점을 적용한다.
+- 입력 버퍼와 출력 버퍼를 함께 조회할 수 있도록 창을 준비한다.</t>
         </is>
       </c>
       <c r="I94" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 이 유닛의 출력은 DSP 라이브러리 또는 HEAR 함수체인 결과에 의존한다.
+- 기댓값을 미리 낼 수 없으므로 실측값을 기록한다.
+- 고정소수점 연산 차이를 고려하여 판정한다.</t>
         </is>
       </c>
       <c r="J94" s="9" t="inlineStr">
         <is>
-          <t>- 해당 유닛을 실행시키고 디버깅용 중단점을 적용하여 출력 데이터를 확인한다.
-- 라이브러리 출력에 의존하므로 실측값을 기록한다.</t>
+          <t>- 신호를 입력한 상태에서 이 유닛의 진입과 복귀에 중단점을 적용한다.
+- 입력 최대값 버퍼와 출력 이득을 함께 조회해 기록한다.</t>
         </is>
       </c>
       <c r="K94" s="9" t="inlineStr">
         <is>
           <t>- 자동 이득 제어 실행 구현
-- 전처리 체인이 만든 최대값 버퍼에 의존한다.
-- 기댓값을 미리 낼 수 없다. 실측값을 기록한다.
-- (고정소수점 연산 고려)</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
+[산출 근거] 전처리 함수체인이 만든 최대값 버퍼에 의존한다. 기댓값을 미리 낼 수 없으므로 지어내지 않는다.
+[판정] 기댓값을 미리 낼 수 없다. 아래 항목의 실측값을 기록한다.
+       고정소수점 연산 차이를 고려하여 판정한다.
+1) 입력 : 시험 벡터 주입
+   예상 출력 : (실측 기록)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="112.5" customHeight="1">
       <c r="B95" s="8" t="inlineStr"/>
       <c r="C95" s="8" t="inlineStr"/>
       <c r="D95" s="9" t="inlineStr">
@@ -3952,30 +3957,35 @@
       </c>
       <c r="H95" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 대상 유닛이 호출되는 지점에 디버깅용 중단점을 적용한다.
+- 입력 버퍼와 출력 버퍼를 함께 조회할 수 있도록 창을 준비한다.</t>
         </is>
       </c>
       <c r="I95" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 이 유닛의 출력은 DSP 라이브러리 또는 HEAR 함수체인 결과에 의존한다.
+- 기댓값을 미리 낼 수 없으므로 실측값을 기록한다.
+- 고정소수점 연산 차이를 고려하여 판정한다.</t>
         </is>
       </c>
       <c r="J95" s="9" t="inlineStr">
         <is>
-          <t>- 해당 유닛을 실행시키고 디버깅용 중단점을 적용하여 출력 데이터를 확인한다.
-- 라이브러리 출력에 의존하므로 실측값을 기록한다.</t>
+          <t>- 중단점에서 입력값과 반환 이득을 조회해 기록한다.
+- 잡음 구간, 증폭 구간, 감쇠 구간 각각에서 한 번씩 기록한다.</t>
         </is>
       </c>
       <c r="K95" s="9" t="inlineStr">
         <is>
           <t>- 이득 계산 구현
-- 입력이 전처리 체인 출력이며 dB 변환 라이브러리를 거친다.
-- 기댓값을 미리 낼 수 없다. 실측값을 기록한다.
-- (고정소수점 연산 고려)</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
+[산출 근거] 입력이 전처리 체인 출력이며 dB 변환 라이브러리를 거친다. 기댓값을 미리 낼 수 없으므로 지어내지 않는다.
+[판정] 기댓값을 미리 낼 수 없다. 아래 항목의 실측값을 기록한다.
+       고정소수점 연산 차이를 고려하여 판정한다.
+1) 입력 : 시험 벡터 주입
+   예상 출력 : (실측 기록)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="200" customHeight="1">
       <c r="B96" s="8" t="inlineStr"/>
       <c r="C96" s="8" t="inlineStr"/>
       <c r="D96" s="9" t="inlineStr">
@@ -4000,35 +4010,47 @@
       </c>
       <c r="H96" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 빌드 설정에 TDC_UNIT_TEST 를 정의한다.
+- src/1__cfx/test/tdc_unit_test_cfx.c 를 빌드에 넣는다.
+- 기존 소스는 수정하지 않는다. 매크로가 없으면 이 파일은 빈 번역 단위가 된다.
+- 디버거에서 tdc_ut_run_all() 을 호출한다.
+- tdc_ut_done 에 1 이 대입되는 지점에 중단점을 걸고 tdc_ut_result 를 조회한다.
+- 하네스가 시험마다 m_prev_agc_10db_gain_Q8_16 을 지정한 값으로 둔다.</t>
         </is>
       </c>
       <c r="I96" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 결과 배열에서 값 -999 는 구분자다. 그 다음 값이 유닛 번호다.
+- 시험은 전역 상태를 바꾼다. 시험 후에는 장치를 재기동한다.
+- 시험 코드는 평시 빌드에서 제외되므로 정상 동작에 영향을 주지 않는다.
+- 직전 이득이 상태로 남으므로 시험 순서를 바꾸면 결과가 달라진다.</t>
         </is>
       </c>
       <c r="J96" s="9" t="inlineStr">
         <is>
-          <t>- 빌드 설정에 TDC_UNIT_TEST 를 정의하고 시험 파일을 빌드에 넣는다.
-- 디버거에서 시험 진입점을 호출한다.
-- done 변수에 중단점을 걸고 결과 배열을 조회한다.
-- 실기 시험 절차서의 기댓값과 대조한다.</t>
+          <t>- 하네스가 아래 5 가지 조합에 대해 직전 이득을 먼저 대입한 뒤 원 함수를 호출한다.
+- 구분자 -999 와 유닛 번호 71 다음에 결과 5 개가 이어진다.</t>
         </is>
       </c>
       <c r="K96" s="9" t="inlineStr">
         <is>
           <t>- 이득 시정수 적용 구현
-- 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
-  직전 이득=0, 입력 이득=65536 -&gt; 655 (릴리즈 경로)
-  직전 이득=65536, 입력 이득=0 -&gt; 3276 (어택 경로)
-  직전 이득=65536, 입력 이득=131072 -&gt; 66190 (릴리즈 경로)
-  직전 이득=131072, 입력 이득=65536 -&gt; 68811 (어택 경로)
-  직전 이득=0, 입력 이득=0 -&gt; 0 (릴리즈 경로)</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
+[산출 근거] 직전 이득이 내부 상태로 남는다. 직전 &lt;= 입력 이면 릴리즈 경로(계수 655, 1-계수 64880), 아니면 어택 경로(계수 62259, 1-계수 3276)다. 결과는 (계수 x 입력 + (1-계수) x 직전) &gt;&gt; 16 이며 24 비트로 포화시킨다.
+[판정] 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
+1) 입력 : 직전 이득=0, 입력 이득=65536
+   예상 출력 : 655  (릴리즈 경로)
+2) 입력 : 직전 이득=65536, 입력 이득=0
+   예상 출력 : 3276  (어택 경로)
+3) 입력 : 직전 이득=65536, 입력 이득=131072
+   예상 출력 : 66190  (릴리즈 경로)
+4) 입력 : 직전 이득=131072, 입력 이득=65536
+   예상 출력 : 68811  (어택 경로)
+5) 입력 : 직전 이득=0, 입력 이득=0
+   예상 출력 : 0  (릴리즈 경로)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="112.5" customHeight="1">
       <c r="B97" s="8" t="inlineStr"/>
       <c r="C97" s="8" t="inlineStr"/>
       <c r="D97" s="9" t="inlineStr">
@@ -4053,30 +4075,34 @@
       </c>
       <c r="H97" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 대상 유닛이 호출되는 지점에 디버깅용 중단점을 적용한다.
+- 입력 버퍼와 출력 버퍼를 함께 조회할 수 있도록 창을 준비한다.</t>
         </is>
       </c>
       <c r="I97" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 이 유닛의 출력은 DSP 라이브러리 또는 HEAR 함수체인 결과에 의존한다.
+- 기댓값을 미리 낼 수 없으므로 실측값을 기록한다.
+- 고정소수점 연산 차이를 고려하여 판정한다.</t>
         </is>
       </c>
       <c r="J97" s="9" t="inlineStr">
         <is>
-          <t>- 해당 유닛을 실행시키고 디버깅용 중단점을 적용하여 출력 데이터를 확인한다.
-- 라이브러리 출력에 의존하므로 실측값을 기록한다.</t>
+          <t>- 적용 전후의 믹서 출력 버퍼 16 표본을 조회해 기록한다.</t>
         </is>
       </c>
       <c r="K97" s="9" t="inlineStr">
         <is>
           <t>- 이득 적용 구현
-- 믹서 출력 버퍼 전체에 적용된다.
-- 기댓값을 미리 낼 수 없다. 실측값을 기록한다.
-- (고정소수점 연산 고려)</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
+[산출 근거] 믹서 출력 버퍼 전체에 적용된다. 기댓값을 미리 낼 수 없으므로 지어내지 않는다.
+[판정] 기댓값을 미리 낼 수 없다. 아래 항목의 실측값을 기록한다.
+       고정소수점 연산 차이를 고려하여 판정한다.
+1) 입력 : 시험 벡터 주입
+   예상 출력 : (실측 기록)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="112.5" customHeight="1">
       <c r="B98" s="8" t="inlineStr"/>
       <c r="C98" s="8" t="inlineStr"/>
       <c r="D98" s="9" t="inlineStr">
@@ -4101,30 +4127,34 @@
       </c>
       <c r="H98" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 대상 유닛이 호출되는 지점에 디버깅용 중단점을 적용한다.
+- 입력 버퍼와 출력 버퍼를 함께 조회할 수 있도록 창을 준비한다.</t>
         </is>
       </c>
       <c r="I98" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 이 유닛의 출력은 DSP 라이브러리 또는 HEAR 함수체인 결과에 의존한다.
+- 기댓값을 미리 낼 수 없으므로 실측값을 기록한다.
+- 고정소수점 연산 차이를 고려하여 판정한다.</t>
         </is>
       </c>
       <c r="J98" s="9" t="inlineStr">
         <is>
-          <t>- 해당 유닛을 실행시키고 디버깅용 중단점을 적용하여 출력 데이터를 확인한다.
-- 라이브러리 출력에 의존하므로 실측값을 기록한다.</t>
+          <t>- 호출 전후의 주파수 분석 입력 버퍼를 조회해 자리 이동이 일어나는지 기록한다.</t>
         </is>
       </c>
       <c r="K98" s="9" t="inlineStr">
         <is>
           <t>- 주파수 분석 입력 갱신 구현
-- HEAR 함수체인 출력 버퍼에 의존한다.
-- 기댓값을 미리 낼 수 없다. 실측값을 기록한다.
-- (고정소수점 연산 고려)</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
+[산출 근거] HEAR 함수체인 출력 버퍼에 의존한다. 기댓값을 미리 낼 수 없으므로 지어내지 않는다.
+[판정] 기댓값을 미리 낼 수 없다. 아래 항목의 실측값을 기록한다.
+       고정소수점 연산 차이를 고려하여 판정한다.
+1) 입력 : 시험 벡터 주입
+   예상 출력 : (실측 기록)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="112.5" customHeight="1">
       <c r="B99" s="8" t="inlineStr"/>
       <c r="C99" s="8" t="inlineStr"/>
       <c r="D99" s="9" t="inlineStr">
@@ -4149,30 +4179,34 @@
       </c>
       <c r="H99" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 대상 유닛이 호출되는 지점에 디버깅용 중단점을 적용한다.
+- 입력 버퍼와 출력 버퍼를 함께 조회할 수 있도록 창을 준비한다.</t>
         </is>
       </c>
       <c r="I99" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 이 유닛의 출력은 DSP 라이브러리 또는 HEAR 함수체인 결과에 의존한다.
+- 기댓값을 미리 낼 수 없으므로 실측값을 기록한다.
+- 고정소수점 연산 차이를 고려하여 판정한다.</t>
         </is>
       </c>
       <c r="J99" s="9" t="inlineStr">
         <is>
-          <t>- 해당 유닛을 실행시키고 디버깅용 중단점을 적용하여 출력 데이터를 확인한다.
-- 라이브러리 출력에 의존하므로 실측값을 기록한다.</t>
+          <t>- 변환 체인 출력과 산출된 대역 대표값을 함께 조회해 기록한다.</t>
         </is>
       </c>
       <c r="K99" s="9" t="inlineStr">
         <is>
           <t>- 분석 대역 대표값 산출 구현
-- 주파수 변환 체인(vMag) 출력에 의존한다.
-- 기댓값을 미리 낼 수 없다. 실측값을 기록한다.
-- (고정소수점 연산 고려)</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
+[산출 근거] 주파수 변환 체인(vMag) 출력에 의존한다. 기댓값을 미리 낼 수 없으므로 지어내지 않는다.
+[판정] 기댓값을 미리 낼 수 없다. 아래 항목의 실측값을 기록한다.
+       고정소수점 연산 차이를 고려하여 판정한다.
+1) 입력 : 시험 벡터 주입
+   예상 출력 : (실측 기록)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="112.5" customHeight="1">
       <c r="B100" s="8" t="inlineStr"/>
       <c r="C100" s="8" t="inlineStr"/>
       <c r="D100" s="9" t="inlineStr">
@@ -4197,28 +4231,36 @@
       </c>
       <c r="H100" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 대상 유닛이 호출되는 지점에 디버깅용 중단점을 적용한다.
+- 입력 버퍼와 출력 버퍼를 함께 조회할 수 있도록 창을 준비한다.</t>
         </is>
       </c>
       <c r="I100" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 이 유닛의 출력은 DSP 라이브러리 또는 HEAR 함수체인 결과에 의존한다.
+- 기댓값을 미리 낼 수 없으므로 실측값을 기록한다.
+- 고정소수점 연산 차이를 고려하여 판정한다.</t>
         </is>
       </c>
       <c r="J100" s="9" t="inlineStr">
         <is>
-          <t>- 해당 유닛을 실행시키고 디버깅용 중단점을 적용하여 출력 데이터를 확인한다.
-- 라이브러리 출력에 의존하므로 실측값을 기록한다.</t>
+          <t>- 맵의 대역 수와 저장 영역의 대역 수가 같은지 먼저 확인한다.
+- 호출 후 g_pass_bin_index 배열을 조회해 저장 영역의 값과 같은지 기록한다.
+- 대역 수가 다를 때는 배열이 바뀌지 않아야 한다. 그 경우도 기록한다.</t>
         </is>
       </c>
       <c r="K100" s="9" t="inlineStr">
         <is>
           <t>- 통과 대역 인덱스 읽기 구현
-- 실기 시험 절차서의 기댓값과 일치해야 한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
+[산출 근거] 파일 시스템 영역에 저장된 통과 대역 색인을 읽어 온다. 저장된 내용에 의존한다. 기댓값을 미리 낼 수 없으므로 지어내지 않는다.
+[판정] 기댓값을 미리 낼 수 없다. 아래 항목의 실측값을 기록한다.
+       고정소수점 연산 차이를 고려하여 판정한다.
+1) 입력 : 시험 벡터 주입
+   예상 출력 : (실측 기록)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="112.5" customHeight="1">
       <c r="B101" s="8" t="inlineStr"/>
       <c r="C101" s="8" t="inlineStr"/>
       <c r="D101" s="9" t="inlineStr">
@@ -4243,28 +4285,34 @@
       </c>
       <c r="H101" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 대상 유닛이 호출되는 지점에 디버깅용 중단점을 적용한다.
+- 입력 버퍼와 출력 버퍼를 함께 조회할 수 있도록 창을 준비한다.</t>
         </is>
       </c>
       <c r="I101" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 이 유닛의 출력은 DSP 라이브러리 또는 HEAR 함수체인 결과에 의존한다.
+- 기댓값을 미리 낼 수 없으므로 실측값을 기록한다.
+- 고정소수점 연산 차이를 고려하여 판정한다.</t>
         </is>
       </c>
       <c r="J101" s="9" t="inlineStr">
         <is>
-          <t>- 해당 유닛을 실행시키고 디버깅용 중단점을 적용하여 출력 데이터를 확인한다.
-- 라이브러리 출력에 의존하므로 실측값을 기록한다.</t>
+          <t>- 공유 메모리의 C/T 레벨과 호출 후 CFX 쪽 배열을 함께 조회해 같은지 기록한다.</t>
         </is>
       </c>
       <c r="K101" s="9" t="inlineStr">
         <is>
           <t>- C 및 T 레벨 읽기 구현
-- 실기 시험 절차서의 기댓값과 일치해야 한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
+[산출 근거] CM3 가 공유 메모리에 올린 C 레벨과 T 레벨을 읽어 온다. CM3 계산 결과에 의존한다. 기댓값을 미리 낼 수 없으므로 지어내지 않는다.
+[판정] 기댓값을 미리 낼 수 없다. 아래 항목의 실측값을 기록한다.
+       고정소수점 연산 차이를 고려하여 판정한다.
+1) 입력 : 시험 벡터 주입
+   예상 출력 : (실측 기록)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="112.5" customHeight="1">
       <c r="B102" s="8" t="inlineStr"/>
       <c r="C102" s="8" t="inlineStr"/>
       <c r="D102" s="9" t="inlineStr">
@@ -4289,28 +4337,34 @@
       </c>
       <c r="H102" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 대상 유닛이 호출되는 지점에 디버깅용 중단점을 적용한다.
+- 입력 버퍼와 출력 버퍼를 함께 조회할 수 있도록 창을 준비한다.</t>
         </is>
       </c>
       <c r="I102" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 이 유닛의 출력은 DSP 라이브러리 또는 HEAR 함수체인 결과에 의존한다.
+- 기댓값을 미리 낼 수 없으므로 실측값을 기록한다.
+- 고정소수점 연산 차이를 고려하여 판정한다.</t>
         </is>
       </c>
       <c r="J102" s="9" t="inlineStr">
         <is>
-          <t>- 해당 유닛을 실행시키고 디버깅용 중단점을 적용하여 출력 데이터를 확인한다.
-- 라이브러리 출력에 의존하므로 실측값을 기록한다.</t>
+          <t>- 자극 볼륨을 1, 5, 10 으로 바꿔 가며 호출하고 산출된 최대 레벨을 기록한다.</t>
         </is>
       </c>
       <c r="K102" s="9" t="inlineStr">
         <is>
           <t>- 자극 최대 레벨 계산 구현
-- 실기 시험 절차서의 기댓값과 일치해야 한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
+[산출 근거] 자극 볼륨과 C/T 레벨로 최대 레벨을 구한다. 맵 데이터에 의존한다. 기댓값을 미리 낼 수 없으므로 지어내지 않는다.
+[판정] 기댓값을 미리 낼 수 없다. 아래 항목의 실측값을 기록한다.
+       고정소수점 연산 차이를 고려하여 판정한다.
+1) 입력 : 시험 벡터 주입
+   예상 출력 : (실측 기록)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="112.5" customHeight="1">
       <c r="B103" s="8" t="inlineStr"/>
       <c r="C103" s="8" t="inlineStr"/>
       <c r="D103" s="9" t="inlineStr">
@@ -4335,30 +4389,34 @@
       </c>
       <c r="H103" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 대상 유닛이 호출되는 지점에 디버깅용 중단점을 적용한다.
+- 입력 버퍼와 출력 버퍼를 함께 조회할 수 있도록 창을 준비한다.</t>
         </is>
       </c>
       <c r="I103" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 이 유닛의 출력은 DSP 라이브러리 또는 HEAR 함수체인 결과에 의존한다.
+- 기댓값을 미리 낼 수 없으므로 실측값을 기록한다.
+- 고정소수점 연산 차이를 고려하여 판정한다.</t>
         </is>
       </c>
       <c r="J103" s="9" t="inlineStr">
         <is>
-          <t>- 해당 유닛을 실행시키고 디버깅용 중단점을 적용하여 출력 데이터를 확인한다.
-- 라이브러리 출력에 의존하므로 실측값을 기록한다.</t>
+          <t>- 호출 후 로그 매핑 계수 A 와 B 를 조회해 기록한다.</t>
         </is>
       </c>
       <c r="K103" s="9" t="inlineStr">
         <is>
           <t>- 로그 매핑 계수 계산 구현
-- dB 변환 라이브러리를 거친다.
-- 기댓값을 미리 낼 수 없다. 실측값을 기록한다.
-- (고정소수점 연산 고려)</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
+[산출 근거] dB 변환 라이브러리를 거친다. 기댓값을 미리 낼 수 없으므로 지어내지 않는다.
+[판정] 기댓값을 미리 낼 수 없다. 아래 항목의 실측값을 기록한다.
+       고정소수점 연산 차이를 고려하여 판정한다.
+1) 입력 : 시험 벡터 주입
+   예상 출력 : (실측 기록)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="112.5" customHeight="1">
       <c r="B104" s="8" t="inlineStr"/>
       <c r="C104" s="8" t="inlineStr"/>
       <c r="D104" s="9" t="inlineStr">
@@ -4383,30 +4441,34 @@
       </c>
       <c r="H104" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 대상 유닛이 호출되는 지점에 디버깅용 중단점을 적용한다.
+- 입력 버퍼와 출력 버퍼를 함께 조회할 수 있도록 창을 준비한다.</t>
         </is>
       </c>
       <c r="I104" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 이 유닛의 출력은 DSP 라이브러리 또는 HEAR 함수체인 결과에 의존한다.
+- 기댓값을 미리 낼 수 없으므로 실측값을 기록한다.
+- 고정소수점 연산 차이를 고려하여 판정한다.</t>
         </is>
       </c>
       <c r="J104" s="9" t="inlineStr">
         <is>
-          <t>- 해당 유닛을 실행시키고 디버깅용 중단점을 적용하여 출력 데이터를 확인한다.
-- 라이브러리 출력에 의존하므로 실측값을 기록한다.</t>
+          <t>- 오디오 볼륨을 바꿔 가며 계수 A 와 B 를 조회해 기록한다.</t>
         </is>
       </c>
       <c r="K104" s="9" t="inlineStr">
         <is>
           <t>- 로그 매핑 계수 계산 유닛, 오디오 볼륨 반영 구현
-- 같은 라이브러리를 거친다.
-- 기댓값을 미리 낼 수 없다. 실측값을 기록한다.
-- (고정소수점 연산 고려)</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
+[산출 근거] 같은 dB 변환 라이브러리를 거친다. 기댓값을 미리 낼 수 없으므로 지어내지 않는다.
+[판정] 기댓값을 미리 낼 수 없다. 아래 항목의 실측값을 기록한다.
+       고정소수점 연산 차이를 고려하여 판정한다.
+1) 입력 : 시험 벡터 주입
+   예상 출력 : (실측 기록)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="12.5" customHeight="1">
       <c r="B105" s="8" t="inlineStr"/>
       <c r="C105" s="8" t="inlineStr"/>
       <c r="D105" s="9" t="inlineStr">
@@ -4450,7 +4512,7 @@
         </is>
       </c>
     </row>
-    <row r="106">
+    <row r="106" ht="237.5" customHeight="1">
       <c r="B106" s="8" t="inlineStr"/>
       <c r="C106" s="8" t="inlineStr"/>
       <c r="D106" s="9" t="inlineStr">
@@ -4475,30 +4537,49 @@
       </c>
       <c r="H106" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 빌드 설정에 TDC_UNIT_TEST 를 정의한다.
+- src/1__cfx/test/tdc_unit_test_cfx.c 를 빌드에 넣는다.
+- 기존 소스는 수정하지 않는다. 매크로가 없으면 이 파일은 빈 번역 단위가 된다.
+- 디버거에서 tdc_ut_run_all() 을 호출한다.
+- tdc_ut_done 에 1 이 대입되는 지점에 중단점을 걸고 tdc_ut_result 를 조회한다.</t>
         </is>
       </c>
       <c r="I106" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 이 유닛의 출력은 DSP 라이브러리 또는 HEAR 함수체인 결과에 의존한다.
+- 기댓값을 미리 낼 수 없으므로 실측값을 기록한다.
+- 고정소수점 연산 차이를 고려하여 판정한다.</t>
         </is>
       </c>
       <c r="J106" s="9" t="inlineStr">
         <is>
-          <t>- 해당 유닛을 실행시키고 디버깅용 중단점을 적용하여 출력 데이터를 확인한다.
-- 라이브러리 출력에 의존하므로 실측값을 기록한다.</t>
+          <t>- 하네스가 입력 0, 1, 100, 1000, 10000, 100000 을 차례로 넣어 호출한다.
+- 구분자 -999 와 유닛 번호 81 다음에 «입력, 출력» 짝으로 12 개가 이어진다.
+- 각 짝의 출력을 그대로 기록한다.</t>
         </is>
       </c>
       <c r="K106" s="9" t="inlineStr">
         <is>
           <t>- 거듭제곱 계산 구현
-- cfx_pwr_to_dB_asm 과 cfx_dB_to_pwr_asm 어셈블리 라이브러리를 거친다.
-- 기댓값을 미리 낼 수 없다. 실측값을 기록한다.
-- (고정소수점 연산 고려)</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
+[산출 근거] cfx_pwr_to_dB_asm 과 cfx_dB_to_pwr_asm 어셈블리 라이브러리를 거친다. 기댓값을 미리 낼 수 없으므로 지어내지 않는다.
+[판정] 기댓값을 미리 낼 수 없다. 아래 항목의 실측값을 기록한다.
+       고정소수점 연산 차이를 고려하여 판정한다.
+1) 입력 : x = 0
+   예상 출력 : 0  (x &lt; 1 이면 0 을 반환해야 한다. 이 항만 확인 가능)
+2) 입력 : x = 1
+   예상 출력 : (실측 기록)
+3) 입력 : x = 100
+   예상 출력 : (실측 기록)
+4) 입력 : x = 1000
+   예상 출력 : (실측 기록)
+5) 입력 : x = 10000
+   예상 출력 : (실측 기록)
+6) 입력 : x = 100000
+   예상 출력 : (실측 기록)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="112.5" customHeight="1">
       <c r="B107" s="8" t="inlineStr"/>
       <c r="C107" s="8" t="inlineStr"/>
       <c r="D107" s="9" t="inlineStr">
@@ -4523,28 +4604,39 @@
       </c>
       <c r="H107" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 빌드 설정에 TDC_UNIT_TEST 를 정의한다.
+- src/1__cfx/test/tdc_unit_test_cfx.c 를 빌드에 넣는다.
+- 기존 소스는 수정하지 않는다. 매크로가 없으면 이 파일은 빈 번역 단위가 된다.
+- 디버거에서 tdc_ut_run_all() 을 호출한다.
+- tdc_ut_done 에 1 이 대입되는 지점에 중단점을 걸고 tdc_ut_result 를 조회한다.
+- PCM 기록 버퍼(HEAR_ADDR_FIFO_PCM_WRITING)를 조회할 수 있게 창을 준비한다.</t>
         </is>
       </c>
       <c r="I107" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 이 유닛의 출력은 DSP 라이브러리 또는 HEAR 함수체인 결과에 의존한다.
+- 기댓값을 미리 낼 수 없으므로 실측값을 기록한다.
+- 고정소수점 연산 차이를 고려하여 판정한다.</t>
         </is>
       </c>
       <c r="J107" s="9" t="inlineStr">
         <is>
-          <t>- 해당 유닛을 실행시키고 디버깅용 중단점을 적용하여 출력 데이터를 확인한다.
-- 라이브러리 출력에 의존하므로 실측값을 기록한다.</t>
+          <t>- 호출 후 준비된 패킷 헤더 값을 조회해 기록한다.
+- 맵의 자극 모드를 바꿔 가며 헤더가 달라지는지 기록한다.</t>
         </is>
       </c>
       <c r="K107" s="9" t="inlineStr">
         <is>
           <t>- 자극 패킷 헤더 준비 구현
-- 실기 시험 절차서의 기댓값과 일치해야 한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
+[산출 근거] 맵의 자극 모드와 전극 배정에 따라 헤더가 정해진다. 맵 데이터에 의존한다. 기댓값을 미리 낼 수 없으므로 지어내지 않는다.
+[판정] 기댓값을 미리 낼 수 없다. 아래 항목의 실측값을 기록한다.
+       고정소수점 연산 차이를 고려하여 판정한다.
+1) 입력 : 시험 벡터 주입
+   예상 출력 : (실측 기록)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="112.5" customHeight="1">
       <c r="B108" s="8" t="inlineStr"/>
       <c r="C108" s="8" t="inlineStr"/>
       <c r="D108" s="9" t="inlineStr">
@@ -4569,28 +4661,40 @@
       </c>
       <c r="H108" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 빌드 설정에 TDC_UNIT_TEST 를 정의한다.
+- src/1__cfx/test/tdc_unit_test_cfx.c 를 빌드에 넣는다.
+- 기존 소스는 수정하지 않는다. 매크로가 없으면 이 파일은 빈 번역 단위가 된다.
+- 디버거에서 tdc_ut_run_all() 을 호출한다.
+- tdc_ut_done 에 1 이 대입되는 지점에 중단점을 걸고 tdc_ut_result 를 조회한다.
+- PCM 기록 버퍼(HEAR_ADDR_FIFO_PCM_WRITING)를 조회할 수 있게 창을 준비한다.</t>
         </is>
       </c>
       <c r="I108" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 이 유닛의 출력은 DSP 라이브러리 또는 HEAR 함수체인 결과에 의존한다.
+- 기댓값을 미리 낼 수 없으므로 실측값을 기록한다.
+- 고정소수점 연산 차이를 고려하여 판정한다.</t>
         </is>
       </c>
       <c r="J108" s="9" t="inlineStr">
         <is>
-          <t>- 해당 유닛을 실행시키고 디버깅용 중단점을 적용하여 출력 데이터를 확인한다.
-- 라이브러리 출력에 의존하므로 실측값을 기록한다.</t>
+          <t>- 맵의 자극 기법을 CIS 로 두고 호출해 어느 하위 유닛이 불리는지 확인한다.
+- NofM 으로 바꿔 다시 호출해 확인한다.
+- 각각의 PCM 출력 버퍼를 조회해 기록한다.</t>
         </is>
       </c>
       <c r="K108" s="9" t="inlineStr">
         <is>
           <t>- 자극 기법 실행 구현
-- 실기 시험 절차서의 기댓값과 일치해야 한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
+[산출 근거] 맵의 자극 기법 설정에 따라 CIS 또는 NofM 으로 갈린다. 기댓값을 미리 낼 수 없으므로 지어내지 않는다.
+[판정] 기댓값을 미리 낼 수 없다. 아래 항목의 실측값을 기록한다.
+       고정소수점 연산 차이를 고려하여 판정한다.
+1) 입력 : 시험 벡터 주입
+   예상 출력 : (실측 기록)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="112.5" customHeight="1">
       <c r="B109" s="8" t="inlineStr"/>
       <c r="C109" s="8" t="inlineStr"/>
       <c r="D109" s="9" t="inlineStr">
@@ -4615,28 +4719,39 @@
       </c>
       <c r="H109" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 빌드 설정에 TDC_UNIT_TEST 를 정의한다.
+- src/1__cfx/test/tdc_unit_test_cfx.c 를 빌드에 넣는다.
+- 기존 소스는 수정하지 않는다. 매크로가 없으면 이 파일은 빈 번역 단위가 된다.
+- 디버거에서 tdc_ut_run_all() 을 호출한다.
+- tdc_ut_done 에 1 이 대입되는 지점에 중단점을 걸고 tdc_ut_result 를 조회한다.
+- PCM 기록 버퍼(HEAR_ADDR_FIFO_PCM_WRITING)를 조회할 수 있게 창을 준비한다.</t>
         </is>
       </c>
       <c r="I109" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 이 유닛의 출력은 DSP 라이브러리 또는 HEAR 함수체인 결과에 의존한다.
+- 기댓값을 미리 낼 수 없으므로 실측값을 기록한다.
+- 고정소수점 연산 차이를 고려하여 판정한다.</t>
         </is>
       </c>
       <c r="J109" s="9" t="inlineStr">
         <is>
-          <t>- 해당 유닛을 실행시키고 디버깅용 중단점을 적용하여 출력 데이터를 확인한다.
-- 라이브러리 출력에 의존하므로 실측값을 기록한다.</t>
+          <t>- 호출 후 PCM 출력 버퍼에서 자극 헤더, 전극 번호, 자극 레벨을 조회해 기록한다.
+- 맵의 CIS 대역 순서와 실제 출력 순서가 맞는지 기록한다.</t>
         </is>
       </c>
       <c r="K109" s="9" t="inlineStr">
         <is>
           <t>- CIS 자극 기법 구현
-- 실기 시험 절차서의 기댓값과 일치해야 한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
+[산출 근거] 대역 대표값과 매핑 결과에 의존한다. 앞단 라이브러리 출력이 입력이 된다. 기댓값을 미리 낼 수 없으므로 지어내지 않는다.
+[판정] 기댓값을 미리 낼 수 없다. 아래 항목의 실측값을 기록한다.
+       고정소수점 연산 차이를 고려하여 판정한다.
+1) 입력 : 시험 벡터 주입
+   예상 출력 : (실측 기록)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="112.5" customHeight="1">
       <c r="B110" s="8" t="inlineStr"/>
       <c r="C110" s="8" t="inlineStr"/>
       <c r="D110" s="9" t="inlineStr">
@@ -4661,28 +4776,38 @@
       </c>
       <c r="H110" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 빌드 설정에 TDC_UNIT_TEST 를 정의한다.
+- src/1__cfx/test/tdc_unit_test_cfx.c 를 빌드에 넣는다.
+- 기존 소스는 수정하지 않는다. 매크로가 없으면 이 파일은 빈 번역 단위가 된다.
+- 디버거에서 tdc_ut_run_all() 을 호출한다.
+- tdc_ut_done 에 1 이 대입되는 지점에 중단점을 걸고 tdc_ut_result 를 조회한다.
+- PCM 기록 버퍼(HEAR_ADDR_FIFO_PCM_WRITING)를 조회할 수 있게 창을 준비한다.</t>
         </is>
       </c>
       <c r="I110" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 이 유닛의 출력은 DSP 라이브러리 또는 HEAR 함수체인 결과에 의존한다.
+- 기댓값을 미리 낼 수 없으므로 실측값을 기록한다.
+- 고정소수점 연산 차이를 고려하여 판정한다.</t>
         </is>
       </c>
       <c r="J110" s="9" t="inlineStr">
         <is>
-          <t>- 해당 유닛을 실행시키고 디버깅용 중단점을 적용하여 출력 데이터를 확인한다.
-- 라이브러리 출력에 의존하므로 실측값을 기록한다.</t>
+          <t>- 호출 후 PCM 출력 버퍼를 조회해 교차 배치 순서대로 자극이 실렸는지 기록한다.</t>
         </is>
       </c>
       <c r="K110" s="9" t="inlineStr">
         <is>
           <t>- NofM 자극 기법 구현
-- 실기 시험 절차서의 기댓값과 일치해야 한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
+[산출 근거] 피크 선택과 인터리빙 결과를 받아 패킷을 만든다. 앞단 결과에 의존한다. 기댓값을 미리 낼 수 없으므로 지어내지 않는다.
+[판정] 기댓값을 미리 낼 수 없다. 아래 항목의 실측값을 기록한다.
+       고정소수점 연산 차이를 고려하여 판정한다.
+1) 입력 : 시험 벡터 주입
+   예상 출력 : (실측 기록)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="150" customHeight="1">
       <c r="B111" s="8" t="inlineStr"/>
       <c r="C111" s="8" t="inlineStr"/>
       <c r="D111" s="9" t="inlineStr">
@@ -4707,31 +4832,43 @@
       </c>
       <c r="H111" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 빌드 설정에 TDC_UNIT_TEST 를 정의한다.
+- src/1__cfx/test/tdc_unit_test_cfx.c 를 빌드에 넣는다.
+- 기존 소스는 수정하지 않는다. 매크로가 없으면 이 파일은 빈 번역 단위가 된다.
+- 디버거에서 tdc_ut_run_all() 을 호출한다.
+- tdc_ut_done 에 1 이 대입되는 지점에 중단점을 걸고 tdc_ut_result 를 조회한다.
+- 하네스가 호출 전에 세 버퍼를 모두 777 로 채운다.</t>
         </is>
       </c>
       <c r="I111" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 결과 배열에서 값 -999 는 구분자다. 그 다음 값이 유닛 번호다.
+- 시험은 전역 상태를 바꾼다. 시험 후에는 장치를 재기동한다.
+- 시험 코드는 평시 빌드에서 제외되므로 정상 동작에 영향을 주지 않는다.</t>
         </is>
       </c>
       <c r="J111" s="9" t="inlineStr">
         <is>
-          <t>- 빌드 설정에 TDC_UNIT_TEST 를 정의하고 시험 파일을 빌드에 넣는다.
-- 디버거에서 시험 진입점을 호출한다.
-- done 변수에 중단점을 걸고 결과 배열을 조회한다.
-- 실기 시험 절차서의 기댓값과 대조한다.</t>
+          <t>- 하네스가 세 버퍼를 777 로 채운 뒤 원 함수를 호출한다.
+- 구분자 -999 와 유닛 번호 86 다음에 결과 64 개가 이어진다.
+- 순서는 선택 버퍼 16, 교차 버퍼 16, 임시 버퍼 32 다.</t>
         </is>
       </c>
       <c r="K111" s="9" t="inlineStr">
         <is>
           <t>- NofM 버퍼 초기화 구현
-- 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
-  버퍼에 임의 값을 채워 둔 뒤 호출 -&gt; g_NofM_adjacent_BandIndex[0..15] = -1, g_NofM_notAdjacent_BandIndex[0..15] = -1, addr_stimulationTempBuff[0..31] = -1</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
+[산출 근거] 선택 버퍼와 교차 버퍼 각 16 칸, 임시 버퍼 32 칸을 모두 -1 로 채운다.
+[판정] 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
+1) 입력 : g_NofM_adjacent_BandIndex[0..15] 을 777 로 채운 뒤 호출
+   예상 출력 : 16 개 모두 -1
+2) 입력 : g_NofM_notAdjacent_BandIndex[0..15] 을 777 로 채운 뒤 호출
+   예상 출력 : 16 개 모두 -1
+3) 입력 : addr_stimulationTempBuff[0..31] 을 777 로 채운 뒤 호출
+   예상 출력 : 32 개 모두 -1</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="175" customHeight="1">
       <c r="B112" s="8" t="inlineStr"/>
       <c r="C112" s="8" t="inlineStr"/>
       <c r="D112" s="9" t="inlineStr">
@@ -4756,34 +4893,46 @@
       </c>
       <c r="H112" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 빌드 설정에 TDC_UNIT_TEST 를 정의한다.
+- src/1__cfx/test/tdc_unit_test_cfx.c 를 빌드에 넣는다.
+- 기존 소스는 수정하지 않는다. 매크로가 없으면 이 파일은 빈 번역 단위가 된다.
+- 디버거에서 tdc_ut_run_all() 을 호출한다.
+- tdc_ut_done 에 1 이 대입되는 지점에 중단점을 걸고 tdc_ut_result 를 조회한다.
+- 하네스가 벡터마다 g_pcm_amplitude_level[0..31] 을 채운다.</t>
         </is>
       </c>
       <c r="I112" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 결과 배열에서 값 -999 는 구분자다. 그 다음 값이 유닛 번호다.
+- 시험은 전역 상태를 바꾼다. 시험 후에는 장치를 재기동한다.
+- 시험 코드는 평시 빌드에서 제외되므로 정상 동작에 영향을 주지 않는다.
+- 벡터 나에서 뒤쪽 색인이 나오면 점수 병합의 부호 규칙이 뒤집힌 것이다.</t>
         </is>
       </c>
       <c r="J112" s="9" t="inlineStr">
         <is>
-          <t>- 빌드 설정에 TDC_UNIT_TEST 를 정의하고 시험 파일을 빌드에 넣는다.
-- 디버거에서 시험 진입점을 호출한다.
-- done 변수에 중단점을 걸고 결과 배열을 조회한다.
-- 실기 시험 절차서의 기댓값과 대조한다.</t>
+          <t>- 하네스가 아래 네 벡터를 차례로 진폭 배열에 넣고 원 함수를 호출한다.
+- 구분자 -999 와 유닛 번호 87 다음에 결과 64 개(벡터당 16 개)가 이어진다.
+- g_NofM_adjacent_BandIndex[0..15] 를 벡터마다 조회한다.</t>
         </is>
       </c>
       <c r="K112" s="9" t="inlineStr">
         <is>
           <t>- NofM 피크 선택 구현
-- 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
-  진폭[i] = i*10 (0, 10, ... 310) -&gt; [16, 17, 18, 19, 20, 21, 22, 23, 24, 25, 26, 27, 28, 29, 30, 31]
-  진폭 전부 100 (동점) -&gt; [0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15]  (같은 크기면 저주파가 살아남는다)
-  짝수 색인 200, 홀수 색인 5 -&gt; [0, 2, 4, 6, 8, 10, 12, 14, 16, 18, 20, 22, 24, 26, 28, 30]
-  색인 20 만 1000, 나머지 0 -&gt; [0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 20]</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
+[산출 근거] 점수 = (진폭 &lt;&lt; 5) | (31 - 색인). 같은 진폭이면 색인이 작은 쪽이 큰 점수를 가지므로 저주파가 보호된다. 32 개 중 16 개를 골라 색인 오름차순으로 낸다. 벡터 나가 저주파 보호 규칙을 확인하는 시험이다.
+[판정] 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
+1) 입력 : 벡터 가 : 진폭[i] = i x 10  (0, 10, 20, ... 310)
+   예상 출력 : 16 17 18 19 20 21 22 23 24 25 26 27 28 29 30 31
+2) 입력 : 벡터 나 : 진폭 32 개가 모두 100 (동점)
+   예상 출력 : 0 1 2 3 4 5 6 7 8 9 10 11 12 13 14 15   &lt;- 같은 크기면 저주파가 살아남는다
+3) 입력 : 벡터 다 : 짝수 색인 200, 홀수 색인 5
+   예상 출력 : 0 2 4 6 8 10 12 14 16 18 20 22 24 26 28 30
+4) 입력 : 벡터 라 : 색인 20 만 1000, 나머지 0
+   예상 출력 : 0 1 2 3 4 5 6 7 8 9 10 11 12 13 14 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="125" customHeight="1">
       <c r="B113" s="8" t="inlineStr"/>
       <c r="C113" s="8" t="inlineStr"/>
       <c r="D113" s="9" t="inlineStr">
@@ -4808,32 +4957,41 @@
       </c>
       <c r="H113" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 빌드 설정에 TDC_UNIT_TEST 를 정의한다.
+- src/1__cfx/test/tdc_unit_test_cfx.c 를 빌드에 넣는다.
+- 기존 소스는 수정하지 않는다. 매크로가 없으면 이 파일은 빈 번역 단위가 된다.
+- 디버거에서 tdc_ut_run_all() 을 호출한다.
+- tdc_ut_done 에 1 이 대입되는 지점에 중단점을 걸고 tdc_ut_result 를 조회한다.
+- 하네스가 벡터마다 g_NofM_adjacent_BandIndex[0..15] 를 채운다.</t>
         </is>
       </c>
       <c r="I113" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 결과 배열에서 값 -999 는 구분자다. 그 다음 값이 유닛 번호다.
+- 시험은 전역 상태를 바꾼다. 시험 후에는 장치를 재기동한다.
+- 시험 코드는 평시 빌드에서 제외되므로 정상 동작에 영향을 주지 않는다.</t>
         </is>
       </c>
       <c r="J113" s="9" t="inlineStr">
         <is>
-          <t>- 빌드 설정에 TDC_UNIT_TEST 를 정의하고 시험 파일을 빌드에 넣는다.
-- 디버거에서 시험 진입점을 호출한다.
-- done 변수에 중단점을 걸고 결과 배열을 조회한다.
-- 실기 시험 절차서의 기댓값과 대조한다.</t>
+          <t>- 하네스가 아래 두 벡터를 차례로 선택 버퍼에 넣고 원 함수를 호출한다.
+- 구분자 -999 와 유닛 번호 88 다음에 결과 32 개(벡터당 16 개)가 이어진다.
+- g_NofM_notAdjacent_BandIndex[0..15] 를 벡터마다 조회한다.</t>
         </is>
       </c>
       <c r="K113" s="9" t="inlineStr">
         <is>
           <t>- NofM 인터리빙 구현
-- 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
-  입력 [0, 1, 2, 3, 4, 5, 6, 7, 8, 9, 10, 11, 12, 13, 14, 15] -&gt; [0, 8, 1, 9, 2, 10, 3, 11, 4, 12, 5, 13, 6, 14, 7, 15]
-  앞 시험 «짝수 색인 200» 의 선택 결과 [0, 2, 4, 6, 8, 10, 12, 14, 16, 18, 20, 22, 24, 26, 28, 30] -&gt; [0, 16, 2, 18, 4, 20, 6, 22, 8, 24, 10, 26, 12, 28, 14, 30]</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
+[산출 근거] 16 개를 앞 8 개와 뒤 8 개로 나눠 한 칸씩 번갈아 배치한다. 출력[i x 2] = 입력[i], 출력[i x 2 + 1] = 입력[i + 8] 이다. 인접 전극이 잇달아 자극되지 않게 하는 처리다.
+[판정] 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
+1) 입력 : 벡터 가 : 선택 결과를 0 1 2 3 ... 15 로 둔 뒤 호출
+   예상 출력 : 0 8 1 9 2 10 3 11 4 12 5 13 6 14 7 15
+2) 입력 : 벡터 나 : 앞 시험의 «짝수 색인 200» 선택 결과 (0 2 4 6 8 10 12 14 16 18 20 22 24 26 28 30) 로 둔 뒤 호출
+   예상 출력 : 0 16 2 18 4 20 6 22 8 24 10 26 12 28 14 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="112.5" customHeight="1">
       <c r="B114" s="8" t="inlineStr"/>
       <c r="C114" s="8" t="inlineStr"/>
       <c r="D114" s="9" t="inlineStr">
@@ -4858,28 +5016,38 @@
       </c>
       <c r="H114" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 빌드 설정에 TDC_UNIT_TEST 를 정의한다.
+- src/1__cfx/test/tdc_unit_test_cfx.c 를 빌드에 넣는다.
+- 기존 소스는 수정하지 않는다. 매크로가 없으면 이 파일은 빈 번역 단위가 된다.
+- 디버거에서 tdc_ut_run_all() 을 호출한다.
+- tdc_ut_done 에 1 이 대입되는 지점에 중단점을 걸고 tdc_ut_result 를 조회한다.
+- PCM 기록 버퍼(HEAR_ADDR_FIFO_PCM_WRITING)를 조회할 수 있게 창을 준비한다.</t>
         </is>
       </c>
       <c r="I114" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 이 유닛의 출력은 DSP 라이브러리 또는 HEAR 함수체인 결과에 의존한다.
+- 기댓값을 미리 낼 수 없으므로 실측값을 기록한다.
+- 고정소수점 연산 차이를 고려하여 판정한다.</t>
         </is>
       </c>
       <c r="J114" s="9" t="inlineStr">
         <is>
-          <t>- 해당 유닛을 실행시키고 디버깅용 중단점을 적용하여 출력 데이터를 확인한다.
-- 라이브러리 출력에 의존하므로 실측값을 기록한다.</t>
+          <t>- 호출 후 만들어진 패킷 값을 조회해 전극 번호와 자극 레벨이 자리에 맞는지 기록한다.</t>
         </is>
       </c>
       <c r="K114" s="9" t="inlineStr">
         <is>
           <t>- NofM 패킷 생성 구현
-- 실기 시험 절차서의 기댓값과 일치해야 한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
+[산출 근거] 선택된 대역의 자극 레벨을 패킷으로 만든다. 매핑 결과에 의존한다. 기댓값을 미리 낼 수 없으므로 지어내지 않는다.
+[판정] 기댓값을 미리 낼 수 없다. 아래 항목의 실측값을 기록한다.
+       고정소수점 연산 차이를 고려하여 판정한다.
+1) 입력 : 시험 벡터 주입
+   예상 출력 : (실측 기록)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="112.5" customHeight="1">
       <c r="B115" s="8" t="inlineStr"/>
       <c r="C115" s="8" t="inlineStr"/>
       <c r="D115" s="9" t="inlineStr">
@@ -4904,28 +5072,38 @@
       </c>
       <c r="H115" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 빌드 설정에 TDC_UNIT_TEST 를 정의한다.
+- src/1__cfx/test/tdc_unit_test_cfx.c 를 빌드에 넣는다.
+- 기존 소스는 수정하지 않는다. 매크로가 없으면 이 파일은 빈 번역 단위가 된다.
+- 디버거에서 tdc_ut_run_all() 을 호출한다.
+- tdc_ut_done 에 1 이 대입되는 지점에 중단점을 걸고 tdc_ut_result 를 조회한다.
+- PCM 기록 버퍼(HEAR_ADDR_FIFO_PCM_WRITING)를 조회할 수 있게 창을 준비한다.</t>
         </is>
       </c>
       <c r="I115" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 이 유닛의 출력은 DSP 라이브러리 또는 HEAR 함수체인 결과에 의존한다.
+- 기댓값을 미리 낼 수 없으므로 실측값을 기록한다.
+- 고정소수점 연산 차이를 고려하여 판정한다.</t>
         </is>
       </c>
       <c r="J115" s="9" t="inlineStr">
         <is>
-          <t>- 해당 유닛을 실행시키고 디버깅용 중단점을 적용하여 출력 데이터를 확인한다.
-- 라이브러리 출력에 의존하므로 실측값을 기록한다.</t>
+          <t>- 호출 전후의 PCM 기록 버퍼를 조회해 기록 위치와 내용을 기록한다.</t>
         </is>
       </c>
       <c r="K115" s="9" t="inlineStr">
         <is>
           <t>- NofM PCM 기록 구현
-- 실기 시험 절차서의 기댓값과 일치해야 한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
+[산출 근거] 만들어진 패킷을 PCM 버퍼에 기록한다. 앞단 결과에 의존한다. 기댓값을 미리 낼 수 없으므로 지어내지 않는다.
+[판정] 기댓값을 미리 낼 수 없다. 아래 항목의 실측값을 기록한다.
+       고정소수점 연산 차이를 고려하여 판정한다.
+1) 입력 : 시험 벡터 주입
+   예상 출력 : (실측 기록)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="37.5" customHeight="1">
       <c r="B116" s="8" t="inlineStr"/>
       <c r="C116" s="8" t="inlineStr">
         <is>
@@ -4975,7 +5153,7 @@
         </is>
       </c>
     </row>
-    <row r="117">
+    <row r="117" ht="125" customHeight="1">
       <c r="B117" s="8" t="inlineStr"/>
       <c r="C117" s="8" t="inlineStr"/>
       <c r="D117" s="9" t="inlineStr">
@@ -5000,28 +5178,44 @@
       </c>
       <c r="H117" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 빌드 설정에 TDC_UNIT_TEST 를 정의한다.
+- src/1__cfx/test/tdc_unit_test_cfx.c 를 빌드에 넣는다.
+- 기존 소스는 수정하지 않는다. 매크로가 없으면 이 파일은 빈 번역 단위가 된다.
+- 디버거에서 tdc_ut_run_all() 을 호출한다.
+- tdc_ut_done 에 1 이 대입되는 지점에 중단점을 걸고 tdc_ut_result 를 조회한다.
+- PCM 기록 버퍼(HEAR_ADDR_FIFO_PCM_WRITING)를 조회할 수 있게 창을 준비한다.
+- 공유 메모리의 PCM 모드 항목도 함께 조회할 수 있게 한다.</t>
         </is>
       </c>
       <c r="I117" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 결과 배열에서 값 -999 는 구분자다. 그 다음 값이 유닛 번호다.
+- 시험은 전역 상태를 바꾼다. 시험 후에는 장치를 재기동한다.
+- 시험 코드는 평시 빌드에서 제외되므로 정상 동작에 영향을 주지 않는다.
+- 버퍼 기록 방향이 감소 방향이다. 시작 주소에서 아래로 24 칸을 본다.
+- 호출마다 상태가 바뀌므로 두 번 연속 호출해 두 갈래를 모두 본다.</t>
         </is>
       </c>
       <c r="J117" s="9" t="inlineStr">
         <is>
-          <t>- 해당 유닛을 실행시키고 디버깅용 중단점을 적용하여 출력 데이터를 확인한다.
-- 라이브러리 출력에 의존하므로 실측값을 기록한다.</t>
+          <t>- PCM 상태 초기화 유닛을 먼저 호출해 상태를 영 채움으로 둔다.
+- 원 함수를 한 번 호출하고 버퍼 24 칸을 조회한다. (1 회차)
+- 원 함수를 한 번 더 호출하고 버퍼 24 칸과 PCM 모드를 조회한다. (2 회차)</t>
         </is>
       </c>
       <c r="K117" s="9" t="inlineStr">
         <is>
           <t>- 프리앰블 생성 구현
-- 실기 시험 절차서의 기댓값과 일치해야 한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
+[산출 근거] 상태 변수 g_pcmPreambleState 에 따라 두 갈래로 동작하고 호출마다 상태가 바뀐다. 영 채움 단계에서는 24 칸을 0 으로 채우고 상태를 토글로 옮긴다. 토글 단계에서는 23 칸을 0xFFFFF 로 채우고 마지막 한 칸에 프리앰블 몰드 0xFF555 를 넣은 뒤, PCM 모드를 대기로 바꾸고 상태를 영 채움으로 되돌린다.
+[판정] 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
+1) 입력 : 1 회차 : 상태가 영 채움인 상태에서 호출
+   예상 출력 : 24 칸 모두 0. 상태가 토글로 바뀐다.
+2) 입력 : 2 회차 : 이어서 한 번 더 호출
+   예상 출력 : 앞 23 칸은 0xFFFFF, 마지막 1 칸은 0xFF555. PCM 모드가 대기로 바뀌고 상태가 영 채움으로 되돌아간다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="112.5" customHeight="1">
       <c r="B118" s="8" t="inlineStr"/>
       <c r="C118" s="8" t="inlineStr"/>
       <c r="D118" s="9" t="inlineStr">
@@ -5046,28 +5240,39 @@
       </c>
       <c r="H118" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 빌드 설정에 TDC_UNIT_TEST 를 정의한다.
+- src/1__cfx/test/tdc_unit_test_cfx.c 를 빌드에 넣는다.
+- 기존 소스는 수정하지 않는다. 매크로가 없으면 이 파일은 빈 번역 단위가 된다.
+- 디버거에서 tdc_ut_run_all() 을 호출한다.
+- tdc_ut_done 에 1 이 대입되는 지점에 중단점을 걸고 tdc_ut_result 를 조회한다.
+- PCM 기록 버퍼(HEAR_ADDR_FIFO_PCM_WRITING)를 조회할 수 있게 창을 준비한다.</t>
         </is>
       </c>
       <c r="I118" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 이 유닛의 출력은 DSP 라이브러리 또는 HEAR 함수체인 결과에 의존한다.
+- 기댓값을 미리 낼 수 없으므로 실측값을 기록한다.
+- 고정소수점 연산 차이를 고려하여 판정한다.</t>
         </is>
       </c>
       <c r="J118" s="9" t="inlineStr">
         <is>
-          <t>- 해당 유닛을 실행시키고 디버깅용 중단점을 적용하여 출력 데이터를 확인한다.
-- 라이브러리 출력에 의존하므로 실측값을 기록한다.</t>
+          <t>- 호출 후 PCM 기록 버퍼 24 칸을 조회해 자극용 헤더, 전극 번호, 자극 레벨을 기록한다.
+- 채널당 프레임 수를 1 과 2 로 바꿔 가며 각각 기록한다.</t>
         </is>
       </c>
       <c r="K118" s="9" t="inlineStr">
         <is>
           <t>- 실시간 자극 비트스트림 생성 구현
-- 실기 시험 절차서의 기댓값과 일치해야 한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
+[산출 근거] 실시간 자극 데이터를 비트스트림으로 만든다. 자극 기법 결과에 의존한다. 기댓값을 미리 낼 수 없으므로 지어내지 않는다.
+[판정] 기댓값을 미리 낼 수 없다. 아래 항목의 실측값을 기록한다.
+       고정소수점 연산 차이를 고려하여 판정한다.
+1) 입력 : 시험 벡터 주입
+   예상 출력 : (실측 기록)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="112.5" customHeight="1">
       <c r="B119" s="8" t="inlineStr"/>
       <c r="C119" s="8" t="inlineStr"/>
       <c r="D119" s="9" t="inlineStr">
@@ -5092,28 +5297,39 @@
       </c>
       <c r="H119" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 빌드 설정에 TDC_UNIT_TEST 를 정의한다.
+- src/1__cfx/test/tdc_unit_test_cfx.c 를 빌드에 넣는다.
+- 기존 소스는 수정하지 않는다. 매크로가 없으면 이 파일은 빈 번역 단위가 된다.
+- 디버거에서 tdc_ut_run_all() 을 호출한다.
+- tdc_ut_done 에 1 이 대입되는 지점에 중단점을 걸고 tdc_ut_result 를 조회한다.
+- PCM 기록 버퍼(HEAR_ADDR_FIFO_PCM_WRITING)를 조회할 수 있게 창을 준비한다.</t>
         </is>
       </c>
       <c r="I119" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 이 유닛의 출력은 DSP 라이브러리 또는 HEAR 함수체인 결과에 의존한다.
+- 기댓값을 미리 낼 수 없으므로 실측값을 기록한다.
+- 고정소수점 연산 차이를 고려하여 판정한다.</t>
         </is>
       </c>
       <c r="J119" s="9" t="inlineStr">
         <is>
-          <t>- 해당 유닛을 실행시키고 디버깅용 중단점을 적용하여 출력 데이터를 확인한다.
-- 라이브러리 출력에 의존하므로 실측값을 기록한다.</t>
+          <t>- 특정 명령 버퍼에 알려진 값을 넣고 호출한다.
+- PCM 기록 버퍼 24 칸이 그 값과 같은지 조회해 기록한다.</t>
         </is>
       </c>
       <c r="K119" s="9" t="inlineStr">
         <is>
           <t>- 특정 명령 비트스트림 생성 구현
-- 실기 시험 절차서의 기댓값과 일치해야 한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
+[산출 근거] 공유 메모리의 특정 명령 버퍼 내용을 그대로 내보낸다. 버퍼 내용에 의존한다. 기댓값을 미리 낼 수 없으므로 지어내지 않는다.
+[판정] 기댓값을 미리 낼 수 없다. 아래 항목의 실측값을 기록한다.
+       고정소수점 연산 차이를 고려하여 판정한다.
+1) 입력 : 시험 벡터 주입
+   예상 출력 : (실측 기록)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="100" customHeight="1">
       <c r="B120" s="8" t="inlineStr"/>
       <c r="C120" s="8" t="inlineStr"/>
       <c r="D120" s="9" t="inlineStr">
@@ -5138,28 +5354,40 @@
       </c>
       <c r="H120" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 빌드 설정에 TDC_UNIT_TEST 를 정의한다.
+- src/1__cfx/test/tdc_unit_test_cfx.c 를 빌드에 넣는다.
+- 기존 소스는 수정하지 않는다. 매크로가 없으면 이 파일은 빈 번역 단위가 된다.
+- 디버거에서 tdc_ut_run_all() 을 호출한다.
+- tdc_ut_done 에 1 이 대입되는 지점에 중단점을 걸고 tdc_ut_result 를 조회한다.
+- PCM 기록 버퍼(HEAR_ADDR_FIFO_PCM_WRITING)를 조회할 수 있게 창을 준비한다.</t>
         </is>
       </c>
       <c r="I120" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 결과 배열에서 값 -999 는 구분자다. 그 다음 값이 유닛 번호다.
+- 시험은 전역 상태를 바꾼다. 시험 후에는 장치를 재기동한다.
+- 시험 코드는 평시 빌드에서 제외되므로 정상 동작에 영향을 주지 않는다.
+- 버퍼 기록 방향이 감소 방향이다. 시작 주소에서 아래로 24 칸을 본다.</t>
         </is>
       </c>
       <c r="J120" s="9" t="inlineStr">
         <is>
-          <t>- 해당 유닛을 실행시키고 디버깅용 중단점을 적용하여 출력 데이터를 확인한다.
-- 라이브러리 출력에 의존하므로 실측값을 기록한다.</t>
+          <t>- 버퍼를 미리 다른 값(예: 0x12345)으로 채워 둔다.
+- 원 함수를 한 번 호출한다.
+- 기록 버퍼 시작 주소부터 감소 방향으로 24 칸을 조회한다.</t>
         </is>
       </c>
       <c r="K120" s="9" t="inlineStr">
         <is>
           <t>- 대기 비트스트림 생성 구현
-- 실기 시험 절차서의 기댓값과 일치해야 한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
+[산출 근거] PCM 기록 버퍼 시작 주소부터 감소 방향으로 24 칸을 같은 값으로 채운다. 채우는 값은 0x25555 다.
+[판정] 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
+1) 입력 : 버퍼를 0x12345 로 채운 뒤 호출
+   예상 출력 : 24 칸 모두 0x25555</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="100" customHeight="1">
       <c r="B121" s="8" t="inlineStr"/>
       <c r="C121" s="8" t="inlineStr"/>
       <c r="D121" s="9" t="inlineStr">
@@ -5184,28 +5412,40 @@
       </c>
       <c r="H121" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 빌드 설정에 TDC_UNIT_TEST 를 정의한다.
+- src/1__cfx/test/tdc_unit_test_cfx.c 를 빌드에 넣는다.
+- 기존 소스는 수정하지 않는다. 매크로가 없으면 이 파일은 빈 번역 단위가 된다.
+- 디버거에서 tdc_ut_run_all() 을 호출한다.
+- tdc_ut_done 에 1 이 대입되는 지점에 중단점을 걸고 tdc_ut_result 를 조회한다.
+- PCM 기록 버퍼(HEAR_ADDR_FIFO_PCM_WRITING)를 조회할 수 있게 창을 준비한다.</t>
         </is>
       </c>
       <c r="I121" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 결과 배열에서 값 -999 는 구분자다. 그 다음 값이 유닛 번호다.
+- 시험은 전역 상태를 바꾼다. 시험 후에는 장치를 재기동한다.
+- 시험 코드는 평시 빌드에서 제외되므로 정상 동작에 영향을 주지 않는다.
+- 버퍼 기록 방향이 감소 방향이다. 시작 주소에서 아래로 24 칸을 본다.</t>
         </is>
       </c>
       <c r="J121" s="9" t="inlineStr">
         <is>
-          <t>- 해당 유닛을 실행시키고 디버깅용 중단점을 적용하여 출력 데이터를 확인한다.
-- 라이브러리 출력에 의존하므로 실측값을 기록한다.</t>
+          <t>- 버퍼를 미리 다른 값(예: 0x12345)으로 채워 둔다.
+- 원 함수를 한 번 호출한다.
+- 기록 버퍼 시작 주소부터 감소 방향으로 24 칸을 조회한다.</t>
         </is>
       </c>
       <c r="K121" s="9" t="inlineStr">
         <is>
           <t>- 연결 검사용 비트스트림 생성 구현
-- 실기 시험 절차서의 기댓값과 일치해야 한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
+[산출 근거] PCM 기록 버퍼 시작 주소부터 감소 방향으로 24 칸을 같은 값으로 채운다. 채우는 값은 0x35555 다.
+[판정] 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
+1) 입력 : 버퍼를 0x12345 로 채운 뒤 호출
+   예상 출력 : 24 칸 모두 0x35555</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="100" customHeight="1">
       <c r="B122" s="8" t="inlineStr"/>
       <c r="C122" s="8" t="inlineStr"/>
       <c r="D122" s="9" t="inlineStr">
@@ -5230,28 +5470,40 @@
       </c>
       <c r="H122" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 빌드 설정에 TDC_UNIT_TEST 를 정의한다.
+- src/1__cfx/test/tdc_unit_test_cfx.c 를 빌드에 넣는다.
+- 기존 소스는 수정하지 않는다. 매크로가 없으면 이 파일은 빈 번역 단위가 된다.
+- 디버거에서 tdc_ut_run_all() 을 호출한다.
+- tdc_ut_done 에 1 이 대입되는 지점에 중단점을 걸고 tdc_ut_result 를 조회한다.
+- PCM 기록 버퍼(HEAR_ADDR_FIFO_PCM_WRITING)를 조회할 수 있게 창을 준비한다.</t>
         </is>
       </c>
       <c r="I122" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 결과 배열에서 값 -999 는 구분자다. 그 다음 값이 유닛 번호다.
+- 시험은 전역 상태를 바꾼다. 시험 후에는 장치를 재기동한다.
+- 시험 코드는 평시 빌드에서 제외되므로 정상 동작에 영향을 주지 않는다.
+- 버퍼 기록 방향이 감소 방향이다. 시작 주소에서 아래로 24 칸을 본다.</t>
         </is>
       </c>
       <c r="J122" s="9" t="inlineStr">
         <is>
-          <t>- 해당 유닛을 실행시키고 디버깅용 중단점을 적용하여 출력 데이터를 확인한다.
-- 라이브러리 출력에 의존하므로 실측값을 기록한다.</t>
+          <t>- 버퍼를 미리 다른 값(예: 0x12345)으로 채워 둔다.
+- 원 함수를 한 번 호출한다.
+- 기록 버퍼 시작 주소부터 감소 방향으로 24 칸을 조회한다.</t>
         </is>
       </c>
       <c r="K122" s="9" t="inlineStr">
         <is>
           <t>- 영 채움 생성 구현
-- 실기 시험 절차서의 기댓값과 일치해야 한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
+[산출 근거] PCM 기록 버퍼 시작 주소부터 감소 방향으로 24 칸을 같은 값으로 채운다. 채우는 값은 0x00000 다.
+[판정] 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
+1) 입력 : 버퍼를 0x12345 로 채운 뒤 호출
+   예상 출력 : 24 칸 모두 0x00000</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="12.5" customHeight="1">
       <c r="B123" s="8" t="inlineStr"/>
       <c r="C123" s="8" t="inlineStr"/>
       <c r="D123" s="9" t="inlineStr">
@@ -5295,7 +5547,7 @@
         </is>
       </c>
     </row>
-    <row r="124">
+    <row r="124" ht="12.5" customHeight="1">
       <c r="B124" s="8" t="inlineStr"/>
       <c r="C124" s="8" t="inlineStr"/>
       <c r="D124" s="9" t="inlineStr">
@@ -5339,7 +5591,7 @@
         </is>
       </c>
     </row>
-    <row r="125">
+    <row r="125" ht="12.5" customHeight="1">
       <c r="B125" s="8" t="inlineStr"/>
       <c r="C125" s="8" t="inlineStr"/>
       <c r="D125" s="9" t="inlineStr">
@@ -5383,7 +5635,7 @@
         </is>
       </c>
     </row>
-    <row r="126">
+    <row r="126" ht="112.5" customHeight="1">
       <c r="B126" s="8" t="inlineStr"/>
       <c r="C126" s="8" t="inlineStr"/>
       <c r="D126" s="9" t="inlineStr">
@@ -5408,28 +5660,39 @@
       </c>
       <c r="H126" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 빌드 설정에 TDC_UNIT_TEST 를 정의한다.
+- src/1__cfx/test/tdc_unit_test_cfx.c 를 빌드에 넣는다.
+- 기존 소스는 수정하지 않는다. 매크로가 없으면 이 파일은 빈 번역 단위가 된다.
+- 디버거에서 tdc_ut_run_all() 을 호출한다.
+- tdc_ut_done 에 1 이 대입되는 지점에 중단점을 걸고 tdc_ut_result 를 조회한다.
+- PCM 기록 버퍼(HEAR_ADDR_FIFO_PCM_WRITING)를 조회할 수 있게 창을 준비한다.</t>
         </is>
       </c>
       <c r="I126" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 이 유닛의 출력은 DSP 라이브러리 또는 HEAR 함수체인 결과에 의존한다.
+- 기댓값을 미리 낼 수 없으므로 실측값을 기록한다.
+- 고정소수점 연산 차이를 고려하여 판정한다.</t>
         </is>
       </c>
       <c r="J126" s="9" t="inlineStr">
         <is>
-          <t>- 해당 유닛을 실행시키고 디버깅용 중단점을 적용하여 출력 데이터를 확인한다.
-- 라이브러리 출력에 의존하므로 실측값을 기록한다.</t>
+          <t>- 채널당 프레임 수를 1 로 두고 호출한다.
+- PCM 기록 버퍼를 조회해 검사 프레임 구성과 자극 자리 배치를 기록한다.</t>
         </is>
       </c>
       <c r="K126" s="9" t="inlineStr">
         <is>
           <t>- 채널별 검사 프레임 생성 구현
-- 실기 시험 절차서의 기댓값과 일치해야 한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
+[산출 근거] 채널당 1 프레임 구성으로 검사 프레임을 만든다. 검사 회로 설정에 의존한다. 기댓값을 미리 낼 수 없으므로 지어내지 않는다.
+[판정] 기댓값을 미리 낼 수 없다. 아래 항목의 실측값을 기록한다.
+       고정소수점 연산 차이를 고려하여 판정한다.
+1) 입력 : 시험 벡터 주입
+   예상 출력 : (실측 기록)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="12.5" customHeight="1">
       <c r="B127" s="8" t="inlineStr"/>
       <c r="C127" s="8" t="inlineStr"/>
       <c r="D127" s="9" t="inlineStr">
@@ -5473,7 +5736,7 @@
         </is>
       </c>
     </row>
-    <row r="128">
+    <row r="128" ht="12.5" customHeight="1">
       <c r="B128" s="8" t="inlineStr"/>
       <c r="C128" s="8" t="inlineStr"/>
       <c r="D128" s="9" t="inlineStr">
@@ -5517,7 +5780,7 @@
         </is>
       </c>
     </row>
-    <row r="129">
+    <row r="129" ht="12.5" customHeight="1">
       <c r="B129" s="8" t="inlineStr"/>
       <c r="C129" s="8" t="inlineStr"/>
       <c r="D129" s="9" t="inlineStr">
@@ -5561,7 +5824,7 @@
         </is>
       </c>
     </row>
-    <row r="130">
+    <row r="130" ht="37.5" customHeight="1">
       <c r="B130" s="8" t="inlineStr">
         <is>
           <t>CM3</t>
@@ -5615,7 +5878,7 @@
         </is>
       </c>
     </row>
-    <row r="131">
+    <row r="131" ht="12.5" customHeight="1">
       <c r="B131" s="8" t="inlineStr"/>
       <c r="C131" s="8" t="inlineStr"/>
       <c r="D131" s="9" t="inlineStr">
@@ -5659,7 +5922,7 @@
         </is>
       </c>
     </row>
-    <row r="132">
+    <row r="132" ht="12.5" customHeight="1">
       <c r="B132" s="8" t="inlineStr"/>
       <c r="C132" s="8" t="inlineStr"/>
       <c r="D132" s="9" t="inlineStr">
@@ -5703,7 +5966,7 @@
         </is>
       </c>
     </row>
-    <row r="133">
+    <row r="133" ht="12.5" customHeight="1">
       <c r="B133" s="8" t="inlineStr"/>
       <c r="C133" s="8" t="inlineStr"/>
       <c r="D133" s="9" t="inlineStr">
@@ -5747,7 +6010,7 @@
         </is>
       </c>
     </row>
-    <row r="134">
+    <row r="134" ht="12.5" customHeight="1">
       <c r="B134" s="8" t="inlineStr"/>
       <c r="C134" s="8" t="inlineStr"/>
       <c r="D134" s="9" t="inlineStr">
@@ -5791,7 +6054,7 @@
         </is>
       </c>
     </row>
-    <row r="135">
+    <row r="135" ht="12.5" customHeight="1">
       <c r="B135" s="8" t="inlineStr"/>
       <c r="C135" s="8" t="inlineStr"/>
       <c r="D135" s="9" t="inlineStr">
@@ -5835,7 +6098,7 @@
         </is>
       </c>
     </row>
-    <row r="136">
+    <row r="136" ht="12.5" customHeight="1">
       <c r="B136" s="8" t="inlineStr"/>
       <c r="C136" s="8" t="inlineStr"/>
       <c r="D136" s="9" t="inlineStr">
@@ -5879,7 +6142,7 @@
         </is>
       </c>
     </row>
-    <row r="137">
+    <row r="137" ht="12.5" customHeight="1">
       <c r="B137" s="8" t="inlineStr"/>
       <c r="C137" s="8" t="inlineStr"/>
       <c r="D137" s="9" t="inlineStr">
@@ -5923,7 +6186,7 @@
         </is>
       </c>
     </row>
-    <row r="138">
+    <row r="138" ht="12.5" customHeight="1">
       <c r="B138" s="8" t="inlineStr"/>
       <c r="C138" s="8" t="inlineStr"/>
       <c r="D138" s="9" t="inlineStr">
@@ -5967,7 +6230,7 @@
         </is>
       </c>
     </row>
-    <row r="139">
+    <row r="139" ht="12.5" customHeight="1">
       <c r="B139" s="8" t="inlineStr"/>
       <c r="C139" s="8" t="inlineStr"/>
       <c r="D139" s="9" t="inlineStr">
@@ -6011,7 +6274,7 @@
         </is>
       </c>
     </row>
-    <row r="140">
+    <row r="140" ht="12.5" customHeight="1">
       <c r="B140" s="8" t="inlineStr"/>
       <c r="C140" s="8" t="inlineStr"/>
       <c r="D140" s="9" t="inlineStr">
@@ -6055,7 +6318,7 @@
         </is>
       </c>
     </row>
-    <row r="141">
+    <row r="141" ht="12.5" customHeight="1">
       <c r="B141" s="8" t="inlineStr"/>
       <c r="C141" s="8" t="inlineStr"/>
       <c r="D141" s="9" t="inlineStr">
@@ -6099,7 +6362,7 @@
         </is>
       </c>
     </row>
-    <row r="142">
+    <row r="142" ht="12.5" customHeight="1">
       <c r="B142" s="8" t="inlineStr"/>
       <c r="C142" s="8" t="inlineStr"/>
       <c r="D142" s="9" t="inlineStr">
@@ -6143,7 +6406,7 @@
         </is>
       </c>
     </row>
-    <row r="143">
+    <row r="143" ht="12.5" customHeight="1">
       <c r="B143" s="8" t="inlineStr"/>
       <c r="C143" s="8" t="inlineStr"/>
       <c r="D143" s="9" t="inlineStr">
@@ -6187,7 +6450,7 @@
         </is>
       </c>
     </row>
-    <row r="144">
+    <row r="144" ht="12.5" customHeight="1">
       <c r="B144" s="8" t="inlineStr"/>
       <c r="C144" s="8" t="inlineStr"/>
       <c r="D144" s="9" t="inlineStr">
@@ -6231,7 +6494,7 @@
         </is>
       </c>
     </row>
-    <row r="145">
+    <row r="145" ht="12.5" customHeight="1">
       <c r="B145" s="8" t="inlineStr"/>
       <c r="C145" s="8" t="inlineStr"/>
       <c r="D145" s="9" t="inlineStr">
@@ -6275,7 +6538,7 @@
         </is>
       </c>
     </row>
-    <row r="146">
+    <row r="146" ht="12.5" customHeight="1">
       <c r="B146" s="8" t="inlineStr"/>
       <c r="C146" s="8" t="inlineStr"/>
       <c r="D146" s="9" t="inlineStr">
@@ -6319,7 +6582,7 @@
         </is>
       </c>
     </row>
-    <row r="147">
+    <row r="147" ht="12.5" customHeight="1">
       <c r="B147" s="8" t="inlineStr"/>
       <c r="C147" s="8" t="inlineStr"/>
       <c r="D147" s="9" t="inlineStr">
@@ -6363,7 +6626,7 @@
         </is>
       </c>
     </row>
-    <row r="148">
+    <row r="148" ht="12.5" customHeight="1">
       <c r="B148" s="8" t="inlineStr"/>
       <c r="C148" s="8" t="inlineStr"/>
       <c r="D148" s="9" t="inlineStr">
@@ -6407,7 +6670,7 @@
         </is>
       </c>
     </row>
-    <row r="149">
+    <row r="149" ht="12.5" customHeight="1">
       <c r="B149" s="8" t="inlineStr"/>
       <c r="C149" s="8" t="inlineStr"/>
       <c r="D149" s="9" t="inlineStr">
@@ -6451,7 +6714,7 @@
         </is>
       </c>
     </row>
-    <row r="150">
+    <row r="150" ht="12.5" customHeight="1">
       <c r="B150" s="8" t="inlineStr"/>
       <c r="C150" s="8" t="inlineStr"/>
       <c r="D150" s="9" t="inlineStr">
@@ -6495,7 +6758,7 @@
         </is>
       </c>
     </row>
-    <row r="151">
+    <row r="151" ht="12.5" customHeight="1">
       <c r="B151" s="8" t="inlineStr"/>
       <c r="C151" s="8" t="inlineStr"/>
       <c r="D151" s="9" t="inlineStr">
@@ -6539,7 +6802,7 @@
         </is>
       </c>
     </row>
-    <row r="152">
+    <row r="152" ht="12.5" customHeight="1">
       <c r="B152" s="8" t="inlineStr"/>
       <c r="C152" s="8" t="inlineStr"/>
       <c r="D152" s="9" t="inlineStr">
@@ -6583,7 +6846,7 @@
         </is>
       </c>
     </row>
-    <row r="153">
+    <row r="153" ht="12.5" customHeight="1">
       <c r="B153" s="8" t="inlineStr"/>
       <c r="C153" s="8" t="inlineStr"/>
       <c r="D153" s="9" t="inlineStr">
@@ -6627,7 +6890,7 @@
         </is>
       </c>
     </row>
-    <row r="154">
+    <row r="154" ht="12.5" customHeight="1">
       <c r="B154" s="8" t="inlineStr"/>
       <c r="C154" s="8" t="inlineStr"/>
       <c r="D154" s="9" t="inlineStr">
@@ -6671,7 +6934,7 @@
         </is>
       </c>
     </row>
-    <row r="155">
+    <row r="155" ht="12.5" customHeight="1">
       <c r="B155" s="8" t="inlineStr"/>
       <c r="C155" s="8" t="inlineStr"/>
       <c r="D155" s="9" t="inlineStr">
@@ -6715,7 +6978,7 @@
         </is>
       </c>
     </row>
-    <row r="156">
+    <row r="156" ht="12.5" customHeight="1">
       <c r="B156" s="8" t="inlineStr"/>
       <c r="C156" s="8" t="inlineStr"/>
       <c r="D156" s="9" t="inlineStr">
@@ -6759,7 +7022,7 @@
         </is>
       </c>
     </row>
-    <row r="157">
+    <row r="157" ht="12.5" customHeight="1">
       <c r="B157" s="8" t="inlineStr"/>
       <c r="C157" s="8" t="inlineStr"/>
       <c r="D157" s="9" t="inlineStr">
@@ -6803,7 +7066,7 @@
         </is>
       </c>
     </row>
-    <row r="158">
+    <row r="158" ht="12.5" customHeight="1">
       <c r="B158" s="8" t="inlineStr"/>
       <c r="C158" s="8" t="inlineStr"/>
       <c r="D158" s="9" t="inlineStr">
@@ -6847,7 +7110,7 @@
         </is>
       </c>
     </row>
-    <row r="159">
+    <row r="159" ht="12.5" customHeight="1">
       <c r="B159" s="8" t="inlineStr"/>
       <c r="C159" s="8" t="inlineStr"/>
       <c r="D159" s="9" t="inlineStr">
@@ -6891,7 +7154,7 @@
         </is>
       </c>
     </row>
-    <row r="160">
+    <row r="160" ht="12.5" customHeight="1">
       <c r="B160" s="8" t="inlineStr"/>
       <c r="C160" s="8" t="inlineStr"/>
       <c r="D160" s="9" t="inlineStr">
@@ -6935,7 +7198,7 @@
         </is>
       </c>
     </row>
-    <row r="161">
+    <row r="161" ht="12.5" customHeight="1">
       <c r="B161" s="8" t="inlineStr"/>
       <c r="C161" s="8" t="inlineStr"/>
       <c r="D161" s="9" t="inlineStr">
@@ -6979,7 +7242,7 @@
         </is>
       </c>
     </row>
-    <row r="162">
+    <row r="162" ht="12.5" customHeight="1">
       <c r="B162" s="8" t="inlineStr"/>
       <c r="C162" s="8" t="inlineStr"/>
       <c r="D162" s="9" t="inlineStr">
@@ -7023,7 +7286,7 @@
         </is>
       </c>
     </row>
-    <row r="163">
+    <row r="163" ht="12.5" customHeight="1">
       <c r="B163" s="8" t="inlineStr"/>
       <c r="C163" s="8" t="inlineStr"/>
       <c r="D163" s="9" t="inlineStr">
@@ -7067,7 +7330,7 @@
         </is>
       </c>
     </row>
-    <row r="164">
+    <row r="164" ht="12.5" customHeight="1">
       <c r="B164" s="8" t="inlineStr"/>
       <c r="C164" s="8" t="inlineStr"/>
       <c r="D164" s="9" t="inlineStr">
@@ -7111,7 +7374,7 @@
         </is>
       </c>
     </row>
-    <row r="165">
+    <row r="165" ht="12.5" customHeight="1">
       <c r="B165" s="8" t="inlineStr"/>
       <c r="C165" s="8" t="inlineStr"/>
       <c r="D165" s="9" t="inlineStr">
@@ -7155,7 +7418,7 @@
         </is>
       </c>
     </row>
-    <row r="166">
+    <row r="166" ht="12.5" customHeight="1">
       <c r="B166" s="8" t="inlineStr"/>
       <c r="C166" s="8" t="inlineStr"/>
       <c r="D166" s="9" t="inlineStr">
@@ -7199,7 +7462,7 @@
         </is>
       </c>
     </row>
-    <row r="167">
+    <row r="167" ht="12.5" customHeight="1">
       <c r="B167" s="8" t="inlineStr"/>
       <c r="C167" s="8" t="inlineStr"/>
       <c r="D167" s="9" t="inlineStr">
@@ -7243,7 +7506,7 @@
         </is>
       </c>
     </row>
-    <row r="168">
+    <row r="168" ht="12.5" customHeight="1">
       <c r="B168" s="8" t="inlineStr"/>
       <c r="C168" s="8" t="inlineStr"/>
       <c r="D168" s="9" t="inlineStr">
@@ -7287,7 +7550,7 @@
         </is>
       </c>
     </row>
-    <row r="169">
+    <row r="169" ht="12.5" customHeight="1">
       <c r="B169" s="8" t="inlineStr"/>
       <c r="C169" s="8" t="inlineStr"/>
       <c r="D169" s="9" t="inlineStr">
@@ -7331,7 +7594,7 @@
         </is>
       </c>
     </row>
-    <row r="170">
+    <row r="170" ht="12.5" customHeight="1">
       <c r="B170" s="8" t="inlineStr"/>
       <c r="C170" s="8" t="inlineStr"/>
       <c r="D170" s="9" t="inlineStr">
@@ -7375,7 +7638,7 @@
         </is>
       </c>
     </row>
-    <row r="171">
+    <row r="171" ht="12.5" customHeight="1">
       <c r="B171" s="8" t="inlineStr"/>
       <c r="C171" s="8" t="inlineStr"/>
       <c r="D171" s="9" t="inlineStr">
@@ -7419,7 +7682,7 @@
         </is>
       </c>
     </row>
-    <row r="172">
+    <row r="172" ht="12.5" customHeight="1">
       <c r="B172" s="8" t="inlineStr"/>
       <c r="C172" s="8" t="inlineStr"/>
       <c r="D172" s="9" t="inlineStr">
@@ -7463,7 +7726,7 @@
         </is>
       </c>
     </row>
-    <row r="173">
+    <row r="173" ht="12.5" customHeight="1">
       <c r="B173" s="8" t="inlineStr"/>
       <c r="C173" s="8" t="inlineStr"/>
       <c r="D173" s="9" t="inlineStr">
@@ -7507,7 +7770,7 @@
         </is>
       </c>
     </row>
-    <row r="174">
+    <row r="174" ht="12.5" customHeight="1">
       <c r="B174" s="8" t="inlineStr"/>
       <c r="C174" s="8" t="inlineStr"/>
       <c r="D174" s="9" t="inlineStr">
@@ -7551,7 +7814,7 @@
         </is>
       </c>
     </row>
-    <row r="175">
+    <row r="175" ht="12.5" customHeight="1">
       <c r="B175" s="8" t="inlineStr"/>
       <c r="C175" s="8" t="inlineStr"/>
       <c r="D175" s="9" t="inlineStr">
@@ -7595,7 +7858,7 @@
         </is>
       </c>
     </row>
-    <row r="176">
+    <row r="176" ht="12.5" customHeight="1">
       <c r="B176" s="8" t="inlineStr"/>
       <c r="C176" s="8" t="inlineStr"/>
       <c r="D176" s="9" t="inlineStr">
@@ -7639,7 +7902,7 @@
         </is>
       </c>
     </row>
-    <row r="177">
+    <row r="177" ht="12.5" customHeight="1">
       <c r="B177" s="8" t="inlineStr"/>
       <c r="C177" s="8" t="inlineStr"/>
       <c r="D177" s="9" t="inlineStr">
@@ -7683,7 +7946,7 @@
         </is>
       </c>
     </row>
-    <row r="178">
+    <row r="178" ht="12.5" customHeight="1">
       <c r="B178" s="8" t="inlineStr"/>
       <c r="C178" s="8" t="inlineStr"/>
       <c r="D178" s="9" t="inlineStr">
@@ -7727,7 +7990,7 @@
         </is>
       </c>
     </row>
-    <row r="179">
+    <row r="179" ht="12.5" customHeight="1">
       <c r="B179" s="8" t="inlineStr"/>
       <c r="C179" s="8" t="inlineStr"/>
       <c r="D179" s="9" t="inlineStr">
@@ -7771,7 +8034,7 @@
         </is>
       </c>
     </row>
-    <row r="180">
+    <row r="180" ht="12.5" customHeight="1">
       <c r="B180" s="8" t="inlineStr"/>
       <c r="C180" s="8" t="inlineStr"/>
       <c r="D180" s="9" t="inlineStr">
@@ -7815,7 +8078,7 @@
         </is>
       </c>
     </row>
-    <row r="181">
+    <row r="181" ht="12.5" customHeight="1">
       <c r="B181" s="8" t="inlineStr"/>
       <c r="C181" s="8" t="inlineStr"/>
       <c r="D181" s="9" t="inlineStr">
@@ -7859,7 +8122,7 @@
         </is>
       </c>
     </row>
-    <row r="182">
+    <row r="182" ht="12.5" customHeight="1">
       <c r="B182" s="8" t="inlineStr"/>
       <c r="C182" s="8" t="inlineStr"/>
       <c r="D182" s="9" t="inlineStr">
@@ -7903,7 +8166,7 @@
         </is>
       </c>
     </row>
-    <row r="183">
+    <row r="183" ht="12.5" customHeight="1">
       <c r="B183" s="8" t="inlineStr"/>
       <c r="C183" s="8" t="inlineStr"/>
       <c r="D183" s="9" t="inlineStr">
@@ -7947,7 +8210,7 @@
         </is>
       </c>
     </row>
-    <row r="184">
+    <row r="184" ht="12.5" customHeight="1">
       <c r="B184" s="8" t="inlineStr"/>
       <c r="C184" s="8" t="inlineStr"/>
       <c r="D184" s="9" t="inlineStr">
@@ -7991,7 +8254,7 @@
         </is>
       </c>
     </row>
-    <row r="185">
+    <row r="185" ht="12.5" customHeight="1">
       <c r="B185" s="8" t="inlineStr"/>
       <c r="C185" s="8" t="inlineStr"/>
       <c r="D185" s="9" t="inlineStr">
@@ -8035,7 +8298,7 @@
         </is>
       </c>
     </row>
-    <row r="186">
+    <row r="186" ht="12.5" customHeight="1">
       <c r="B186" s="8" t="inlineStr"/>
       <c r="C186" s="8" t="inlineStr"/>
       <c r="D186" s="9" t="inlineStr">
@@ -8079,7 +8342,7 @@
         </is>
       </c>
     </row>
-    <row r="187">
+    <row r="187" ht="12.5" customHeight="1">
       <c r="B187" s="8" t="inlineStr"/>
       <c r="C187" s="8" t="inlineStr"/>
       <c r="D187" s="9" t="inlineStr">
@@ -8123,7 +8386,7 @@
         </is>
       </c>
     </row>
-    <row r="188">
+    <row r="188" ht="12.5" customHeight="1">
       <c r="B188" s="8" t="inlineStr"/>
       <c r="C188" s="8" t="inlineStr"/>
       <c r="D188" s="9" t="inlineStr">
@@ -8167,7 +8430,7 @@
         </is>
       </c>
     </row>
-    <row r="189">
+    <row r="189" ht="12.5" customHeight="1">
       <c r="B189" s="8" t="inlineStr"/>
       <c r="C189" s="8" t="inlineStr"/>
       <c r="D189" s="9" t="inlineStr">
@@ -8211,7 +8474,7 @@
         </is>
       </c>
     </row>
-    <row r="190">
+    <row r="190" ht="12.5" customHeight="1">
       <c r="B190" s="8" t="inlineStr"/>
       <c r="C190" s="8" t="inlineStr"/>
       <c r="D190" s="9" t="inlineStr">
@@ -8255,7 +8518,7 @@
         </is>
       </c>
     </row>
-    <row r="191">
+    <row r="191" ht="12.5" customHeight="1">
       <c r="B191" s="8" t="inlineStr"/>
       <c r="C191" s="8" t="inlineStr"/>
       <c r="D191" s="9" t="inlineStr">
@@ -8299,7 +8562,7 @@
         </is>
       </c>
     </row>
-    <row r="192">
+    <row r="192" ht="12.5" customHeight="1">
       <c r="B192" s="8" t="inlineStr"/>
       <c r="C192" s="8" t="inlineStr"/>
       <c r="D192" s="9" t="inlineStr">
@@ -8343,7 +8606,7 @@
         </is>
       </c>
     </row>
-    <row r="193">
+    <row r="193" ht="12.5" customHeight="1">
       <c r="B193" s="8" t="inlineStr"/>
       <c r="C193" s="8" t="inlineStr"/>
       <c r="D193" s="9" t="inlineStr">
@@ -8387,7 +8650,7 @@
         </is>
       </c>
     </row>
-    <row r="194">
+    <row r="194" ht="12.5" customHeight="1">
       <c r="B194" s="8" t="inlineStr"/>
       <c r="C194" s="8" t="inlineStr"/>
       <c r="D194" s="9" t="inlineStr">
@@ -8431,7 +8694,7 @@
         </is>
       </c>
     </row>
-    <row r="195">
+    <row r="195" ht="12.5" customHeight="1">
       <c r="B195" s="8" t="inlineStr"/>
       <c r="C195" s="8" t="inlineStr"/>
       <c r="D195" s="9" t="inlineStr">
@@ -8475,7 +8738,7 @@
         </is>
       </c>
     </row>
-    <row r="196">
+    <row r="196" ht="12.5" customHeight="1">
       <c r="B196" s="8" t="inlineStr"/>
       <c r="C196" s="8" t="inlineStr"/>
       <c r="D196" s="9" t="inlineStr">
@@ -8519,7 +8782,7 @@
         </is>
       </c>
     </row>
-    <row r="197">
+    <row r="197" ht="12.5" customHeight="1">
       <c r="B197" s="8" t="inlineStr"/>
       <c r="C197" s="8" t="inlineStr"/>
       <c r="D197" s="9" t="inlineStr">
@@ -8563,7 +8826,7 @@
         </is>
       </c>
     </row>
-    <row r="198">
+    <row r="198" ht="12.5" customHeight="1">
       <c r="B198" s="8" t="inlineStr"/>
       <c r="C198" s="8" t="inlineStr"/>
       <c r="D198" s="9" t="inlineStr">
@@ -8607,7 +8870,7 @@
         </is>
       </c>
     </row>
-    <row r="199">
+    <row r="199" ht="12.5" customHeight="1">
       <c r="B199" s="8" t="inlineStr"/>
       <c r="C199" s="8" t="inlineStr"/>
       <c r="D199" s="9" t="inlineStr">
@@ -8651,7 +8914,7 @@
         </is>
       </c>
     </row>
-    <row r="200">
+    <row r="200" ht="12.5" customHeight="1">
       <c r="B200" s="8" t="inlineStr"/>
       <c r="C200" s="8" t="inlineStr"/>
       <c r="D200" s="9" t="inlineStr">
@@ -8695,7 +8958,7 @@
         </is>
       </c>
     </row>
-    <row r="201">
+    <row r="201" ht="12.5" customHeight="1">
       <c r="B201" s="8" t="inlineStr"/>
       <c r="C201" s="8" t="inlineStr"/>
       <c r="D201" s="9" t="inlineStr">
@@ -8739,7 +9002,7 @@
         </is>
       </c>
     </row>
-    <row r="202">
+    <row r="202" ht="12.5" customHeight="1">
       <c r="B202" s="8" t="inlineStr"/>
       <c r="C202" s="8" t="inlineStr"/>
       <c r="D202" s="9" t="inlineStr">
@@ -8783,7 +9046,7 @@
         </is>
       </c>
     </row>
-    <row r="203">
+    <row r="203" ht="12.5" customHeight="1">
       <c r="B203" s="8" t="inlineStr"/>
       <c r="C203" s="8" t="inlineStr"/>
       <c r="D203" s="9" t="inlineStr">
@@ -8827,7 +9090,7 @@
         </is>
       </c>
     </row>
-    <row r="204">
+    <row r="204" ht="12.5" customHeight="1">
       <c r="B204" s="8" t="inlineStr"/>
       <c r="C204" s="8" t="inlineStr"/>
       <c r="D204" s="9" t="inlineStr">
@@ -8871,7 +9134,7 @@
         </is>
       </c>
     </row>
-    <row r="205">
+    <row r="205" ht="12.5" customHeight="1">
       <c r="B205" s="8" t="inlineStr"/>
       <c r="C205" s="8" t="inlineStr"/>
       <c r="D205" s="9" t="inlineStr">
@@ -8915,7 +9178,7 @@
         </is>
       </c>
     </row>
-    <row r="206">
+    <row r="206" ht="12.5" customHeight="1">
       <c r="B206" s="8" t="inlineStr"/>
       <c r="C206" s="8" t="inlineStr"/>
       <c r="D206" s="9" t="inlineStr">
@@ -8959,7 +9222,7 @@
         </is>
       </c>
     </row>
-    <row r="207">
+    <row r="207" ht="12.5" customHeight="1">
       <c r="B207" s="8" t="inlineStr"/>
       <c r="C207" s="8" t="inlineStr"/>
       <c r="D207" s="9" t="inlineStr">
@@ -9003,7 +9266,7 @@
         </is>
       </c>
     </row>
-    <row r="208">
+    <row r="208" ht="12.5" customHeight="1">
       <c r="B208" s="8" t="inlineStr"/>
       <c r="C208" s="8" t="inlineStr"/>
       <c r="D208" s="9" t="inlineStr">
@@ -9047,7 +9310,7 @@
         </is>
       </c>
     </row>
-    <row r="209">
+    <row r="209" ht="12.5" customHeight="1">
       <c r="B209" s="8" t="inlineStr"/>
       <c r="C209" s="8" t="inlineStr"/>
       <c r="D209" s="9" t="inlineStr">
@@ -9091,7 +9354,7 @@
         </is>
       </c>
     </row>
-    <row r="210">
+    <row r="210" ht="12.5" customHeight="1">
       <c r="B210" s="8" t="inlineStr"/>
       <c r="C210" s="8" t="inlineStr"/>
       <c r="D210" s="9" t="inlineStr">
@@ -9135,7 +9398,7 @@
         </is>
       </c>
     </row>
-    <row r="211">
+    <row r="211" ht="12.5" customHeight="1">
       <c r="B211" s="8" t="inlineStr"/>
       <c r="C211" s="8" t="inlineStr"/>
       <c r="D211" s="9" t="inlineStr">
@@ -9179,7 +9442,7 @@
         </is>
       </c>
     </row>
-    <row r="212">
+    <row r="212" ht="12.5" customHeight="1">
       <c r="B212" s="8" t="inlineStr"/>
       <c r="C212" s="8" t="inlineStr"/>
       <c r="D212" s="9" t="inlineStr">
@@ -9223,7 +9486,7 @@
         </is>
       </c>
     </row>
-    <row r="213">
+    <row r="213" ht="12.5" customHeight="1">
       <c r="B213" s="8" t="inlineStr"/>
       <c r="C213" s="8" t="inlineStr"/>
       <c r="D213" s="9" t="inlineStr">
@@ -9267,7 +9530,7 @@
         </is>
       </c>
     </row>
-    <row r="214">
+    <row r="214" ht="12.5" customHeight="1">
       <c r="B214" s="8" t="inlineStr"/>
       <c r="C214" s="8" t="inlineStr"/>
       <c r="D214" s="9" t="inlineStr">
@@ -9311,7 +9574,7 @@
         </is>
       </c>
     </row>
-    <row r="215">
+    <row r="215" ht="12.5" customHeight="1">
       <c r="B215" s="8" t="inlineStr"/>
       <c r="C215" s="8" t="inlineStr"/>
       <c r="D215" s="9" t="inlineStr">
@@ -9355,7 +9618,7 @@
         </is>
       </c>
     </row>
-    <row r="216">
+    <row r="216" ht="12.5" customHeight="1">
       <c r="B216" s="8" t="inlineStr"/>
       <c r="C216" s="8" t="inlineStr"/>
       <c r="D216" s="9" t="inlineStr">
@@ -9399,7 +9662,7 @@
         </is>
       </c>
     </row>
-    <row r="217">
+    <row r="217" ht="12.5" customHeight="1">
       <c r="B217" s="8" t="inlineStr"/>
       <c r="C217" s="8" t="inlineStr"/>
       <c r="D217" s="9" t="inlineStr">
@@ -9443,7 +9706,7 @@
         </is>
       </c>
     </row>
-    <row r="218">
+    <row r="218" ht="12.5" customHeight="1">
       <c r="B218" s="8" t="inlineStr"/>
       <c r="C218" s="8" t="inlineStr"/>
       <c r="D218" s="9" t="inlineStr">
@@ -9487,7 +9750,7 @@
         </is>
       </c>
     </row>
-    <row r="219">
+    <row r="219" ht="12.5" customHeight="1">
       <c r="B219" s="8" t="inlineStr"/>
       <c r="C219" s="8" t="inlineStr"/>
       <c r="D219" s="9" t="inlineStr">
@@ -9531,7 +9794,7 @@
         </is>
       </c>
     </row>
-    <row r="220">
+    <row r="220" ht="12.5" customHeight="1">
       <c r="B220" s="8" t="inlineStr"/>
       <c r="C220" s="8" t="inlineStr"/>
       <c r="D220" s="9" t="inlineStr">
@@ -9575,7 +9838,7 @@
         </is>
       </c>
     </row>
-    <row r="221">
+    <row r="221" ht="12.5" customHeight="1">
       <c r="B221" s="8" t="inlineStr"/>
       <c r="C221" s="8" t="inlineStr"/>
       <c r="D221" s="9" t="inlineStr">
@@ -9619,7 +9882,7 @@
         </is>
       </c>
     </row>
-    <row r="222">
+    <row r="222" ht="12.5" customHeight="1">
       <c r="B222" s="8" t="inlineStr"/>
       <c r="C222" s="8" t="inlineStr"/>
       <c r="D222" s="9" t="inlineStr">
@@ -9663,7 +9926,7 @@
         </is>
       </c>
     </row>
-    <row r="223">
+    <row r="223" ht="12.5" customHeight="1">
       <c r="B223" s="8" t="inlineStr"/>
       <c r="C223" s="8" t="inlineStr"/>
       <c r="D223" s="9" t="inlineStr">
@@ -9707,7 +9970,7 @@
         </is>
       </c>
     </row>
-    <row r="224">
+    <row r="224" ht="12.5" customHeight="1">
       <c r="B224" s="8" t="inlineStr"/>
       <c r="C224" s="8" t="inlineStr"/>
       <c r="D224" s="9" t="inlineStr">
@@ -9751,7 +10014,7 @@
         </is>
       </c>
     </row>
-    <row r="225">
+    <row r="225" ht="12.5" customHeight="1">
       <c r="B225" s="8" t="inlineStr"/>
       <c r="C225" s="8" t="inlineStr"/>
       <c r="D225" s="9" t="inlineStr">
@@ -9795,7 +10058,7 @@
         </is>
       </c>
     </row>
-    <row r="226">
+    <row r="226" ht="12.5" customHeight="1">
       <c r="B226" s="8" t="inlineStr"/>
       <c r="C226" s="8" t="inlineStr"/>
       <c r="D226" s="9" t="inlineStr">
@@ -9839,7 +10102,7 @@
         </is>
       </c>
     </row>
-    <row r="227">
+    <row r="227" ht="12.5" customHeight="1">
       <c r="B227" s="8" t="inlineStr"/>
       <c r="C227" s="8" t="inlineStr"/>
       <c r="D227" s="9" t="inlineStr">
@@ -9883,7 +10146,7 @@
         </is>
       </c>
     </row>
-    <row r="228">
+    <row r="228" ht="12.5" customHeight="1">
       <c r="B228" s="8" t="inlineStr"/>
       <c r="C228" s="8" t="inlineStr"/>
       <c r="D228" s="9" t="inlineStr">
@@ -9927,7 +10190,7 @@
         </is>
       </c>
     </row>
-    <row r="229">
+    <row r="229" ht="12.5" customHeight="1">
       <c r="B229" s="8" t="inlineStr"/>
       <c r="C229" s="8" t="inlineStr"/>
       <c r="D229" s="9" t="inlineStr">
@@ -9971,7 +10234,7 @@
         </is>
       </c>
     </row>
-    <row r="230">
+    <row r="230" ht="12.5" customHeight="1">
       <c r="B230" s="8" t="inlineStr"/>
       <c r="C230" s="8" t="inlineStr"/>
       <c r="D230" s="9" t="inlineStr">
@@ -10015,7 +10278,7 @@
         </is>
       </c>
     </row>
-    <row r="231">
+    <row r="231" ht="12.5" customHeight="1">
       <c r="B231" s="8" t="inlineStr"/>
       <c r="C231" s="8" t="inlineStr"/>
       <c r="D231" s="9" t="inlineStr">
@@ -10059,7 +10322,7 @@
         </is>
       </c>
     </row>
-    <row r="232">
+    <row r="232" ht="12.5" customHeight="1">
       <c r="B232" s="8" t="inlineStr"/>
       <c r="C232" s="8" t="inlineStr"/>
       <c r="D232" s="9" t="inlineStr">
@@ -10103,7 +10366,7 @@
         </is>
       </c>
     </row>
-    <row r="233">
+    <row r="233" ht="12.5" customHeight="1">
       <c r="B233" s="8" t="inlineStr"/>
       <c r="C233" s="8" t="inlineStr"/>
       <c r="D233" s="9" t="inlineStr">
@@ -10147,7 +10410,7 @@
         </is>
       </c>
     </row>
-    <row r="234">
+    <row r="234" ht="12.5" customHeight="1">
       <c r="B234" s="8" t="inlineStr"/>
       <c r="C234" s="8" t="inlineStr"/>
       <c r="D234" s="9" t="inlineStr">
@@ -10191,7 +10454,7 @@
         </is>
       </c>
     </row>
-    <row r="235">
+    <row r="235" ht="12.5" customHeight="1">
       <c r="B235" s="8" t="inlineStr"/>
       <c r="C235" s="8" t="inlineStr"/>
       <c r="D235" s="9" t="inlineStr">
@@ -10235,7 +10498,7 @@
         </is>
       </c>
     </row>
-    <row r="236">
+    <row r="236" ht="37.5" customHeight="1">
       <c r="B236" s="8" t="inlineStr"/>
       <c r="C236" s="8" t="inlineStr">
         <is>
@@ -10285,7 +10548,7 @@
         </is>
       </c>
     </row>
-    <row r="237">
+    <row r="237" ht="250" customHeight="1">
       <c r="B237" s="8" t="inlineStr"/>
       <c r="C237" s="8" t="inlineStr"/>
       <c r="D237" s="9" t="inlineStr">
@@ -10310,37 +10573,49 @@
       </c>
       <c r="H237" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 빌드 설정에 TDC_UNIT_TEST 를 정의한다.
+- src/2__cm3/Cortex-M3-src/test/tdc_unit_test_cm3.c 를 빌드에 넣는다.
+- 기존 소스는 수정하지 않는다. 매크로가 없으면 이 파일은 빈 번역 단위가 된다.
+- 디버거에서 tdc_ut_cm3_run_all() 을 호출한다.
+- tdc_ut_cm3_done 에 1 이 대입되는 지점에 중단점을 걸고 tdc_ut_cm3_result 를 조회한다.</t>
         </is>
       </c>
       <c r="I237" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 결과 배열에서 값 -999 는 구분자다. 그 다음 값이 유닛 번호다.
+- 시험은 전역 상태를 바꾼다. 시험 후에는 장치를 재기동한다.
+- 시험 코드는 평시 빌드에서 제외되므로 정상 동작에 영향을 주지 않는다.</t>
         </is>
       </c>
       <c r="J237" s="9" t="inlineStr">
         <is>
-          <t>- 빌드 설정에 TDC_UNIT_TEST 를 정의하고 시험 파일을 빌드에 넣는다.
-- 디버거에서 시험 진입점을 호출한다.
-- done 변수에 중단점을 걸고 결과 배열을 조회한다.
-- 실기 시험 절차서의 기댓값과 대조한다.</t>
+          <t>- 하네스가 아래 7 가지 펄스 폭을 차례로 넣어 원 함수를 호출한다.
+- 구분자 -999 와 유닛 번호 108 다음에 결과 7 개가 이어진다.</t>
         </is>
       </c>
       <c r="K237" s="9" t="inlineStr">
         <is>
           <t>- 채널당 프레임 수 산출 구현
-- 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
-  pulsewidth=10 -&gt; 1
-  pulsewidth=20 -&gt; 2
-  pulsewidth=25 -&gt; 2
-  pulsewidth=30 -&gt; 2
-  pulsewidth=40 -&gt; 3
-  pulsewidth=50 -&gt; 3
-  (나머지는 실기 시험 절차서 참조)</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
+[산출 근거] duration = 2 x pulsewidth + 4 + 10 이 41 의 몇 배인지로 정해진다. 상수는 FPGA_oneChannelDataTokenTime 41, FPGA_interphaseGapTokenTime 4, FPGA_electrodAndStimulLevelTokenTime 10 이다.
+[판정] 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
+1) 입력 : pulsewidth=10
+   예상 출력 : 1
+2) 입력 : pulsewidth=20
+   예상 출력 : 2
+3) 입력 : pulsewidth=25
+   예상 출력 : 2
+4) 입력 : pulsewidth=30
+   예상 출력 : 2
+5) 입력 : pulsewidth=40
+   예상 출력 : 3
+6) 입력 : pulsewidth=50
+   예상 출력 : 3
+7) 입력 : pulsewidth=60
+   예상 출력 : 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="375" customHeight="1">
       <c r="B238" s="8" t="inlineStr"/>
       <c r="C238" s="8" t="inlineStr"/>
       <c r="D238" s="9" t="inlineStr">
@@ -10365,36 +10640,61 @@
       </c>
       <c r="H238" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 빌드 설정에 TDC_UNIT_TEST 를 정의한다.
+- src/2__cm3/Cortex-M3-src/test/tdc_unit_test_cm3.c 를 빌드에 넣는다.
+- 기존 소스는 수정하지 않는다. 매크로가 없으면 이 파일은 빈 번역 단위가 된다.
+- 디버거에서 tdc_ut_cm3_run_all() 을 호출한다.
+- tdc_ut_cm3_done 에 1 이 대입되는 지점에 중단점을 걸고 tdc_ut_cm3_result 를 조회한다.</t>
         </is>
       </c>
       <c r="I238" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 결과 배열에서 값 -999 는 구분자다. 그 다음 값이 유닛 번호다.
+- 시험은 전역 상태를 바꾼다. 시험 후에는 장치를 재기동한다.
+- 시험 코드는 평시 빌드에서 제외되므로 정상 동작에 영향을 주지 않는다.
+- 뒤 6 개는 둘째 인자만 8 로 바꾼 대조 시험이다.</t>
         </is>
       </c>
       <c r="J238" s="9" t="inlineStr">
         <is>
-          <t>- 빌드 설정에 TDC_UNIT_TEST 를 정의하고 시험 파일을 빌드에 넣는다.
-- 디버거에서 시험 진입점을 호출한다.
-- done 변수에 중단점을 걸고 결과 배열을 조회한다.
-- 실기 시험 절차서의 기댓값과 대조한다.</t>
+          <t>- 하네스가 앞 6 가지 조합을 넣고, 이어서 둘째 인자만 8 로 바꿔 6 회를 더 호출한다.
+- 구분자 -999 와 유닛 번호 109 다음에 결과 12 개가 이어진다.
+- 앞 6 개와 뒤 6 개가 완전히 같은지 확인한다. 다르면 둘째 인자를 쓰는 경로가 살아 있는 것이다.</t>
         </is>
       </c>
       <c r="K238" s="9" t="inlineStr">
         <is>
           <t>- 전달 가능 채널 수 산출 구현
-- 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
-  numFramePerChannel=1, usableElectrodNum=16 -&gt; 24
-  numFramePerChannel=2, usableElectrodNum=16 -&gt; 12
-  numFramePerChannel=3, usableElectrodNum=16 -&gt; 8
-  numFramePerChannel=4, usableElectrodNum=22 -&gt; 6
-  numFramePerChannel=5, usableElectrodNum=22 -&gt; 4
-  numFramePerChannel=8, usableElectrodNum=22 -&gt; 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
+[산출 근거] 활성 경로는 df_MaxNumTransferableChannel(24) / numFramePerChannel 한 줄뿐이고 둘째 인자를 쓰지 않는다. 둘째 인자를 바꿔도 결과가 같아야 한다는 것까지 시험한다.
+[판정] 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
+1) 입력 : numFramePerChannel=1, usableElectrodNum=16
+   예상 출력 : 24
+2) 입력 : numFramePerChannel=2, usableElectrodNum=16
+   예상 출력 : 12
+3) 입력 : numFramePerChannel=3, usableElectrodNum=16
+   예상 출력 : 8
+4) 입력 : numFramePerChannel=4, usableElectrodNum=22
+   예상 출력 : 6
+5) 입력 : numFramePerChannel=5, usableElectrodNum=22
+   예상 출력 : 4
+6) 입력 : numFramePerChannel=8, usableElectrodNum=22
+   예상 출력 : 3
+7) 입력 : numFramePerChannel=1, usableElectrodNum=8 (대조)
+   예상 출력 : 24 (앞의 같은 프레임 수 결과와 같아야 한다)
+8) 입력 : numFramePerChannel=2, usableElectrodNum=8 (대조)
+   예상 출력 : 12 (앞의 같은 프레임 수 결과와 같아야 한다)
+9) 입력 : numFramePerChannel=3, usableElectrodNum=8 (대조)
+   예상 출력 : 8 (앞의 같은 프레임 수 결과와 같아야 한다)
+10) 입력 : numFramePerChannel=4, usableElectrodNum=8 (대조)
+   예상 출력 : 6 (앞의 같은 프레임 수 결과와 같아야 한다)
+11) 입력 : numFramePerChannel=5, usableElectrodNum=8 (대조)
+   예상 출력 : 4 (앞의 같은 프레임 수 결과와 같아야 한다)
+12) 입력 : numFramePerChannel=8, usableElectrodNum=8 (대조)
+   예상 출력 : 3 (앞의 같은 프레임 수 결과와 같아야 한다)</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="112.5" customHeight="1">
       <c r="B239" s="8" t="inlineStr"/>
       <c r="C239" s="8" t="inlineStr"/>
       <c r="D239" s="9" t="inlineStr">
@@ -10419,30 +10719,34 @@
       </c>
       <c r="H239" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 대상 유닛이 호출되는 지점에 디버깅용 중단점을 적용한다.
+- 입력 버퍼와 출력 버퍼를 함께 조회할 수 있도록 창을 준비한다.</t>
         </is>
       </c>
       <c r="I239" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 이 유닛의 출력은 DSP 라이브러리 또는 HEAR 함수체인 결과에 의존한다.
+- 기댓값을 미리 낼 수 없으므로 실측값을 기록한다.
+- 고정소수점 연산 차이를 고려하여 판정한다.</t>
         </is>
       </c>
       <c r="J239" s="9" t="inlineStr">
         <is>
-          <t>- 해당 유닛을 실행시키고 디버깅용 중단점을 적용하여 출력 데이터를 확인한다.
-- 라이브러리 출력에 의존하므로 실측값을 기록한다.</t>
+          <t>- 호출 후 255 단계로 환산된 T 레벨과 C 레벨 배열을 조회해 기록한다.</t>
         </is>
       </c>
       <c r="K239" s="9" t="inlineStr">
         <is>
           <t>- 자극 범위 설정 구현
-- 출력단 보정 설정과 맵 데이터에 의존한다.
-- 기댓값을 미리 낼 수 없다. 실측값을 기록한다.
-- (고정소수점 연산 고려)</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
+[산출 근거] 출력단 보정 설정과 맵 데이터에 의존한다. 기댓값을 미리 낼 수 없으므로 지어내지 않는다.
+[판정] 기댓값을 미리 낼 수 없다. 아래 항목의 실측값을 기록한다.
+       고정소수점 연산 차이를 고려하여 판정한다.
+1) 입력 : 시험 벡터 주입
+   예상 출력 : (실측 기록)</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="100" customHeight="1">
       <c r="B240" s="8" t="inlineStr"/>
       <c r="C240" s="8" t="inlineStr"/>
       <c r="D240" s="9" t="inlineStr">
@@ -10467,31 +10771,38 @@
       </c>
       <c r="H240" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 빌드 설정에 TDC_UNIT_TEST 를 정의한다.
+- src/2__cm3/Cortex-M3-src/test/tdc_unit_test_cm3.c 를 빌드에 넣는다.
+- 기존 소스는 수정하지 않는다. 매크로가 없으면 이 파일은 빈 번역 단위가 된다.
+- 디버거에서 tdc_ut_cm3_run_all() 을 호출한다.
+- tdc_ut_cm3_done 에 1 이 대입되는 지점에 중단점을 걸고 tdc_ut_cm3_result 를 조회한다.</t>
         </is>
       </c>
       <c r="I240" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 결과 배열에서 값 -999 는 구분자다. 그 다음 값이 유닛 번호다.
+- 시험은 전역 상태를 바꾼다. 시험 후에는 장치를 재기동한다.
+- 시험 코드는 평시 빌드에서 제외되므로 정상 동작에 영향을 주지 않는다.</t>
         </is>
       </c>
       <c r="J240" s="9" t="inlineStr">
         <is>
-          <t>- 빌드 설정에 TDC_UNIT_TEST 를 정의하고 시험 파일을 빌드에 넣는다.
-- 디버거에서 시험 진입점을 호출한다.
-- done 변수에 중단점을 걸고 결과 배열을 조회한다.
-- 실기 시험 절차서의 기댓값과 대조한다.</t>
+          <t>- 하네스가 원 함수를 한 번 호출한다.
+- 구분자 -999 와 유닛 번호 111 다음에 결과 1 개가 이어진다.
+- 그 값이 소스의 DAC_offset_uA 정의값과 같은지 확인한다.</t>
         </is>
       </c>
       <c r="K240" s="9" t="inlineStr">
         <is>
           <t>- 출력단 보정 값 읽기 구현
-- 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
-  없음 -&gt; DAC_offset_uA 정의값과 같아야 한다</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
+[산출 근거] 상수 DAC_offset_uA 를 그대로 반환한다.
+[판정] 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
+1) 입력 : 인자 없음
+   예상 출력 : 소스의 DAC_offset_uA 정의값과 같아야 한다</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="200" customHeight="1">
       <c r="B241" s="8" t="inlineStr"/>
       <c r="C241" s="8" t="inlineStr"/>
       <c r="D241" s="9" t="inlineStr">
@@ -10516,35 +10827,46 @@
       </c>
       <c r="H241" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 빌드 설정에 TDC_UNIT_TEST 를 정의한다.
+- src/2__cm3/Cortex-M3-src/test/tdc_unit_test_cm3.c 를 빌드에 넣는다.
+- 기존 소스는 수정하지 않는다. 매크로가 없으면 이 파일은 빈 번역 단위가 된다.
+- 디버거에서 tdc_ut_cm3_run_all() 을 호출한다.
+- tdc_ut_cm3_done 에 1 이 대입되는 지점에 중단점을 걸고 tdc_ut_cm3_result 를 조회한다.</t>
         </is>
       </c>
       <c r="I241" s="9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>- 결과 배열에서 값 -999 는 구분자다. 그 다음 값이 유닛 번호다.
+- 시험은 전역 상태를 바꾼다. 시험 후에는 장치를 재기동한다.
+- 시험 코드는 평시 빌드에서 제외되므로 정상 동작에 영향을 주지 않는다.</t>
         </is>
       </c>
       <c r="J241" s="9" t="inlineStr">
         <is>
-          <t>- 빌드 설정에 TDC_UNIT_TEST 를 정의하고 시험 파일을 빌드에 넣는다.
-- 디버거에서 시험 진입점을 호출한다.
-- done 변수에 중단점을 걸고 결과 배열을 조회한다.
-- 실기 시험 절차서의 기댓값과 대조한다.</t>
+          <t>- 하네스가 아래 5 가지 입력을 차례로 넣어 원 함수를 호출한다.
+- 구분자 -999 와 유닛 번호 112 다음에 결과 5 개가 이어진다.
+- 결과를 16 진수로 보아 아래 예상 출력과 대조한다.</t>
         </is>
       </c>
       <c r="K241" s="9" t="inlineStr">
         <is>
           <t>- 비트 구간 소거 구현
-- 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
-  Data=0xFFFF, bitPosition=0, bitLength=4 -&gt; 0xFFF0
-  Data=0xFFFF, bitPosition=4, bitLength=4 -&gt; 0xFF0F
-  Data=0x00FF, bitPosition=2, bitLength=3 -&gt; 0x00E3
-  Data=0x1234, bitPosition=8, bitLength=8 -&gt; 0x0034
-  Data=0xAAAA, bitPosition=1, bitLength=1 -&gt; 0xAAA8</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
+[산출 근거] 순수 비트 연산이라 입력에 대한 출력이 결정된다.
+[판정] 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
+1) 입력 : Data=0xFFFF, bitPosition=0, bitLength=4
+   예상 출력 : 0xFFF0
+2) 입력 : Data=0xFFFF, bitPosition=4, bitLength=4
+   예상 출력 : 0xFF0F
+3) 입력 : Data=0x00FF, bitPosition=2, bitLength=3
+   예상 출력 : 0x00E3
+4) 입력 : Data=0x1234, bitPosition=8, bitLength=8
+   예상 출력 : 0x0034
+5) 입력 : Data=0xAAAA, bitPosition=1, bitLength=1
+   예상 출력 : 0xAAA8</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="37.5" customHeight="1">
       <c r="B242" s="8" t="inlineStr"/>
       <c r="C242" s="8" t="inlineStr">
         <is>
@@ -10594,7 +10916,7 @@
         </is>
       </c>
     </row>
-    <row r="243">
+    <row r="243" ht="12.5" customHeight="1">
       <c r="B243" s="8" t="inlineStr"/>
       <c r="C243" s="8" t="inlineStr"/>
       <c r="D243" s="9" t="inlineStr">
@@ -10638,7 +10960,7 @@
         </is>
       </c>
     </row>
-    <row r="244">
+    <row r="244" ht="12.5" customHeight="1">
       <c r="B244" s="8" t="inlineStr"/>
       <c r="C244" s="8" t="inlineStr"/>
       <c r="D244" s="9" t="inlineStr">
@@ -10682,7 +11004,7 @@
         </is>
       </c>
     </row>
-    <row r="245">
+    <row r="245" ht="12.5" customHeight="1">
       <c r="B245" s="8" t="inlineStr"/>
       <c r="C245" s="8" t="inlineStr"/>
       <c r="D245" s="9" t="inlineStr">
@@ -10726,7 +11048,7 @@
         </is>
       </c>
     </row>
-    <row r="246">
+    <row r="246" ht="12.5" customHeight="1">
       <c r="B246" s="8" t="inlineStr"/>
       <c r="C246" s="8" t="inlineStr"/>
       <c r="D246" s="9" t="inlineStr">
@@ -10770,7 +11092,7 @@
         </is>
       </c>
     </row>
-    <row r="247">
+    <row r="247" ht="12.5" customHeight="1">
       <c r="B247" s="8" t="inlineStr"/>
       <c r="C247" s="8" t="inlineStr"/>
       <c r="D247" s="9" t="inlineStr">
@@ -10814,7 +11136,7 @@
         </is>
       </c>
     </row>
-    <row r="248">
+    <row r="248" ht="12.5" customHeight="1">
       <c r="B248" s="8" t="inlineStr"/>
       <c r="C248" s="8" t="inlineStr"/>
       <c r="D248" s="9" t="inlineStr">
@@ -10858,7 +11180,7 @@
         </is>
       </c>
     </row>
-    <row r="249">
+    <row r="249" ht="12.5" customHeight="1">
       <c r="B249" s="8" t="inlineStr"/>
       <c r="C249" s="8" t="inlineStr"/>
       <c r="D249" s="9" t="inlineStr">
@@ -10902,7 +11224,7 @@
         </is>
       </c>
     </row>
-    <row r="250">
+    <row r="250" ht="12.5" customHeight="1">
       <c r="B250" s="8" t="inlineStr"/>
       <c r="C250" s="8" t="inlineStr"/>
       <c r="D250" s="9" t="inlineStr">
@@ -10946,7 +11268,7 @@
         </is>
       </c>
     </row>
-    <row r="251">
+    <row r="251" ht="12.5" customHeight="1">
       <c r="B251" s="8" t="inlineStr"/>
       <c r="C251" s="8" t="inlineStr"/>
       <c r="D251" s="9" t="inlineStr">
@@ -10990,7 +11312,7 @@
         </is>
       </c>
     </row>
-    <row r="252">
+    <row r="252" ht="12.5" customHeight="1">
       <c r="B252" s="8" t="inlineStr"/>
       <c r="C252" s="8" t="inlineStr"/>
       <c r="D252" s="9" t="inlineStr">
@@ -11034,7 +11356,7 @@
         </is>
       </c>
     </row>
-    <row r="253">
+    <row r="253" ht="12.5" customHeight="1">
       <c r="B253" s="8" t="inlineStr"/>
       <c r="C253" s="8" t="inlineStr"/>
       <c r="D253" s="9" t="inlineStr">
@@ -11078,7 +11400,7 @@
         </is>
       </c>
     </row>
-    <row r="254">
+    <row r="254" ht="12.5" customHeight="1">
       <c r="B254" s="8" t="inlineStr"/>
       <c r="C254" s="8" t="inlineStr"/>
       <c r="D254" s="9" t="inlineStr">
@@ -11122,7 +11444,7 @@
         </is>
       </c>
     </row>
-    <row r="255">
+    <row r="255" ht="12.5" customHeight="1">
       <c r="B255" s="8" t="inlineStr"/>
       <c r="C255" s="8" t="inlineStr"/>
       <c r="D255" s="9" t="inlineStr">
@@ -11166,7 +11488,7 @@
         </is>
       </c>
     </row>
-    <row r="256">
+    <row r="256" ht="12.5" customHeight="1">
       <c r="B256" s="8" t="inlineStr"/>
       <c r="C256" s="8" t="inlineStr"/>
       <c r="D256" s="9" t="inlineStr">
@@ -11210,7 +11532,7 @@
         </is>
       </c>
     </row>
-    <row r="257">
+    <row r="257" ht="12.5" customHeight="1">
       <c r="B257" s="8" t="inlineStr"/>
       <c r="C257" s="8" t="inlineStr"/>
       <c r="D257" s="9" t="inlineStr">
@@ -11254,7 +11576,7 @@
         </is>
       </c>
     </row>
-    <row r="258">
+    <row r="258" ht="12.5" customHeight="1">
       <c r="B258" s="8" t="inlineStr"/>
       <c r="C258" s="8" t="inlineStr"/>
       <c r="D258" s="9" t="inlineStr">
@@ -11298,7 +11620,7 @@
         </is>
       </c>
     </row>
-    <row r="259">
+    <row r="259" ht="12.5" customHeight="1">
       <c r="B259" s="8" t="inlineStr"/>
       <c r="C259" s="8" t="inlineStr"/>
       <c r="D259" s="9" t="inlineStr">
@@ -11342,7 +11664,7 @@
         </is>
       </c>
     </row>
-    <row r="260">
+    <row r="260" ht="12.5" customHeight="1">
       <c r="B260" s="8" t="inlineStr"/>
       <c r="C260" s="8" t="inlineStr"/>
       <c r="D260" s="9" t="inlineStr">
@@ -11386,7 +11708,7 @@
         </is>
       </c>
     </row>
-    <row r="261">
+    <row r="261" ht="12.5" customHeight="1">
       <c r="B261" s="8" t="inlineStr"/>
       <c r="C261" s="8" t="inlineStr"/>
       <c r="D261" s="9" t="inlineStr">
@@ -11430,7 +11752,7 @@
         </is>
       </c>
     </row>
-    <row r="262">
+    <row r="262" ht="12.5" customHeight="1">
       <c r="B262" s="8" t="inlineStr"/>
       <c r="C262" s="8" t="inlineStr"/>
       <c r="D262" s="9" t="inlineStr">
@@ -11474,7 +11796,7 @@
         </is>
       </c>
     </row>
-    <row r="263">
+    <row r="263" ht="12.5" customHeight="1">
       <c r="B263" s="8" t="inlineStr"/>
       <c r="C263" s="8" t="inlineStr"/>
       <c r="D263" s="9" t="inlineStr">
@@ -11518,7 +11840,7 @@
         </is>
       </c>
     </row>
-    <row r="264">
+    <row r="264" ht="12.5" customHeight="1">
       <c r="B264" s="8" t="inlineStr"/>
       <c r="C264" s="8" t="inlineStr"/>
       <c r="D264" s="9" t="inlineStr">
@@ -11562,7 +11884,7 @@
         </is>
       </c>
     </row>
-    <row r="265">
+    <row r="265" ht="12.5" customHeight="1">
       <c r="B265" s="8" t="inlineStr"/>
       <c r="C265" s="8" t="inlineStr"/>
       <c r="D265" s="9" t="inlineStr">
@@ -11606,7 +11928,7 @@
         </is>
       </c>
     </row>
-    <row r="266">
+    <row r="266" ht="12.5" customHeight="1">
       <c r="B266" s="8" t="inlineStr"/>
       <c r="C266" s="8" t="inlineStr"/>
       <c r="D266" s="9" t="inlineStr">
@@ -11650,7 +11972,7 @@
         </is>
       </c>
     </row>
-    <row r="267">
+    <row r="267" ht="12.5" customHeight="1">
       <c r="B267" s="8" t="inlineStr"/>
       <c r="C267" s="8" t="inlineStr"/>
       <c r="D267" s="9" t="inlineStr">
@@ -11694,7 +12016,7 @@
         </is>
       </c>
     </row>
-    <row r="268">
+    <row r="268" ht="12.5" customHeight="1">
       <c r="B268" s="8" t="inlineStr"/>
       <c r="C268" s="8" t="inlineStr"/>
       <c r="D268" s="9" t="inlineStr">
@@ -11738,7 +12060,7 @@
         </is>
       </c>
     </row>
-    <row r="269">
+    <row r="269" ht="12.5" customHeight="1">
       <c r="B269" s="8" t="inlineStr"/>
       <c r="C269" s="8" t="inlineStr"/>
       <c r="D269" s="9" t="inlineStr">
@@ -11782,7 +12104,7 @@
         </is>
       </c>
     </row>
-    <row r="270">
+    <row r="270" ht="12.5" customHeight="1">
       <c r="B270" s="8" t="inlineStr"/>
       <c r="C270" s="8" t="inlineStr"/>
       <c r="D270" s="9" t="inlineStr">
@@ -11826,7 +12148,7 @@
         </is>
       </c>
     </row>
-    <row r="271">
+    <row r="271" ht="12.5" customHeight="1">
       <c r="B271" s="8" t="inlineStr"/>
       <c r="C271" s="8" t="inlineStr"/>
       <c r="D271" s="9" t="inlineStr">
@@ -11870,7 +12192,7 @@
         </is>
       </c>
     </row>
-    <row r="272">
+    <row r="272" ht="12.5" customHeight="1">
       <c r="B272" s="8" t="inlineStr"/>
       <c r="C272" s="8" t="inlineStr"/>
       <c r="D272" s="9" t="inlineStr">
@@ -11914,7 +12236,7 @@
         </is>
       </c>
     </row>
-    <row r="273">
+    <row r="273" ht="12.5" customHeight="1">
       <c r="B273" s="8" t="inlineStr"/>
       <c r="C273" s="8" t="inlineStr"/>
       <c r="D273" s="9" t="inlineStr">
@@ -11958,7 +12280,7 @@
         </is>
       </c>
     </row>
-    <row r="274">
+    <row r="274" ht="12.5" customHeight="1">
       <c r="B274" s="8" t="inlineStr"/>
       <c r="C274" s="8" t="inlineStr"/>
       <c r="D274" s="9" t="inlineStr">
@@ -12002,7 +12324,7 @@
         </is>
       </c>
     </row>
-    <row r="275">
+    <row r="275" ht="12.5" customHeight="1">
       <c r="B275" s="8" t="inlineStr"/>
       <c r="C275" s="8" t="inlineStr"/>
       <c r="D275" s="9" t="inlineStr">
@@ -12046,7 +12368,7 @@
         </is>
       </c>
     </row>
-    <row r="276">
+    <row r="276" ht="12.5" customHeight="1">
       <c r="B276" s="8" t="inlineStr"/>
       <c r="C276" s="8" t="inlineStr"/>
       <c r="D276" s="9" t="inlineStr">
@@ -12090,7 +12412,7 @@
         </is>
       </c>
     </row>
-    <row r="277">
+    <row r="277" ht="12.5" customHeight="1">
       <c r="B277" s="8" t="inlineStr"/>
       <c r="C277" s="8" t="inlineStr"/>
       <c r="D277" s="9" t="inlineStr">
@@ -12134,7 +12456,7 @@
         </is>
       </c>
     </row>
-    <row r="278">
+    <row r="278" ht="12.5" customHeight="1">
       <c r="B278" s="8" t="inlineStr"/>
       <c r="C278" s="8" t="inlineStr"/>
       <c r="D278" s="9" t="inlineStr">
@@ -12178,7 +12500,7 @@
         </is>
       </c>
     </row>
-    <row r="279">
+    <row r="279" ht="12.5" customHeight="1">
       <c r="B279" s="8" t="inlineStr"/>
       <c r="C279" s="8" t="inlineStr"/>
       <c r="D279" s="9" t="inlineStr">
@@ -12222,7 +12544,7 @@
         </is>
       </c>
     </row>
-    <row r="280">
+    <row r="280" ht="12.5" customHeight="1">
       <c r="B280" s="8" t="inlineStr"/>
       <c r="C280" s="8" t="inlineStr"/>
       <c r="D280" s="9" t="inlineStr">
@@ -12266,7 +12588,7 @@
         </is>
       </c>
     </row>
-    <row r="281">
+    <row r="281" ht="12.5" customHeight="1">
       <c r="B281" s="8" t="inlineStr"/>
       <c r="C281" s="8" t="inlineStr"/>
       <c r="D281" s="9" t="inlineStr">
@@ -12310,7 +12632,7 @@
         </is>
       </c>
     </row>
-    <row r="282">
+    <row r="282" ht="12.5" customHeight="1">
       <c r="B282" s="8" t="inlineStr"/>
       <c r="C282" s="8" t="inlineStr"/>
       <c r="D282" s="9" t="inlineStr">
@@ -12354,7 +12676,7 @@
         </is>
       </c>
     </row>
-    <row r="283">
+    <row r="283" ht="12.5" customHeight="1">
       <c r="B283" s="8" t="inlineStr"/>
       <c r="C283" s="8" t="inlineStr"/>
       <c r="D283" s="9" t="inlineStr">
@@ -12398,7 +12720,7 @@
         </is>
       </c>
     </row>
-    <row r="284">
+    <row r="284" ht="12.5" customHeight="1">
       <c r="B284" s="8" t="inlineStr"/>
       <c r="C284" s="8" t="inlineStr"/>
       <c r="D284" s="9" t="inlineStr">
@@ -12442,7 +12764,7 @@
         </is>
       </c>
     </row>
-    <row r="285">
+    <row r="285" ht="37.5" customHeight="1">
       <c r="B285" s="8" t="inlineStr"/>
       <c r="C285" s="8" t="inlineStr">
         <is>
@@ -12492,7 +12814,7 @@
         </is>
       </c>
     </row>
-    <row r="286">
+    <row r="286" ht="12.5" customHeight="1">
       <c r="B286" s="8" t="inlineStr"/>
       <c r="C286" s="8" t="inlineStr"/>
       <c r="D286" s="9" t="inlineStr">
@@ -12536,7 +12858,7 @@
         </is>
       </c>
     </row>
-    <row r="287">
+    <row r="287" ht="12.5" customHeight="1">
       <c r="B287" s="8" t="inlineStr"/>
       <c r="C287" s="8" t="inlineStr"/>
       <c r="D287" s="9" t="inlineStr">
@@ -12580,7 +12902,7 @@
         </is>
       </c>
     </row>
-    <row r="288">
+    <row r="288" ht="12.5" customHeight="1">
       <c r="B288" s="8" t="inlineStr"/>
       <c r="C288" s="8" t="inlineStr"/>
       <c r="D288" s="9" t="inlineStr">
@@ -12624,7 +12946,7 @@
         </is>
       </c>
     </row>
-    <row r="289">
+    <row r="289" ht="12.5" customHeight="1">
       <c r="B289" s="8" t="inlineStr"/>
       <c r="C289" s="8" t="inlineStr"/>
       <c r="D289" s="9" t="inlineStr">
@@ -12668,7 +12990,7 @@
         </is>
       </c>
     </row>
-    <row r="290">
+    <row r="290" ht="12.5" customHeight="1">
       <c r="B290" s="8" t="inlineStr"/>
       <c r="C290" s="8" t="inlineStr"/>
       <c r="D290" s="9" t="inlineStr">
@@ -12712,7 +13034,7 @@
         </is>
       </c>
     </row>
-    <row r="291">
+    <row r="291" ht="12.5" customHeight="1">
       <c r="B291" s="8" t="inlineStr"/>
       <c r="C291" s="8" t="inlineStr"/>
       <c r="D291" s="9" t="inlineStr">
@@ -12756,7 +13078,7 @@
         </is>
       </c>
     </row>
-    <row r="292">
+    <row r="292" ht="12.5" customHeight="1">
       <c r="B292" s="8" t="inlineStr"/>
       <c r="C292" s="8" t="inlineStr"/>
       <c r="D292" s="9" t="inlineStr">
@@ -12800,7 +13122,7 @@
         </is>
       </c>
     </row>
-    <row r="293">
+    <row r="293" ht="12.5" customHeight="1">
       <c r="B293" s="8" t="inlineStr"/>
       <c r="C293" s="8" t="inlineStr"/>
       <c r="D293" s="9" t="inlineStr">
@@ -12844,7 +13166,7 @@
         </is>
       </c>
     </row>
-    <row r="294">
+    <row r="294" ht="12.5" customHeight="1">
       <c r="B294" s="8" t="inlineStr"/>
       <c r="C294" s="8" t="inlineStr"/>
       <c r="D294" s="9" t="inlineStr">
@@ -12888,7 +13210,7 @@
         </is>
       </c>
     </row>
-    <row r="295">
+    <row r="295" ht="12.5" customHeight="1">
       <c r="B295" s="8" t="inlineStr"/>
       <c r="C295" s="8" t="inlineStr"/>
       <c r="D295" s="9" t="inlineStr">
@@ -12932,7 +13254,7 @@
         </is>
       </c>
     </row>
-    <row r="296">
+    <row r="296" ht="12.5" customHeight="1">
       <c r="B296" s="8" t="inlineStr"/>
       <c r="C296" s="8" t="inlineStr"/>
       <c r="D296" s="9" t="inlineStr">
@@ -12976,7 +13298,7 @@
         </is>
       </c>
     </row>
-    <row r="297">
+    <row r="297" ht="12.5" customHeight="1">
       <c r="B297" s="8" t="inlineStr"/>
       <c r="C297" s="8" t="inlineStr"/>
       <c r="D297" s="9" t="inlineStr">
@@ -13020,7 +13342,7 @@
         </is>
       </c>
     </row>
-    <row r="298">
+    <row r="298" ht="12.5" customHeight="1">
       <c r="B298" s="8" t="inlineStr"/>
       <c r="C298" s="8" t="inlineStr"/>
       <c r="D298" s="9" t="inlineStr">
@@ -13064,7 +13386,7 @@
         </is>
       </c>
     </row>
-    <row r="299">
+    <row r="299" ht="12.5" customHeight="1">
       <c r="B299" s="8" t="inlineStr"/>
       <c r="C299" s="8" t="inlineStr"/>
       <c r="D299" s="9" t="inlineStr">
@@ -13108,7 +13430,7 @@
         </is>
       </c>
     </row>
-    <row r="300">
+    <row r="300" ht="12.5" customHeight="1">
       <c r="B300" s="8" t="inlineStr"/>
       <c r="C300" s="8" t="inlineStr"/>
       <c r="D300" s="9" t="inlineStr">
@@ -13152,7 +13474,7 @@
         </is>
       </c>
     </row>
-    <row r="301">
+    <row r="301" ht="12.5" customHeight="1">
       <c r="B301" s="8" t="inlineStr"/>
       <c r="C301" s="8" t="inlineStr"/>
       <c r="D301" s="9" t="inlineStr">
@@ -13196,7 +13518,7 @@
         </is>
       </c>
     </row>
-    <row r="302">
+    <row r="302" ht="12.5" customHeight="1">
       <c r="B302" s="8" t="inlineStr"/>
       <c r="C302" s="8" t="inlineStr"/>
       <c r="D302" s="9" t="inlineStr">
@@ -13240,7 +13562,7 @@
         </is>
       </c>
     </row>
-    <row r="303">
+    <row r="303" ht="37.5" customHeight="1">
       <c r="B303" s="8" t="inlineStr">
         <is>
           <t>BOOT</t>
@@ -13294,7 +13616,7 @@
         </is>
       </c>
     </row>
-    <row r="304">
+    <row r="304" ht="12.5" customHeight="1">
       <c r="B304" s="8" t="inlineStr"/>
       <c r="C304" s="8" t="inlineStr"/>
       <c r="D304" s="9" t="inlineStr">
@@ -13338,7 +13660,7 @@
         </is>
       </c>
     </row>
-    <row r="305">
+    <row r="305" ht="12.5" customHeight="1">
       <c r="B305" s="8" t="inlineStr"/>
       <c r="C305" s="8" t="inlineStr"/>
       <c r="D305" s="9" t="inlineStr">
@@ -13382,7 +13704,7 @@
         </is>
       </c>
     </row>
-    <row r="306">
+    <row r="306" ht="12.5" customHeight="1">
       <c r="B306" s="8" t="inlineStr"/>
       <c r="C306" s="8" t="inlineStr"/>
       <c r="D306" s="9" t="inlineStr">
@@ -13426,7 +13748,7 @@
         </is>
       </c>
     </row>
-    <row r="307">
+    <row r="307" ht="12.5" customHeight="1">
       <c r="B307" s="8" t="inlineStr"/>
       <c r="C307" s="8" t="inlineStr"/>
       <c r="D307" s="9" t="inlineStr">
@@ -13470,7 +13792,7 @@
         </is>
       </c>
     </row>
-    <row r="308">
+    <row r="308" ht="12.5" customHeight="1">
       <c r="B308" s="8" t="inlineStr"/>
       <c r="C308" s="8" t="inlineStr"/>
       <c r="D308" s="9" t="inlineStr">
@@ -13514,7 +13836,7 @@
         </is>
       </c>
     </row>
-    <row r="309">
+    <row r="309" ht="12.5" customHeight="1">
       <c r="B309" s="8" t="inlineStr"/>
       <c r="C309" s="8" t="inlineStr"/>
       <c r="D309" s="9" t="inlineStr">
@@ -13558,7 +13880,7 @@
         </is>
       </c>
     </row>
-    <row r="310">
+    <row r="310" ht="12.5" customHeight="1">
       <c r="B310" s="8" t="inlineStr"/>
       <c r="C310" s="8" t="inlineStr"/>
       <c r="D310" s="9" t="inlineStr">
@@ -13602,7 +13924,7 @@
         </is>
       </c>
     </row>
-    <row r="311">
+    <row r="311" ht="12.5" customHeight="1">
       <c r="B311" s="8" t="inlineStr"/>
       <c r="C311" s="8" t="inlineStr"/>
       <c r="D311" s="9" t="inlineStr">
@@ -13646,7 +13968,7 @@
         </is>
       </c>
     </row>
-    <row r="312">
+    <row r="312" ht="12.5" customHeight="1">
       <c r="B312" s="8" t="inlineStr"/>
       <c r="C312" s="8" t="inlineStr"/>
       <c r="D312" s="9" t="inlineStr">
@@ -13690,7 +14012,7 @@
         </is>
       </c>
     </row>
-    <row r="313">
+    <row r="313" ht="12.5" customHeight="1">
       <c r="B313" s="8" t="inlineStr"/>
       <c r="C313" s="8" t="inlineStr"/>
       <c r="D313" s="9" t="inlineStr">
@@ -13734,7 +14056,7 @@
         </is>
       </c>
     </row>
-    <row r="314">
+    <row r="314" ht="12.5" customHeight="1">
       <c r="B314" s="8" t="inlineStr"/>
       <c r="C314" s="8" t="inlineStr"/>
       <c r="D314" s="9" t="inlineStr">
@@ -13778,7 +14100,7 @@
         </is>
       </c>
     </row>
-    <row r="315">
+    <row r="315" ht="12.5" customHeight="1">
       <c r="B315" s="8" t="inlineStr"/>
       <c r="C315" s="8" t="inlineStr"/>
       <c r="D315" s="9" t="inlineStr">
@@ -13822,7 +14144,7 @@
         </is>
       </c>
     </row>
-    <row r="316">
+    <row r="316" ht="12.5" customHeight="1">
       <c r="B316" s="8" t="inlineStr"/>
       <c r="C316" s="8" t="inlineStr"/>
       <c r="D316" s="9" t="inlineStr">
@@ -13866,7 +14188,7 @@
         </is>
       </c>
     </row>
-    <row r="317">
+    <row r="317" ht="37.5" customHeight="1">
       <c r="B317" s="8" t="inlineStr"/>
       <c r="C317" s="8" t="inlineStr">
         <is>
@@ -13916,7 +14238,7 @@
         </is>
       </c>
     </row>
-    <row r="318">
+    <row r="318" ht="12.5" customHeight="1">
       <c r="B318" s="8" t="inlineStr"/>
       <c r="C318" s="8" t="inlineStr"/>
       <c r="D318" s="9" t="inlineStr">
@@ -13960,7 +14282,7 @@
         </is>
       </c>
     </row>
-    <row r="319">
+    <row r="319" ht="12.5" customHeight="1">
       <c r="B319" s="8" t="inlineStr"/>
       <c r="C319" s="8" t="inlineStr"/>
       <c r="D319" s="9" t="inlineStr">
@@ -14004,7 +14326,7 @@
         </is>
       </c>
     </row>
-    <row r="320">
+    <row r="320" ht="12.5" customHeight="1">
       <c r="B320" s="8" t="inlineStr"/>
       <c r="C320" s="8" t="inlineStr"/>
       <c r="D320" s="9" t="inlineStr">
@@ -14048,7 +14370,7 @@
         </is>
       </c>
     </row>
-    <row r="321">
+    <row r="321" ht="12.5" customHeight="1">
       <c r="B321" s="8" t="inlineStr"/>
       <c r="C321" s="8" t="inlineStr"/>
       <c r="D321" s="9" t="inlineStr">
@@ -14092,7 +14414,7 @@
         </is>
       </c>
     </row>
-    <row r="322">
+    <row r="322" ht="12.5" customHeight="1">
       <c r="B322" s="8" t="inlineStr"/>
       <c r="C322" s="8" t="inlineStr"/>
       <c r="D322" s="9" t="inlineStr">
@@ -14136,7 +14458,7 @@
         </is>
       </c>
     </row>
-    <row r="323">
+    <row r="323" ht="12.5" customHeight="1">
       <c r="B323" s="8" t="inlineStr"/>
       <c r="C323" s="8" t="inlineStr"/>
       <c r="D323" s="9" t="inlineStr">
@@ -14180,7 +14502,7 @@
         </is>
       </c>
     </row>
-    <row r="324">
+    <row r="324" ht="12.5" customHeight="1">
       <c r="B324" s="8" t="inlineStr"/>
       <c r="C324" s="8" t="inlineStr"/>
       <c r="D324" s="9" t="inlineStr">
@@ -14224,7 +14546,7 @@
         </is>
       </c>
     </row>
-    <row r="325">
+    <row r="325" ht="12.5" customHeight="1">
       <c r="B325" s="8" t="inlineStr"/>
       <c r="C325" s="8" t="inlineStr"/>
       <c r="D325" s="9" t="inlineStr">
@@ -14268,7 +14590,7 @@
         </is>
       </c>
     </row>
-    <row r="326">
+    <row r="326" ht="12.5" customHeight="1">
       <c r="B326" s="8" t="inlineStr"/>
       <c r="C326" s="8" t="inlineStr"/>
       <c r="D326" s="9" t="inlineStr">
@@ -14312,7 +14634,7 @@
         </is>
       </c>
     </row>
-    <row r="327">
+    <row r="327" ht="12.5" customHeight="1">
       <c r="B327" s="8" t="inlineStr"/>
       <c r="C327" s="8" t="inlineStr"/>
       <c r="D327" s="9" t="inlineStr">
@@ -14356,7 +14678,7 @@
         </is>
       </c>
     </row>
-    <row r="328">
+    <row r="328" ht="12.5" customHeight="1">
       <c r="B328" s="8" t="inlineStr"/>
       <c r="C328" s="8" t="inlineStr"/>
       <c r="D328" s="9" t="inlineStr">
@@ -14400,7 +14722,7 @@
         </is>
       </c>
     </row>
-    <row r="329">
+    <row r="329" ht="12.5" customHeight="1">
       <c r="B329" s="8" t="inlineStr"/>
       <c r="C329" s="8" t="inlineStr"/>
       <c r="D329" s="9" t="inlineStr">
@@ -14444,7 +14766,7 @@
         </is>
       </c>
     </row>
-    <row r="330">
+    <row r="330" ht="12.5" customHeight="1">
       <c r="B330" s="8" t="inlineStr"/>
       <c r="C330" s="8" t="inlineStr"/>
       <c r="D330" s="9" t="inlineStr">
@@ -14488,7 +14810,7 @@
         </is>
       </c>
     </row>
-    <row r="331">
+    <row r="331" ht="12.5" customHeight="1">
       <c r="B331" s="8" t="inlineStr"/>
       <c r="C331" s="8" t="inlineStr"/>
       <c r="D331" s="9" t="inlineStr">
@@ -14532,7 +14854,7 @@
         </is>
       </c>
     </row>
-    <row r="332">
+    <row r="332" ht="12.5" customHeight="1">
       <c r="B332" s="8" t="inlineStr"/>
       <c r="C332" s="8" t="inlineStr"/>
       <c r="D332" s="9" t="inlineStr">
@@ -14576,7 +14898,7 @@
         </is>
       </c>
     </row>
-    <row r="333">
+    <row r="333" ht="12.5" customHeight="1">
       <c r="B333" s="8" t="inlineStr"/>
       <c r="C333" s="8" t="inlineStr"/>
       <c r="D333" s="9" t="inlineStr">
@@ -14620,7 +14942,7 @@
         </is>
       </c>
     </row>
-    <row r="334">
+    <row r="334" ht="12.5" customHeight="1">
       <c r="B334" s="8" t="inlineStr"/>
       <c r="C334" s="8" t="inlineStr"/>
       <c r="D334" s="9" t="inlineStr">
@@ -14664,7 +14986,7 @@
         </is>
       </c>
     </row>
-    <row r="335">
+    <row r="335" ht="12.5" customHeight="1">
       <c r="B335" s="8" t="inlineStr"/>
       <c r="C335" s="8" t="inlineStr"/>
       <c r="D335" s="9" t="inlineStr">
@@ -14708,7 +15030,7 @@
         </is>
       </c>
     </row>
-    <row r="336">
+    <row r="336" ht="12.5" customHeight="1">
       <c r="B336" s="8" t="inlineStr"/>
       <c r="C336" s="8" t="inlineStr"/>
       <c r="D336" s="9" t="inlineStr">
@@ -14752,7 +15074,7 @@
         </is>
       </c>
     </row>
-    <row r="337">
+    <row r="337" ht="37.5" customHeight="1">
       <c r="B337" s="8" t="inlineStr"/>
       <c r="C337" s="8" t="inlineStr">
         <is>
@@ -14802,7 +15124,7 @@
         </is>
       </c>
     </row>
-    <row r="338">
+    <row r="338" ht="12.5" customHeight="1">
       <c r="B338" s="8" t="inlineStr"/>
       <c r="C338" s="8" t="inlineStr"/>
       <c r="D338" s="9" t="inlineStr">
@@ -14846,7 +15168,7 @@
         </is>
       </c>
     </row>
-    <row r="339">
+    <row r="339" ht="12.5" customHeight="1">
       <c r="B339" s="8" t="inlineStr"/>
       <c r="C339" s="8" t="inlineStr"/>
       <c r="D339" s="9" t="inlineStr">
@@ -14890,7 +15212,7 @@
         </is>
       </c>
     </row>
-    <row r="340">
+    <row r="340" ht="12.5" customHeight="1">
       <c r="B340" s="8" t="inlineStr"/>
       <c r="C340" s="8" t="inlineStr"/>
       <c r="D340" s="9" t="inlineStr">
@@ -14934,7 +15256,7 @@
         </is>
       </c>
     </row>
-    <row r="341">
+    <row r="341" ht="12.5" customHeight="1">
       <c r="B341" s="8" t="inlineStr"/>
       <c r="C341" s="8" t="inlineStr"/>
       <c r="D341" s="9" t="inlineStr">
@@ -14978,7 +15300,7 @@
         </is>
       </c>
     </row>
-    <row r="342">
+    <row r="342" ht="12.5" customHeight="1">
       <c r="B342" s="8" t="inlineStr"/>
       <c r="C342" s="8" t="inlineStr"/>
       <c r="D342" s="9" t="inlineStr">
@@ -15022,7 +15344,7 @@
         </is>
       </c>
     </row>
-    <row r="343">
+    <row r="343" ht="12.5" customHeight="1">
       <c r="B343" s="8" t="inlineStr"/>
       <c r="C343" s="8" t="inlineStr"/>
       <c r="D343" s="9" t="inlineStr">
@@ -15066,7 +15388,7 @@
         </is>
       </c>
     </row>
-    <row r="344">
+    <row r="344" ht="12.5" customHeight="1">
       <c r="B344" s="8" t="inlineStr"/>
       <c r="C344" s="8" t="inlineStr"/>
       <c r="D344" s="9" t="inlineStr">
@@ -15110,7 +15432,7 @@
         </is>
       </c>
     </row>
-    <row r="345">
+    <row r="345" ht="12.5" customHeight="1">
       <c r="B345" s="8" t="inlineStr"/>
       <c r="C345" s="8" t="inlineStr"/>
       <c r="D345" s="9" t="inlineStr">
@@ -15154,7 +15476,7 @@
         </is>
       </c>
     </row>
-    <row r="346">
+    <row r="346" ht="12.5" customHeight="1">
       <c r="B346" s="8" t="inlineStr"/>
       <c r="C346" s="8" t="inlineStr"/>
       <c r="D346" s="9" t="inlineStr">
@@ -15198,7 +15520,7 @@
         </is>
       </c>
     </row>
-    <row r="347">
+    <row r="347" ht="25" customHeight="1">
       <c r="B347" s="8" t="inlineStr"/>
       <c r="C347" s="8" t="inlineStr">
         <is>
@@ -15247,7 +15569,7 @@
         </is>
       </c>
     </row>
-    <row r="348">
+    <row r="348" ht="12.5" customHeight="1">
       <c r="B348" s="8" t="inlineStr"/>
       <c r="C348" s="8" t="inlineStr"/>
       <c r="D348" s="9" t="inlineStr">
@@ -15291,7 +15613,7 @@
         </is>
       </c>
     </row>
-    <row r="349">
+    <row r="349" ht="12.5" customHeight="1">
       <c r="B349" s="8" t="inlineStr"/>
       <c r="C349" s="8" t="inlineStr"/>
       <c r="D349" s="9" t="inlineStr">
@@ -15335,7 +15657,7 @@
         </is>
       </c>
     </row>
-    <row r="350">
+    <row r="350" ht="12.5" customHeight="1">
       <c r="B350" s="8" t="inlineStr"/>
       <c r="C350" s="8" t="inlineStr"/>
       <c r="D350" s="9" t="inlineStr">

--- a/docs/참고/인허가/사운드1/[04] SUVC-FW-SND1 소프트웨어 유닛 검증 기준서.xlsx
+++ b/docs/참고/인허가/사운드1/[04] SUVC-FW-SND1 소프트웨어 유닛 검증 기준서.xlsx
@@ -3873,7 +3873,7 @@
         </is>
       </c>
     </row>
-    <row r="94" ht="112.5" customHeight="1">
+    <row r="94" ht="200" customHeight="1">
       <c r="B94" s="8" t="inlineStr"/>
       <c r="C94" s="8" t="inlineStr">
         <is>
@@ -3905,34 +3905,42 @@
       <c r="H94" s="9" t="inlineStr">
         <is>
           <t>- 대상 유닛이 호출되는 지점에 디버깅용 중단점을 적용한다.
-- 입력 버퍼와 출력 버퍼를 함께 조회할 수 있도록 창을 준비한다.</t>
+- 입력 버퍼와 출력 버퍼를 함께 조회할 수 있도록 창을 준비한다.
+- HEAR_ADDR_AUDIO_MIX_ABS_MAX_VALUE 버퍼에 시험 값을 직접 쓴다.
+- m_audio_volume 을 0, m_prev_agc_10db_gain_Q8_16 을 0 으로 둔다.</t>
         </is>
       </c>
       <c r="I94" s="9" t="inlineStr">
         <is>
-          <t>- 이 유닛의 출력은 DSP 라이브러리 또는 HEAR 함수체인 결과에 의존한다.
-- 기댓값을 미리 낼 수 없으므로 실측값을 기록한다.
-- 고정소수점 연산 차이를 고려하여 판정한다.</t>
+          <t>- 직전 이득이 상태로 남으므로 시험마다 0 으로 되돌린다.
+- 하드웨어 log2/exp2 유닛의 마지막 자리 오차가 있을 수 있다. (고정소수점 연산 고려)</t>
         </is>
       </c>
       <c r="J94" s="9" t="inlineStr">
         <is>
-          <t>- 신호를 입력한 상태에서 이 유닛의 진입과 복귀에 중단점을 적용한다.
-- 입력 최대값 버퍼와 출력 이득을 함께 조회해 기록한다.</t>
+          <t>- 최대값 버퍼에 시험 값을 쓰고 원 함수를 호출한다.
+- 공유 메모리의 maxAudioInput 과 이득 계산 반환값을 조회해 기록한다.</t>
         </is>
       </c>
       <c r="K94" s="9" t="inlineStr">
         <is>
           <t>- 자동 이득 제어 실행 구현
-[산출 근거] 전처리 함수체인이 만든 최대값 버퍼에 의존한다. 기댓값을 미리 낼 수 없으므로 지어내지 않는다.
-[판정] 기댓값을 미리 낼 수 없다. 아래 항목의 실측값을 기록한다.
-       고정소수점 연산 차이를 고려하여 판정한다.
-1) 입력 : 시험 벡터 주입
-   예상 출력 : (실측 기록)</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="112.5" customHeight="1">
+[산출 근거] HEAR Configurable Accelerator Reference 로 체인 구성을 확인했다. vAbsolute(p.279)는 실수 벡터의 절대값, MaxElement(p.333)는 최대값이며 둘 다 정확 연산이다. 이 유닛은 그 결과 버퍼를 입력으로 받으므로 버퍼에 시험 벡터를 주입하면 출력이 결정된다. 이 유닛은 최대값을 공유 메모리에 그대로 옮긴 뒤 이득 계산과 이득 적용을 차례로 부른다.
+[판정] 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
+1) 입력 : 믹서 절대값 최대 버퍼에 1 주입 (볼륨 0, 직전 이득 0)
+   예상 출력 : 공유 메모리 maxAudioInput = 1, 산출 이득 = 580 [잡음 구간]
+2) 입력 : 믹서 절대값 최대 버퍼에 10 주입 (볼륨 0, 직전 이득 0)
+   예상 출력 : 공유 메모리 maxAudioInput = 10, 산출 이득 = 4096 [증폭 구간]
+3) 입력 : 믹서 절대값 최대 버퍼에 1000 주입 (볼륨 0, 직전 이득 0)
+   예상 출력 : 공유 메모리 maxAudioInput = 1000, 산출 이득 = 4096 [증폭 구간]
+4) 입력 : 믹서 절대값 최대 버퍼에 100000 주입 (볼륨 0, 직전 이득 0)
+   예상 출력 : 공유 메모리 maxAudioInput = 100000, 산출 이득 = 1402 [감쇠 구간]
+5) 입력 : 믹서 절대값 최대 버퍼에 8388607 주입 (볼륨 0, 직전 이득 0)
+   예상 출력 : 공유 메모리 maxAudioInput = 8388607, 산출 이득 = 454 [감쇠 구간]</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="350" customHeight="1">
       <c r="B95" s="8" t="inlineStr"/>
       <c r="C95" s="8" t="inlineStr"/>
       <c r="D95" s="9" t="inlineStr">
@@ -3958,30 +3966,51 @@
       <c r="H95" s="9" t="inlineStr">
         <is>
           <t>- 대상 유닛이 호출되는 지점에 디버깅용 중단점을 적용한다.
-- 입력 버퍼와 출력 버퍼를 함께 조회할 수 있도록 창을 준비한다.</t>
+- 입력 버퍼와 출력 버퍼를 함께 조회할 수 있도록 창을 준비한다.
+- 시험 전에 m_audio_volume 과 m_prev_agc_10db_gain_Q8_16 을 지정한 값으로 둔다.</t>
         </is>
       </c>
       <c r="I95" s="9" t="inlineStr">
         <is>
-          <t>- 이 유닛의 출력은 DSP 라이브러리 또는 HEAR 함수체인 결과에 의존한다.
-- 기댓값을 미리 낼 수 없으므로 실측값을 기록한다.
-- 고정소수점 연산 차이를 고려하여 판정한다.</t>
+          <t>- 직전 이득이 상태로 남으므로 시험마다 0 으로 되돌린다.
+- 하드웨어 log2/exp2 유닛의 마지막 자리 오차가 있을 수 있다. (고정소수점 연산 고려)
+- 입력 스케일은 frac48 재해석(2^47)을 전제로 계산했다. 첫 케이스의 구간 판정이 어긋나면 이 전제부터 확인한다.</t>
         </is>
       </c>
       <c r="J95" s="9" t="inlineStr">
         <is>
-          <t>- 중단점에서 입력값과 반환 이득을 조회해 기록한다.
-- 잡음 구간, 증폭 구간, 감쇠 구간 각각에서 한 번씩 기록한다.</t>
+          <t>- 중단점에서 agc_input 을 지정한 값으로 바꾸고 함수를 실행시킨다.
+- 반환된 선형 이득(Q12.12)과 내부 구간 판정을 조회해 기록한다.
+- 볼륨을 0, 5, 9 로 바꿔 세 번 더 수행한다.</t>
         </is>
       </c>
       <c r="K95" s="9" t="inlineStr">
         <is>
           <t>- 이득 계산 구현
-[산출 근거] 입력이 전처리 체인 출력이며 dB 변환 라이브러리를 거친다. 기댓값을 미리 낼 수 없으므로 지어내지 않는다.
-[판정] 기댓값을 미리 낼 수 없다. 아래 항목의 실측값을 기록한다.
-       고정소수점 연산 차이를 고려하여 판정한다.
-1) 입력 : 시험 벡터 주입
-   예상 출력 : (실측 기록)</t>
+[산출 근거] 입력을 5 비트 올려 frac48 로 재해석한 뒤 10*log10 을 취해 세 구간으로 나눈다. 잡음 게이트 -117.4972 dB 미만은 잡음 구간, 회전점 -94.7472 dB 초과는 감쇠 구간, 그 사이는 증폭 구간이다. 구간마다 기울기와 절편이 다르고 볼륨 10 단계로 갈린다. 이어서 시정수를 적용하고 라이브러리 정규화 이득을 빼고 되곱해 선형 Q12.12 로 낸다. 증폭 구간에서 볼륨 0 이면 절편이 0 이라 이득이 정확히 4096(선형 1.0)이 된다.
+[판정] 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
+1) 입력 : agc_input=1 (볼륨 0, 직전 이득 0)
+   예상 출력 : 580  [잡음 구간, 입력 -126.433 dB]
+2) 입력 : agc_input=10 (볼륨 0, 직전 이득 0)
+   예상 출력 : 4096  [증폭 구간, 입력 -116.433 dB]
+3) 입력 : agc_input=100 (볼륨 0, 직전 이득 0)
+   예상 출력 : 4096  [증폭 구간, 입력 -106.433 dB]
+4) 입력 : agc_input=1000 (볼륨 0, 직전 이득 0)
+   예상 출력 : 4096  [증폭 구간, 입력 -96.433 dB]
+5) 입력 : agc_input=10000 (볼륨 0, 직전 이득 0)
+   예상 출력 : 2518  [감쇠 구간, 입력 -86.433 dB]
+6) 입력 : agc_input=100000 (볼륨 0, 직전 이득 0)
+   예상 출력 : 1402  [감쇠 구간, 입력 -76.433 dB]
+7) 입력 : agc_input=1000000 (볼륨 0, 직전 이득 0)
+   예상 출력 : 780  [감쇠 구간, 입력 -66.433 dB]
+8) 입력 : agc_input=8388607 (볼륨 0, 직전 이득 0)
+   예상 출력 : 454  [감쇠 구간, 입력 -57.196 dB]
+9) 입력 : agc_input=100000, 볼륨=0, 직전 이득 0
+   예상 출력 : 1402  [감쇠 구간]
+10) 입력 : agc_input=100000, 볼륨=5, 직전 이득 0
+   예상 출력 : 1961  [감쇠 구간]
+11) 입력 : agc_input=100000, 볼륨=9, 직전 이득 0
+   예상 출력 : 2565  [감쇠 구간]</t>
         </is>
       </c>
     </row>
@@ -4050,7 +4079,7 @@
         </is>
       </c>
     </row>
-    <row r="97" ht="112.5" customHeight="1">
+    <row r="97" ht="150" customHeight="1">
       <c r="B97" s="8" t="inlineStr"/>
       <c r="C97" s="8" t="inlineStr"/>
       <c r="D97" s="9" t="inlineStr">
@@ -4076,33 +4105,38 @@
       <c r="H97" s="9" t="inlineStr">
         <is>
           <t>- 대상 유닛이 호출되는 지점에 디버깅용 중단점을 적용한다.
-- 입력 버퍼와 출력 버퍼를 함께 조회할 수 있도록 창을 준비한다.</t>
+- 입력 버퍼와 출력 버퍼를 함께 조회할 수 있도록 창을 준비한다.
+- HEAR_ADDR_AUDIO_MIX 버퍼 16 칸에 시험 벡터를 직접 쓴다.</t>
         </is>
       </c>
       <c r="I97" s="9" t="inlineStr">
         <is>
-          <t>- 이 유닛의 출력은 DSP 라이브러리 또는 HEAR 함수체인 결과에 의존한다.
-- 기댓값을 미리 낼 수 없으므로 실측값을 기록한다.
-- 고정소수점 연산 차이를 고려하여 판정한다.</t>
+          <t>- 24 비트 최대 8388607, 최소 -8388608 에서 잘린다. 이득 2.0 시험이 그 경계를 지난다.
+- 출력은 m_agc_output_buffer 16 칸이다.</t>
         </is>
       </c>
       <c r="J97" s="9" t="inlineStr">
         <is>
-          <t>- 적용 전후의 믹서 출력 버퍼 16 표본을 조회해 기록한다.</t>
+          <t>- 믹서 버퍼에 시험 벡터를 쓰고 이득을 인자로 넣어 호출한다.
+- m_agc_output_buffer 16 칸을 조회해 기록한다.
+- 이득 4096, 2048, 8192 로 세 번 수행한다.</t>
         </is>
       </c>
       <c r="K97" s="9" t="inlineStr">
         <is>
           <t>- 이득 적용 구현
-[산출 근거] 믹서 출력 버퍼 전체에 적용된다. 기댓값을 미리 낼 수 없으므로 지어내지 않는다.
-[판정] 기댓값을 미리 낼 수 없다. 아래 항목의 실측값을 기록한다.
-       고정소수점 연산 차이를 고려하여 판정한다.
-1) 입력 : 시험 벡터 주입
-   예상 출력 : (실측 기록)</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="112.5" customHeight="1">
+[산출 근거] 믹서 버퍼 16 표본 각각에 선형 이득(Q12.12)을 곱하고 12 비트 내린 뒤 24 비트로 포화시켜 AGC 출력 버퍼에 넣는다. 정수 연산이라 그대로 재현된다. 이득 4096 은 선형 1.0 이므로 포화가 없는 한 입력이 그대로 나와야 한다.
+[판정] 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
+1) 입력 : 믹서 버퍼 1000 -1000 4000000 -4000000 8388607 -8388608 ..., 이득 4096 (선형 1.00)
+   예상 출력 : 1000 -1000 4000000 -4000000 8388607 -8388608 0 1 -1 100 -100 32768 -32768 500000 -500000 12345
+2) 입력 : 믹서 버퍼 1000 -1000 4000000 -4000000 8388607 -8388608 ..., 이득 2048 (선형 0.50)
+   예상 출력 : 500 -500 2000000 -2000000 4194303 -4194304 0 0 -1 50 -50 16384 -16384 250000 -250000 6172
+3) 입력 : 믹서 버퍼 1000 -1000 4000000 -4000000 8388607 -8388608 ..., 이득 8192 (선형 2.00)
+   예상 출력 : 2000 -2000 8000000 -8000000 8388607 -8388608 0 2 -2 200 -200 65536 -65536 1000000 -1000000 24690</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="100" customHeight="1">
       <c r="B98" s="8" t="inlineStr"/>
       <c r="C98" s="8" t="inlineStr"/>
       <c r="D98" s="9" t="inlineStr">
@@ -4128,33 +4162,33 @@
       <c r="H98" s="9" t="inlineStr">
         <is>
           <t>- 대상 유닛이 호출되는 지점에 디버깅용 중단점을 적용한다.
-- 입력 버퍼와 출력 버퍼를 함께 조회할 수 있도록 창을 준비한다.</t>
+- 입력 버퍼와 출력 버퍼를 함께 조회할 수 있도록 창을 준비한다.
+- m_agc_output_buffer 16 칸에 시험 벡터를 직접 쓴다.</t>
         </is>
       </c>
       <c r="I98" s="9" t="inlineStr">
         <is>
-          <t>- 이 유닛의 출력은 DSP 라이브러리 또는 HEAR 함수체인 결과에 의존한다.
-- 기댓값을 미리 낼 수 없으므로 실측값을 기록한다.
-- 고정소수점 연산 차이를 고려하여 판정한다.</t>
+          <t>- FIFO 에 들어간 순서를 확인해야 하므로 FIFO 를 비운 상태에서 시작한다.</t>
         </is>
       </c>
       <c r="J98" s="9" t="inlineStr">
         <is>
-          <t>- 호출 전후의 주파수 분석 입력 버퍼를 조회해 자리 이동이 일어나는지 기록한다.</t>
+          <t>- AGC 출력 버퍼에 1 부터 16 을 차례로 쓴다.
+- 원 함수를 호출한다.
+- FIFO 에 들어간 순서를 조회해 기록한다.</t>
         </is>
       </c>
       <c r="K98" s="9" t="inlineStr">
         <is>
           <t>- 주파수 분석 입력 갱신 구현
-[산출 근거] HEAR 함수체인 출력 버퍼에 의존한다. 기댓값을 미리 낼 수 없으므로 지어내지 않는다.
-[판정] 기댓값을 미리 낼 수 없다. 아래 항목의 실측값을 기록한다.
-       고정소수점 연산 차이를 고려하여 판정한다.
-1) 입력 : 시험 벡터 주입
-   예상 출력 : (실측 기록)</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="112.5" customHeight="1">
+[산출 근거] AGC 출력 버퍼를 «역순» 으로 FIFO 에 밀어넣는다. 버퍼 끝에서 시작해 앞으로 오며 하나씩 쓴다. 순서가 뒤집히는 것이 이 유닛의 핵심이다.
+[판정] 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
+1) 입력 : AGC 출력 버퍼 = 1 2 3 4 5 6 7 8 9 10 11 12 13 14 15 16
+   예상 출력 : FIFO 기록 순서 = 16 15 14 13 12 11 10 9 8 7 6 5 4 3 2 1  (역순)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="125" customHeight="1">
       <c r="B99" s="8" t="inlineStr"/>
       <c r="C99" s="8" t="inlineStr"/>
       <c r="D99" s="9" t="inlineStr">
@@ -4180,29 +4214,32 @@
       <c r="H99" s="9" t="inlineStr">
         <is>
           <t>- 대상 유닛이 호출되는 지점에 디버깅용 중단점을 적용한다.
-- 입력 버퍼와 출력 버퍼를 함께 조회할 수 있도록 창을 준비한다.</t>
+- 입력 버퍼와 출력 버퍼를 함께 조회할 수 있도록 창을 준비한다.
+- HEAR_ADDR_VMAG_OUTPUT 버퍼 256 칸과 g_pass_bin_index 에 시험 벡터를 직접 쓴다.</t>
         </is>
       </c>
       <c r="I99" s="9" t="inlineStr">
         <is>
-          <t>- 이 유닛의 출력은 DSP 라이브러리 또는 HEAR 함수체인 결과에 의존한다.
-- 기댓값을 미리 낼 수 없으므로 실측값을 기록한다.
-- 고정소수점 연산 차이를 고려하여 판정한다.</t>
+          <t>- vMag 자체는 제곱근을 테이블로 근사하지만(HEAR Reference p.243), 이 유닛은 그 «출력» 을 입력으로 받으므로 값을 주입하면 결정적이다.
+- 대역 색인이 음수인 자리는 건너뛴다.</t>
         </is>
       </c>
       <c r="J99" s="9" t="inlineStr">
         <is>
-          <t>- 변환 체인 출력과 산출된 대역 대표값을 함께 조회해 기록한다.</t>
+          <t>- vMag 출력 버퍼 256 칸을 0 으로 채운 뒤 아래 자리에만 값을 넣는다.
+- 통과 대역 색인을 8 칸마다 한 대역씩(색인 = i / 8) 채운다.
+- 원 함수를 호출하고 g_freq_rep_values 와 g_freq_rep_values_scaled 를 조회한다.</t>
         </is>
       </c>
       <c r="K99" s="9" t="inlineStr">
         <is>
           <t>- 분석 대역 대표값 산출 구현
-[산출 근거] 주파수 변환 체인(vMag) 출력에 의존한다. 기댓값을 미리 낼 수 없으므로 지어내지 않는다.
-[판정] 기댓값을 미리 낼 수 없다. 아래 항목의 실측값을 기록한다.
-       고정소수점 연산 차이를 고려하여 판정한다.
-1) 입력 : 시험 벡터 주입
-   예상 출력 : (실측 기록)</t>
+[산출 근거] HEAR Configurable Accelerator Reference 로 체인 구성을 확인했다. 이 유닛은 그 결과 버퍼를 입력으로 받으므로 버퍼에 시험 벡터를 주입하면 출력이 결정된다. 대역 색인이 0 이상인 자리만 보고 그 대역의 최대 크기를 남긴 뒤 4 비트 내려 축소본을 만든다. 대표값 배열을 먼저 0 으로 지우므로 이전 값이 남지 않는다.
+[판정] 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
+1) 입력 : vMag[3]=5000, vMag[10]=8000, vMag[11]=3000, vMag[20]=12000, vMag[250]=700, 나머지 0. 대역 색인 = i / 8
+   예상 출력 : 대표값이 0 이 아닌 대역: 대역0=5000(축소 312), 대역1=8000(축소 500), 대역2=12000(축소 750), 대역31=700(축소 43)
+2) 입력 : 같은 입력에서 대역 1 확인 (vMag 색인 8~15 구간)
+   예상 출력 : 8000 이 남는다. 같은 대역의 3000 은 최대값이 아니라 버려진다</t>
         </is>
       </c>
     </row>
@@ -4512,7 +4549,7 @@
         </is>
       </c>
     </row>
-    <row r="106" ht="237.5" customHeight="1">
+    <row r="106" ht="225" customHeight="1">
       <c r="B106" s="8" t="inlineStr"/>
       <c r="C106" s="8" t="inlineStr"/>
       <c r="D106" s="9" t="inlineStr">
@@ -4546,36 +4583,36 @@
       </c>
       <c r="I106" s="9" t="inlineStr">
         <is>
-          <t>- 이 유닛의 출력은 DSP 라이브러리 또는 HEAR 함수체인 결과에 의존한다.
-- 기댓값을 미리 낼 수 없으므로 실측값을 기록한다.
-- 고정소수점 연산 차이를 고려하여 판정한다.</t>
+          <t>- 결과 배열에서 값 -999 는 구분자다. 그 다음 값이 유닛 번호다.
+- 시험은 전역 상태를 바꾼다. 시험 후에는 장치를 재기동한다.
+- 시험 코드는 평시 빌드에서 제외되므로 정상 동작에 영향을 주지 않는다.
+- 하드웨어 log2/exp2 유닛의 마지막 자리 오차가 있을 수 있다. (고정소수점 연산 고려)
+- to_lfix(int) 의 스케일을 frac48 재해석(2^47)로 보고 계산했다. x=1 결과가 크게 어긋나면 이 전제부터 확인한다.</t>
         </is>
       </c>
       <c r="J106" s="9" t="inlineStr">
         <is>
           <t>- 하네스가 입력 0, 1, 100, 1000, 10000, 100000 을 차례로 넣어 호출한다.
-- 구분자 -999 와 유닛 번호 81 다음에 «입력, 출력» 짝으로 12 개가 이어진다.
-- 각 짝의 출력을 그대로 기록한다.</t>
+- 구분자 -999 와 유닛 번호 81 다음에 «입력, 출력» 짝으로 12 개가 이어진다.</t>
         </is>
       </c>
       <c r="K106" s="9" t="inlineStr">
         <is>
           <t>- 거듭제곱 계산 구현
-[산출 근거] cfx_pwr_to_dB_asm 과 cfx_dB_to_pwr_asm 어셈블리 라이브러리를 거친다. 기댓값을 미리 낼 수 없으므로 지어내지 않는다.
-[판정] 기댓값을 미리 낼 수 없다. 아래 항목의 실측값을 기록한다.
-       고정소수점 연산 차이를 고려하여 판정한다.
+[산출 근거] dB 도메인에서 x^p 를 구한다. p = 0.15 (g_coeff_p_Q1_23 = 1258291). 입력을 5 비트 올려 10*log10 을 취하고, p 를 곱한 뒤 10^(dB/10) 로 되돌리고, 정규화 인자 5163793 을 곱해 Q8.16 으로 낸다. dB 변환 수식이 SDK 헤더에 명세되어 있어 재현된다.
+[판정] 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
 1) 입력 : x = 0
-   예상 출력 : 0  (x &lt; 1 이면 0 을 반환해야 한다. 이 항만 확인 가능)
+   예상 출력 : 0  (x &lt; 1 이면 0 을 반환한다)
 2) 입력 : x = 1
-   예상 출력 : (실측 기록)
+   예상 출력 : 65535  (실수 1.0000)
 3) 입력 : x = 100
-   예상 출력 : (실측 기록)
+   예상 출력 : 130761  (실수 1.9953)
 4) 입력 : x = 1000
-   예상 출력 : (실측 기록)
+   예상 출력 : 184705  (실수 2.8184)
 5) 입력 : x = 10000
-   예상 출력 : (실측 기록)
+   예상 출력 : 260903  (실수 3.9811)
 6) 입력 : x = 100000
-   예상 출력 : (실측 기록)</t>
+   예상 출력 : 368535  (실수 5.6234)</t>
         </is>
       </c>
     </row>

--- a/docs/참고/인허가/사운드1/[04] SUVC-FW-SND1 소프트웨어 유닛 검증 기준서.xlsx
+++ b/docs/참고/인허가/사운드1/[04] SUVC-FW-SND1 소프트웨어 유닛 검증 기준서.xlsx
@@ -4243,7 +4243,7 @@
         </is>
       </c>
     </row>
-    <row r="100" ht="112.5" customHeight="1">
+    <row r="100" ht="125" customHeight="1">
       <c r="B100" s="8" t="inlineStr"/>
       <c r="C100" s="8" t="inlineStr"/>
       <c r="D100" s="9" t="inlineStr">
@@ -4269,35 +4269,37 @@
       <c r="H100" s="9" t="inlineStr">
         <is>
           <t>- 대상 유닛이 호출되는 지점에 디버깅용 중단점을 적용한다.
-- 입력 버퍼와 출력 버퍼를 함께 조회할 수 있도록 창을 준비한다.</t>
+- 입력 버퍼와 출력 버퍼를 함께 조회할 수 있도록 창을 준비한다.
+- 저장 영역의 대역 수와 색인 배열에 시험 값을 쓴다.
+- addr_MapProgramData_FrequencyAnalysisBandNumbers 를 지정한 값으로 둔다.</t>
         </is>
       </c>
       <c r="I100" s="9" t="inlineStr">
         <is>
-          <t>- 이 유닛의 출력은 DSP 라이브러리 또는 HEAR 함수체인 결과에 의존한다.
-- 기댓값을 미리 낼 수 없으므로 실측값을 기록한다.
-- 고정소수점 연산 차이를 고려하여 판정한다.</t>
+          <t>- 복사는 256 칸(절반 FFT 크기)이다.</t>
         </is>
       </c>
       <c r="J100" s="9" t="inlineStr">
         <is>
-          <t>- 맵의 대역 수와 저장 영역의 대역 수가 같은지 먼저 확인한다.
-- 호출 후 g_pass_bin_index 배열을 조회해 저장 영역의 값과 같은지 기록한다.
-- 대역 수가 다를 때는 배열이 바뀌지 않아야 한다. 그 경우도 기록한다.</t>
+          <t>- 저장 영역 대역 수를 16, 색인 배열을 0 부터 255 로 채운다.
+- g_pass_bin_index 를 -1 로 미리 채운다.
+- 맵 대역 수를 16 으로 두고 호출해 조회한다. (일치 경우)
+- 맵 대역 수를 22 로 바꿔 다시 호출해 조회한다. (불일치 경우)</t>
         </is>
       </c>
       <c r="K100" s="9" t="inlineStr">
         <is>
           <t>- 통과 대역 인덱스 읽기 구현
-[산출 근거] 파일 시스템 영역에 저장된 통과 대역 색인을 읽어 온다. 저장된 내용에 의존한다. 기댓값을 미리 낼 수 없으므로 지어내지 않는다.
-[판정] 기댓값을 미리 낼 수 없다. 아래 항목의 실측값을 기록한다.
-       고정소수점 연산 차이를 고려하여 판정한다.
-1) 입력 : 시험 벡터 주입
-   예상 출력 : (실측 기록)</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="112.5" customHeight="1">
+[산출 근거] 맵의 대역 수와 저장 영역의 대역 수가 «같을 때만» 통과 대역 색인 256 칸을 복사한다. 다르면 아무 것도 하지 않고 기존 배열이 그대로 남는다. 이 조건 분기가 판정의 핵심이다.
+[판정] 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
+1) 입력 : 맵 대역 수 16 = 저장 영역 대역 수 16 (일치)
+   예상 출력 : g_pass_bin_index[0..255] = 0 1 2 ... 255 (저장 값이 복사된다)
+2) 입력 : 맵 대역 수 22, 저장 영역 대역 수 16 (불일치)
+   예상 출력 : g_pass_bin_index 가 바뀌지 않는다. 미리 채운 -1 이 그대로 남는다</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="125" customHeight="1">
       <c r="B101" s="8" t="inlineStr"/>
       <c r="C101" s="8" t="inlineStr"/>
       <c r="D101" s="9" t="inlineStr">
@@ -4323,33 +4325,40 @@
       <c r="H101" s="9" t="inlineStr">
         <is>
           <t>- 대상 유닛이 호출되는 지점에 디버깅용 중단점을 적용한다.
-- 입력 버퍼와 출력 버퍼를 함께 조회할 수 있도록 창을 준비한다.</t>
+- 입력 버퍼와 출력 버퍼를 함께 조회할 수 있도록 창을 준비한다.
+- 공유 메모리 calculatedStimulPara_byCM3 의 T_level_255 와 C_level_255 에 시험 값을 직접 쓴다.
+시험 맵 (앞 4 전극만 다르게 두고 나머지는 같은 값)
+  T 레벨  : 10, 20, 30, 40, 나머지 10
+  C 레벨  : 100, 150, 200, 250, 나머지 100
+  xMin    : 100, 200, 300, 400, 나머지 100
+  xMax    : 10000, 20000, 30000, 40000, 나머지 10000</t>
         </is>
       </c>
       <c r="I101" s="9" t="inlineStr">
         <is>
-          <t>- 이 유닛의 출력은 DSP 라이브러리 또는 HEAR 함수체인 결과에 의존한다.
-- 기댓값을 미리 낼 수 없으므로 실측값을 기록한다.
-- 고정소수점 연산 차이를 고려하여 판정한다.</t>
+          <t>- 복사만 하므로 입력과 출력이 같아야 한다. 다르면 색인이나 길이가 어긋난 것이다.</t>
         </is>
       </c>
       <c r="J101" s="9" t="inlineStr">
         <is>
-          <t>- 공유 메모리의 C/T 레벨과 호출 후 CFX 쪽 배열을 함께 조회해 같은지 기록한다.</t>
+          <t>- 공유 메모리에 시험 T/C 레벨을 쓴다.
+- 원 함수를 호출한다.
+- g_mapping_stimulus_amplitude_T_level 과 _C_level 32 칸을 조회한다.</t>
         </is>
       </c>
       <c r="K101" s="9" t="inlineStr">
         <is>
           <t>- C 및 T 레벨 읽기 구현
-[산출 근거] CM3 가 공유 메모리에 올린 C 레벨과 T 레벨을 읽어 온다. CM3 계산 결과에 의존한다. 기댓값을 미리 낼 수 없으므로 지어내지 않는다.
-[판정] 기댓값을 미리 낼 수 없다. 아래 항목의 실측값을 기록한다.
-       고정소수점 연산 차이를 고려하여 판정한다.
-1) 입력 : 시험 벡터 주입
-   예상 출력 : (실측 기록)</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="112.5" customHeight="1">
+[산출 근거] 공유 메모리의 계산된 자극 파라미터에서 T 레벨과 C 레벨 32 칸씩을 CFX 쪽 배열로 그대로 복사한다. 값을 바꾸지 않는 순수 복사다.
+[판정] 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
+1) 입력 : 공유 메모리 T_level_255[0..3] = 10, 20, 30, 40
+   예상 출력 : g_mapping_stimulus_amplitude_T_level[0..3] = 10 20 30 40 (그대로)
+2) 입력 : 공유 메모리 C_level_255[0..3] = 100, 150, 200, 250
+   예상 출력 : g_mapping_stimulus_amplitude_C_level[0..3] = 100 150 200 250 (그대로)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="175" customHeight="1">
       <c r="B102" s="8" t="inlineStr"/>
       <c r="C102" s="8" t="inlineStr"/>
       <c r="D102" s="9" t="inlineStr">
@@ -4375,33 +4384,44 @@
       <c r="H102" s="9" t="inlineStr">
         <is>
           <t>- 대상 유닛이 호출되는 지점에 디버깅용 중단점을 적용한다.
-- 입력 버퍼와 출력 버퍼를 함께 조회할 수 있도록 창을 준비한다.</t>
+- 입력 버퍼와 출력 버퍼를 함께 조회할 수 있도록 창을 준비한다.
+- 먼저 C/T 레벨 읽기 유닛으로 시험 값을 채운다.
+시험 맵 (앞 4 전극만 다르게 두고 나머지는 같은 값)
+  T 레벨  : 10, 20, 30, 40, 나머지 10
+  C 레벨  : 100, 150, 200, 250, 나머지 100
+  xMin    : 100, 200, 300, 400, 나머지 100
+  xMax    : 10000, 20000, 30000, 40000, 나머지 10000</t>
         </is>
       </c>
       <c r="I102" s="9" t="inlineStr">
         <is>
-          <t>- 이 유닛의 출력은 DSP 라이브러리 또는 HEAR 함수체인 결과에 의존한다.
-- 기댓값을 미리 낼 수 없으므로 실측값을 기록한다.
-- 고정소수점 연산 차이를 고려하여 판정한다.</t>
+          <t>- 볼륨 인자는 1 부터 시작한다. 배열 접근이 volume - 1 이다.</t>
         </is>
       </c>
       <c r="J102" s="9" t="inlineStr">
         <is>
-          <t>- 자극 볼륨을 1, 5, 10 으로 바꿔 가며 호출하고 산출된 최대 레벨을 기록한다.</t>
+          <t>- 시험 C/T 레벨을 채운 뒤 자극 볼륨을 인자로 넣어 호출한다.
+- g_max_limit_stimulus_amplitude_C_level 앞 4 칸을 조회한다.
+- 볼륨 1, 2, 3, 4 로 네 번 수행한다.</t>
         </is>
       </c>
       <c r="K102" s="9" t="inlineStr">
         <is>
           <t>- 자극 최대 레벨 계산 구현
-[산출 근거] 자극 볼륨과 C/T 레벨로 최대 레벨을 구한다. 맵 데이터에 의존한다. 기댓값을 미리 낼 수 없으므로 지어내지 않는다.
-[판정] 기댓값을 미리 낼 수 없다. 아래 항목의 실측값을 기록한다.
-       고정소수점 연산 차이를 고려하여 판정한다.
-1) 입력 : 시험 벡터 주입
-   예상 출력 : (실측 기록)</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="112.5" customHeight="1">
+[산출 근거] (C - T) 에 자극 볼륨 비율(Q2.22)을 곱해 22 비트 내린 값을 동적 범위로 삼고 T 를 더해 새 C 를 만든다. 새 C 는 원래 C 와 T 사이로 잘린다. 볼륨 비율은 단계 1 부터 0.7, 0.8, 0.9, 1.0 이다. 볼륨 4 는 비율이 1.0 이라 원래 C 가 그대로 나와야 한다.
+[판정] 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
+1) 입력 : 자극 볼륨 1 (비율 0.7)
+   예상 출력 : 앞 4 전극 = 72 110 148 186
+2) 입력 : 자극 볼륨 2 (비율 0.8)
+   예상 출력 : 앞 4 전극 = 81 123 165 207
+3) 입력 : 자극 볼륨 3 (비율 0.9)
+   예상 출력 : 앞 4 전극 = 90 136 182 228
+4) 입력 : 자극 볼륨 4 (비율 1.0)
+   예상 출력 : 앞 4 전극 = 100 150 200 250</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="175" customHeight="1">
       <c r="B103" s="8" t="inlineStr"/>
       <c r="C103" s="8" t="inlineStr"/>
       <c r="D103" s="9" t="inlineStr">
@@ -4427,33 +4447,45 @@
       <c r="H103" s="9" t="inlineStr">
         <is>
           <t>- 대상 유닛이 호출되는 지점에 디버깅용 중단점을 적용한다.
-- 입력 버퍼와 출력 버퍼를 함께 조회할 수 있도록 창을 준비한다.</t>
+- 입력 버퍼와 출력 버퍼를 함께 조회할 수 있도록 창을 준비한다.
+- 자극 볼륨 4 로 최대 레벨을 먼저 계산해 둔다.
+시험 맵 (앞 4 전극만 다르게 두고 나머지는 같은 값)
+  T 레벨  : 10, 20, 30, 40, 나머지 10
+  C 레벨  : 100, 150, 200, 250, 나머지 100
+  xMin    : 100, 200, 300, 400, 나머지 100
+  xMax    : 10000, 20000, 30000, 40000, 나머지 10000</t>
         </is>
       </c>
       <c r="I103" s="9" t="inlineStr">
         <is>
-          <t>- 이 유닛의 출력은 DSP 라이브러리 또는 HEAR 함수체인 결과에 의존한다.
-- 기댓값을 미리 낼 수 없으므로 실측값을 기록한다.
-- 고정소수점 연산 차이를 고려하여 판정한다.</t>
+          <t>- 하드웨어 log2/exp2 와 나눗셈의 마지막 자리 오차가 있을 수 있다. (고정소수점 연산 고려)
+- xMax^p 와 xMin^p 가 같으면 0 으로 나누게 된다. 시험 맵은 그 경우를 피한다.</t>
         </is>
       </c>
       <c r="J103" s="9" t="inlineStr">
         <is>
-          <t>- 호출 후 로그 매핑 계수 A 와 B 를 조회해 기록한다.</t>
+          <t>- 시험 맵을 채우고 자극 볼륨 4 로 최대 레벨을 계산한다.
+- 원 함수를 호출한다.
+- g_logaritmMapping_coeff_A_Q16_8 과 _B_Q16_8 앞 4 칸을 조회한다.</t>
         </is>
       </c>
       <c r="K103" s="9" t="inlineStr">
         <is>
           <t>- 로그 매핑 계수 계산 구현
-[산출 근거] dB 변환 라이브러리를 거친다. 기댓값을 미리 낼 수 없으므로 지어내지 않는다.
-[판정] 기댓값을 미리 낼 수 없다. 아래 항목의 실측값을 기록한다.
-       고정소수점 연산 차이를 고려하여 판정한다.
-1) 입력 : 시험 벡터 주입
-   예상 출력 : (실측 기록)</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="112.5" customHeight="1">
+[산출 근거] 전극마다 A 와 B 두 계수를 만든다. A = ((C - T) &lt;&lt; 13) / (xMax^p - xMin^p) 를 13 비트 내린 값이고, B = (C &lt;&lt; 8) - ((A * xMax^p) &gt;&gt; 16) 이다. x^p 는 거듭제곱 계산 유닛을 쓰고 나눗셈은 SDK 의 하드웨어 나눗셈을 쓴다. 두 함수 모두 수식이 명세되어 있어 재현된다.
+[판정] 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
+1) 입력 : 전극 0 : xMin=100, xMax=10000, C=100, T=10
+   예상 출력 : A = 11602, B = -20588
+2) 입력 : 전극 1 : xMin=200, xMax=20000, C=150, T=20
+   예상 출력 : A = 15103, B = -28313
+3) 입력 : 전극 2 : xMin=300, xMax=30000, C=200, T=30
+   예상 출력 : A = 18585, B = -36042
+4) 입력 : 전극 3 : xMin=400, xMax=40000, C=250, T=40
+   예상 출력 : A = 21989, B = -43773</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="150" customHeight="1">
       <c r="B104" s="8" t="inlineStr"/>
       <c r="C104" s="8" t="inlineStr"/>
       <c r="D104" s="9" t="inlineStr">
@@ -4479,29 +4511,38 @@
       <c r="H104" s="9" t="inlineStr">
         <is>
           <t>- 대상 유닛이 호출되는 지점에 디버깅용 중단점을 적용한다.
-- 입력 버퍼와 출력 버퍼를 함께 조회할 수 있도록 창을 준비한다.</t>
+- 입력 버퍼와 출력 버퍼를 함께 조회할 수 있도록 창을 준비한다.
+- m_audio_volume 을 지정한 값으로 둔다.
+시험 맵 (앞 4 전극만 다르게 두고 나머지는 같은 값)
+  T 레벨  : 10, 20, 30, 40, 나머지 10
+  C 레벨  : 100, 150, 200, 250, 나머지 100
+  xMin    : 100, 200, 300, 400, 나머지 100
+  xMax    : 10000, 20000, 30000, 40000, 나머지 10000</t>
         </is>
       </c>
       <c r="I104" s="9" t="inlineStr">
         <is>
-          <t>- 이 유닛의 출력은 DSP 라이브러리 또는 HEAR 함수체인 결과에 의존한다.
-- 기댓값을 미리 낼 수 없으므로 실측값을 기록한다.
-- 고정소수점 연산 차이를 고려하여 판정한다.</t>
+          <t>- 볼륨 반영 뒤에도 24 비트로 포화시킨다.
+- 앞 유닛과 같은 나눗셈을 쓰므로 같은 오차 기준을 적용한다.</t>
         </is>
       </c>
       <c r="J104" s="9" t="inlineStr">
         <is>
-          <t>- 오디오 볼륨을 바꿔 가며 계수 A 와 B 를 조회해 기록한다.</t>
+          <t>- 오디오 볼륨을 0, 5, 9 로 바꿔 가며 원 함수를 호출한다.
+- 볼륨 반영된 xMin 중간값과 최종 계수 A, B 를 조회해 기록한다.</t>
         </is>
       </c>
       <c r="K104" s="9" t="inlineStr">
         <is>
           <t>- 로그 매핑 계수 계산 유닛, 오디오 볼륨 반영 구현
-[산출 근거] 같은 dB 변환 라이브러리를 거친다. 기댓값을 미리 낼 수 없으므로 지어내지 않는다.
-[판정] 기댓값을 미리 낼 수 없다. 아래 항목의 실측값을 기록한다.
-       고정소수점 연산 차이를 고려하여 판정한다.
-1) 입력 : 시험 벡터 주입
-   예상 출력 : (실측 기록)</t>
+[산출 근거] 앞 유닛과 같은 계수를 만들되, xMin 과 xMax 에 오디오 볼륨의 선형 이득(Q9.15)을 먼저 곱하고 15 비트 내린다. 이득은 볼륨 0 에서 1.0, 볼륨 9 에서 30.5535 다. 볼륨 0 이면 이득이 정확히 1.0 이라 입력이 그대로 나와야 한다.
+[판정] 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
+1) 입력 : 오디오 볼륨 0 (선형 이득 1.0000)
+   예상 출력 : 볼륨 반영 xMin 앞 4 = 100 200 300 400
+2) 입력 : 오디오 볼륨 5 (선형 이득 6.5503)
+   예상 출력 : 볼륨 반영 xMin 앞 4 = 655 1310 1965 2620
+3) 입력 : 오디오 볼륨 9 (선형 이득 29.9424)
+   예상 출력 : 볼륨 반영 xMin 앞 4 = 2994 5988 8982 11976</t>
         </is>
       </c>
     </row>
@@ -4616,7 +4657,7 @@
         </is>
       </c>
     </row>
-    <row r="107" ht="112.5" customHeight="1">
+    <row r="107" ht="125" customHeight="1">
       <c r="B107" s="8" t="inlineStr"/>
       <c r="C107" s="8" t="inlineStr"/>
       <c r="D107" s="9" t="inlineStr">
@@ -4641,39 +4682,35 @@
       </c>
       <c r="H107" s="9" t="inlineStr">
         <is>
-          <t>- 빌드 설정에 TDC_UNIT_TEST 를 정의한다.
-- src/1__cfx/test/tdc_unit_test_cfx.c 를 빌드에 넣는다.
-- 기존 소스는 수정하지 않는다. 매크로가 없으면 이 파일은 빈 번역 단위가 된다.
-- 디버거에서 tdc_ut_run_all() 을 호출한다.
-- tdc_ut_done 에 1 이 대입되는 지점에 중단점을 걸고 tdc_ut_result 를 조회한다.
-- PCM 기록 버퍼(HEAR_ADDR_FIFO_PCM_WRITING)를 조회할 수 있게 창을 준비한다.</t>
+          <t>- 대상 유닛이 호출되는 지점에 디버깅용 중단점을 적용한다.
+- 입력 버퍼와 출력 버퍼를 함께 조회할 수 있도록 창을 준비한다.
+- addr_MapProgramData_firstPulsePhase 를 지정한 값으로 둔다.</t>
         </is>
       </c>
       <c r="I107" s="9" t="inlineStr">
         <is>
-          <t>- 이 유닛의 출력은 DSP 라이브러리 또는 HEAR 함수체인 결과에 의존한다.
-- 기댓값을 미리 낼 수 없으므로 실측값을 기록한다.
-- 고정소수점 연산 차이를 고려하여 판정한다.</t>
+          <t>- 선행 펄스 위상은 1 비트다. 0 또는 1 만 넣는다.</t>
         </is>
       </c>
       <c r="J107" s="9" t="inlineStr">
         <is>
-          <t>- 호출 후 준비된 패킷 헤더 값을 조회해 기록한다.
-- 맵의 자극 모드를 바꿔 가며 헤더가 달라지는지 기록한다.</t>
+          <t>- 선행 펄스 위상을 0 으로 두고 호출해 헤더를 조회한다.
+- 1 로 바꿔 다시 호출해 조회한다.</t>
         </is>
       </c>
       <c r="K107" s="9" t="inlineStr">
         <is>
           <t>- 자극 패킷 헤더 준비 구현
-[산출 근거] 맵의 자극 모드와 전극 배정에 따라 헤더가 정해진다. 맵 데이터에 의존한다. 기댓값을 미리 낼 수 없으므로 지어내지 않는다.
-[판정] 기댓값을 미리 낼 수 없다. 아래 항목의 실측값을 기록한다.
-       고정소수점 연산 차이를 고려하여 판정한다.
-1) 입력 : 시험 벡터 주입
-   예상 출력 : (실측 기록)</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="112.5" customHeight="1">
+[산출 근거] 자극 몰드 0x40000 에 맵의 선행 펄스 위상을 15 비트 자리로 얹어 헤더를 만든다. 단순 비트 조합이라 그대로 재현된다.
+[판정] 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
+1) 입력 : 맵의 선행 펄스 위상 = 0
+   예상 출력 : 0x40000
+2) 입력 : 맵의 선행 펄스 위상 = 1
+   예상 출력 : 0x48000</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="150" customHeight="1">
       <c r="B108" s="8" t="inlineStr"/>
       <c r="C108" s="8" t="inlineStr"/>
       <c r="D108" s="9" t="inlineStr">
@@ -4698,40 +4735,38 @@
       </c>
       <c r="H108" s="9" t="inlineStr">
         <is>
-          <t>- 빌드 설정에 TDC_UNIT_TEST 를 정의한다.
-- src/1__cfx/test/tdc_unit_test_cfx.c 를 빌드에 넣는다.
-- 기존 소스는 수정하지 않는다. 매크로가 없으면 이 파일은 빈 번역 단위가 된다.
-- 디버거에서 tdc_ut_run_all() 을 호출한다.
-- tdc_ut_done 에 1 이 대입되는 지점에 중단점을 걸고 tdc_ut_result 를 조회한다.
-- PCM 기록 버퍼(HEAR_ADDR_FIFO_PCM_WRITING)를 조회할 수 있게 창을 준비한다.</t>
+          <t>- 대상 유닛이 호출되는 지점에 디버깅용 중단점을 적용한다.
+- 입력 버퍼와 출력 버퍼를 함께 조회할 수 있도록 창을 준비한다.
+- addr_MapProgramData_stimulationStrategy 를 지정한 값으로 둔다.
+- 각 하위 유닛 진입점에 중단점을 걸어 둔다.</t>
         </is>
       </c>
       <c r="I108" s="9" t="inlineStr">
         <is>
-          <t>- 이 유닛의 출력은 DSP 라이브러리 또는 HEAR 함수체인 결과에 의존한다.
-- 기댓값을 미리 낼 수 없으므로 실측값을 기록한다.
-- 고정소수점 연산 차이를 고려하여 판정한다.</t>
+          <t>- 정의되지 않은 값은 medium 과 같이 아무 것도 하지 않는다.</t>
         </is>
       </c>
       <c r="J108" s="9" t="inlineStr">
         <is>
-          <t>- 맵의 자극 기법을 CIS 로 두고 호출해 어느 하위 유닛이 불리는지 확인한다.
-- NofM 으로 바꿔 다시 호출해 확인한다.
-- 각각의 PCM 출력 버퍼를 조회해 기록한다.</t>
+          <t>- 자극 기법을 1, 2, 3 으로 바꿔 가며 호출한다.
+- 어느 하위 유닛 중단점에 걸리는지 기록한다.</t>
         </is>
       </c>
       <c r="K108" s="9" t="inlineStr">
         <is>
           <t>- 자극 기법 실행 구현
-[산출 근거] 맵의 자극 기법 설정에 따라 CIS 또는 NofM 으로 갈린다. 기댓값을 미리 낼 수 없으므로 지어내지 않는다.
-[판정] 기댓값을 미리 낼 수 없다. 아래 항목의 실측값을 기록한다.
-       고정소수점 연산 차이를 고려하여 판정한다.
-1) 입력 : 시험 벡터 주입
-   예상 출력 : (실측 기록)</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="112.5" customHeight="1">
+[산출 근거] 맵의 자극 기법 설정으로 갈린다. CIS(1)면 대역 대표값 산출과 로그 매핑을 거쳐 CIS 유닛을, NofM(2)이면 NofM 유닛을 부른다. medium(3)은 아무 것도 하지 않는다. 어느 하위 유닛이 불리는지가 판정 대상이다.
+[판정] 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
+1) 입력 : 맵의 자극 기법 = 1 (CIS)
+   예상 출력 : 대역 대표값 산출 -&gt; 로그 매핑 -&gt; CIS 자극 기법
+2) 입력 : 맵의 자극 기법 = 2 (NofM)
+   예상 출력 : NofM 자극 기법
+3) 입력 : 맵의 자극 기법 = 3 (medium)
+   예상 출력 : 아무 것도 하지 않는다</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="100" customHeight="1">
       <c r="B109" s="8" t="inlineStr"/>
       <c r="C109" s="8" t="inlineStr"/>
       <c r="D109" s="9" t="inlineStr">
@@ -4756,39 +4791,39 @@
       </c>
       <c r="H109" s="9" t="inlineStr">
         <is>
-          <t>- 빌드 설정에 TDC_UNIT_TEST 를 정의한다.
-- src/1__cfx/test/tdc_unit_test_cfx.c 를 빌드에 넣는다.
-- 기존 소스는 수정하지 않는다. 매크로가 없으면 이 파일은 빈 번역 단위가 된다.
-- 디버거에서 tdc_ut_run_all() 을 호출한다.
-- tdc_ut_done 에 1 이 대입되는 지점에 중단점을 걸고 tdc_ut_result 를 조회한다.
-- PCM 기록 버퍼(HEAR_ADDR_FIFO_PCM_WRITING)를 조회할 수 있게 창을 준비한다.</t>
+          <t>- 대상 유닛이 호출되는 지점에 디버깅용 중단점을 적용한다.
+- 입력 버퍼와 출력 버퍼를 함께 조회할 수 있도록 창을 준비한다.
+- g_pcm_amplitude_level 32 칸과 addr_MapProgramData_CIS_FreqBandOrder 를 시험 값으로 채운다.
+시험 맵 (앞 4 전극만 다르게 두고 나머지는 같은 값)
+  T 레벨  : 10, 20, 30, 40, 나머지 10
+  C 레벨  : 100, 150, 200, 250, 나머지 100
+  xMin    : 100, 200, 300, 400, 나머지 100
+  xMax    : 10000, 20000, 30000, 40000, 나머지 10000</t>
         </is>
       </c>
       <c r="I109" s="9" t="inlineStr">
         <is>
-          <t>- 이 유닛의 출력은 DSP 라이브러리 또는 HEAR 함수체인 결과에 의존한다.
-- 기댓값을 미리 낼 수 없으므로 실측값을 기록한다.
-- 고정소수점 연산 차이를 고려하여 판정한다.</t>
+          <t>- 시험 맵을 고정한 상태에서만 이 기댓값이 성립한다.
+- 앞단 유닛의 결과를 입력으로 쓰므로 그 유닛을 먼저 시험한다.</t>
         </is>
       </c>
       <c r="J109" s="9" t="inlineStr">
         <is>
-          <t>- 호출 후 PCM 출력 버퍼에서 자극 헤더, 전극 번호, 자극 레벨을 조회해 기록한다.
-- 맵의 CIS 대역 순서와 실제 출력 순서가 맞는지 기록한다.</t>
+          <t>- 자극 레벨을 전극 색인과 같게(0..31) 채우고 CIS 대역 순서를 0..31 로 둔다.
+- 원 함수를 호출하고 addr_stimulationTempBuff 를 조회한다.</t>
         </is>
       </c>
       <c r="K109" s="9" t="inlineStr">
         <is>
           <t>- CIS 자극 기법 구현
-[산출 근거] 대역 대표값과 매핑 결과에 의존한다. 앞단 라이브러리 출력이 입력이 된다. 기댓값을 미리 낼 수 없으므로 지어내지 않는다.
-[판정] 기댓값을 미리 낼 수 없다. 아래 항목의 실측값을 기록한다.
-       고정소수점 연산 차이를 고려하여 판정한다.
-1) 입력 : 시험 벡터 주입
-   예상 출력 : (실측 기록)</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="112.5" customHeight="1">
+[산출 근거] 맵 데이터와 공유 메모리를 시험용 상수로 고정하면 출력이 결정된다. 아래 시험 맵을 쓴다. 맵의 CIS 대역 순서대로 전극을 돌며 자극 레벨을 패킷에 싣는다. 대역 대표값과 매핑 결과를 입력으로 받으므로 그 버퍼를 고정하면 결정적이다.
+[판정] 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
+1) 입력 : 자극 레벨[i] = i, CIS 대역 순서 = 0 1 2 ... 31, 선행 펄스 위상 0
+   예상 출력 : 각 자리에 «자극 몰드 | 전극번호 &lt;&lt; 10 | 자극레벨 &lt;&lt; 2» 가 실린다. 전극 0 자리는 0x40000 가 기준이다</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="100" customHeight="1">
       <c r="B110" s="8" t="inlineStr"/>
       <c r="C110" s="8" t="inlineStr"/>
       <c r="D110" s="9" t="inlineStr">
@@ -4813,34 +4848,31 @@
       </c>
       <c r="H110" s="9" t="inlineStr">
         <is>
-          <t>- 빌드 설정에 TDC_UNIT_TEST 를 정의한다.
-- src/1__cfx/test/tdc_unit_test_cfx.c 를 빌드에 넣는다.
-- 기존 소스는 수정하지 않는다. 매크로가 없으면 이 파일은 빈 번역 단위가 된다.
-- 디버거에서 tdc_ut_run_all() 을 호출한다.
-- tdc_ut_done 에 1 이 대입되는 지점에 중단점을 걸고 tdc_ut_result 를 조회한다.
-- PCM 기록 버퍼(HEAR_ADDR_FIFO_PCM_WRITING)를 조회할 수 있게 창을 준비한다.</t>
+          <t>- 대상 유닛이 호출되는 지점에 디버깅용 중단점을 적용한다.
+- 입력 버퍼와 출력 버퍼를 함께 조회할 수 있도록 창을 준비한다.
+- g_pcm_amplitude_level 32 칸을 시험 벡터로 채운다.</t>
         </is>
       </c>
       <c r="I110" s="9" t="inlineStr">
         <is>
-          <t>- 이 유닛의 출력은 DSP 라이브러리 또는 HEAR 함수체인 결과에 의존한다.
-- 기댓값을 미리 낼 수 없으므로 실측값을 기록한다.
-- 고정소수점 연산 차이를 고려하여 판정한다.</t>
+          <t>- 시험 맵을 고정한 상태에서만 이 기댓값이 성립한다.
+- 앞단 유닛의 결과를 입력으로 쓰므로 그 유닛을 먼저 시험한다.</t>
         </is>
       </c>
       <c r="J110" s="9" t="inlineStr">
         <is>
-          <t>- 호출 후 PCM 출력 버퍼를 조회해 교차 배치 순서대로 자극이 실렸는지 기록한다.</t>
+          <t>- 진폭 32 개를 모두 100 으로 채운다. (동점 벡터)
+- 원 함수를 호출한다.
+- 선택 결과, 교차 결과, PCM 버퍼를 차례로 조회한다.</t>
         </is>
       </c>
       <c r="K110" s="9" t="inlineStr">
         <is>
           <t>- NofM 자극 기법 구현
-[산출 근거] 피크 선택과 인터리빙 결과를 받아 패킷을 만든다. 앞단 결과에 의존한다. 기댓값을 미리 낼 수 없으므로 지어내지 않는다.
-[판정] 기댓값을 미리 낼 수 없다. 아래 항목의 실측값을 기록한다.
-       고정소수점 연산 차이를 고려하여 판정한다.
-1) 입력 : 시험 벡터 주입
-   예상 출력 : (실측 기록)</t>
+[산출 근거] 맵 데이터와 공유 메모리를 시험용 상수로 고정하면 출력이 결정된다. 아래 시험 맵을 쓴다. 피크 선택, 인터리빙, 패킷 생성, PCM 기록을 차례로 부른다. 앞 네 유닛이 각각 재현되므로 이 유닛은 그 호출 순서와 연결을 확인한다.
+[판정] 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
+1) 입력 : 진폭 32 개가 모두 100 (동점)
+   예상 출력 : 선택 결과 = 0 1 2 ... 15 (저주파 보호), 교차 결과 = 0 8 1 9 2 10 3 11 4 12 5 13 6 14 7 15, PCM 버퍼에 그 순서로 자극이 실린다</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5060,7 @@
         </is>
       </c>
     </row>
-    <row r="114" ht="112.5" customHeight="1">
+    <row r="114" ht="150" customHeight="1">
       <c r="B114" s="8" t="inlineStr"/>
       <c r="C114" s="8" t="inlineStr"/>
       <c r="D114" s="9" t="inlineStr">
@@ -5053,38 +5085,37 @@
       </c>
       <c r="H114" s="9" t="inlineStr">
         <is>
-          <t>- 빌드 설정에 TDC_UNIT_TEST 를 정의한다.
-- src/1__cfx/test/tdc_unit_test_cfx.c 를 빌드에 넣는다.
-- 기존 소스는 수정하지 않는다. 매크로가 없으면 이 파일은 빈 번역 단위가 된다.
-- 디버거에서 tdc_ut_run_all() 을 호출한다.
-- tdc_ut_done 에 1 이 대입되는 지점에 중단점을 걸고 tdc_ut_result 를 조회한다.
-- PCM 기록 버퍼(HEAR_ADDR_FIFO_PCM_WRITING)를 조회할 수 있게 창을 준비한다.</t>
+          <t>- 대상 유닛이 호출되는 지점에 디버깅용 중단점을 적용한다.
+- 입력 버퍼와 출력 버퍼를 함께 조회할 수 있도록 창을 준비한다.
+- g_NofM_notAdjacent_BandIndex 16 칸과 g_NofM_LastStimulus_BandIndex 를 지정한 값으로 둔다.</t>
         </is>
       </c>
       <c r="I114" s="9" t="inlineStr">
         <is>
-          <t>- 이 유닛의 출력은 DSP 라이브러리 또는 HEAR 함수체인 결과에 의존한다.
-- 기댓값을 미리 낼 수 없으므로 실측값을 기록한다.
-- 고정소수점 연산 차이를 고려하여 판정한다.</t>
+          <t>- 거리는 절대값으로 잰다. 같으면 앞에서 시작한다.</t>
         </is>
       </c>
       <c r="J114" s="9" t="inlineStr">
         <is>
-          <t>- 호출 후 만들어진 패킷 값을 조회해 전극 번호와 자극 레벨이 자리에 맞는지 기록한다.</t>
+          <t>- 교차 배열을 지정한 값으로 채우고 직전 자극 전극을 0, 15, 8 로 바꿔 호출한다.
+- 시작 색인과 갱신된 직전 자극 전극을 조회해 기록한다.</t>
         </is>
       </c>
       <c r="K114" s="9" t="inlineStr">
         <is>
           <t>- NofM 패킷 생성 구현
-[산출 근거] 선택된 대역의 자극 레벨을 패킷으로 만든다. 매핑 결과에 의존한다. 기댓값을 미리 낼 수 없으므로 지어내지 않는다.
-[판정] 기댓값을 미리 낼 수 없다. 아래 항목의 실측값을 기록한다.
-       고정소수점 연산 차이를 고려하여 판정한다.
-1) 입력 : 시험 벡터 주입
-   예상 출력 : (실측 기록)</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="112.5" customHeight="1">
+[산출 근거] 직전에 자극한 전극에서 교차 배열의 처음과 끝 중 어느 쪽이 더 먼지 재어 먼 쪽에서 시작한다. 연달아 가까운 전극을 자극하지 않게 하는 처리다. 시작 방향에 따라 다음 주기의 직전 자극 전극도 달라진다.
+[판정] 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
+1) 입력 : 교차 배열 0 8 1 9 2 10 3 11 4 12 5 13 6 14 7 15, 직전 자극 전극 0
+   예상 출력 : 시작 색인 15 (뒤에서), 갱신될 직전 자극 전극 7
+2) 입력 : 교차 배열 0 8 1 9 2 10 3 11 4 12 5 13 6 14 7 15, 직전 자극 전극 15
+   예상 출력 : 시작 색인 0 (앞에서), 갱신될 직전 자극 전극 15
+3) 입력 : 교차 배열 0 8 1 9 2 10 3 11 4 12 5 13 6 14 7 15, 직전 자극 전극 8
+   예상 출력 : 시작 색인 0 (앞에서), 갱신될 직전 자극 전극 15</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="125" customHeight="1">
       <c r="B115" s="8" t="inlineStr"/>
       <c r="C115" s="8" t="inlineStr"/>
       <c r="D115" s="9" t="inlineStr">
@@ -5109,34 +5140,34 @@
       </c>
       <c r="H115" s="9" t="inlineStr">
         <is>
-          <t>- 빌드 설정에 TDC_UNIT_TEST 를 정의한다.
-- src/1__cfx/test/tdc_unit_test_cfx.c 를 빌드에 넣는다.
-- 기존 소스는 수정하지 않는다. 매크로가 없으면 이 파일은 빈 번역 단위가 된다.
-- 디버거에서 tdc_ut_run_all() 을 호출한다.
-- tdc_ut_done 에 1 이 대입되는 지점에 중단점을 걸고 tdc_ut_result 를 조회한다.
-- PCM 기록 버퍼(HEAR_ADDR_FIFO_PCM_WRITING)를 조회할 수 있게 창을 준비한다.</t>
+          <t>- 대상 유닛이 호출되는 지점에 디버깅용 중단점을 적용한다.
+- 입력 버퍼와 출력 버퍼를 함께 조회할 수 있도록 창을 준비한다.
+- addr_stimulationTempBuff 16 칸에 시험 값을 쓴다.
+- g_pcmFrameNum_per_channel 과 g_transferableChannelNum_per_1msec 를 지정한 값으로 둔다.
+- addr_transferred_index 를 0 으로 둔다.</t>
         </is>
       </c>
       <c r="I115" s="9" t="inlineStr">
         <is>
-          <t>- 이 유닛의 출력은 DSP 라이브러리 또는 HEAR 함수체인 결과에 의존한다.
-- 기댓값을 미리 낼 수 없으므로 실측값을 기록한다.
-- 고정소수점 연산 차이를 고려하여 판정한다.</t>
+          <t>- FIFO 기록 방향이 감소 방향이다. 조회할 때 그 순서를 고려한다.</t>
         </is>
       </c>
       <c r="J115" s="9" t="inlineStr">
         <is>
-          <t>- 호출 전후의 PCM 기록 버퍼를 조회해 기록 위치와 내용을 기록한다.</t>
+          <t>- 임시 버퍼와 두 설정값을 채우고 호출한다.
+- PCM 기록 버퍼 24 칸과 addr_transferred_index 를 조회한다.
+- 프레임 수 1(전달 24)과 3(전달 8) 두 조합으로 수행한다.</t>
         </is>
       </c>
       <c r="K115" s="9" t="inlineStr">
         <is>
           <t>- NofM PCM 기록 구현
-[산출 근거] 만들어진 패킷을 PCM 버퍼에 기록한다. 앞단 결과에 의존한다. 기댓값을 미리 낼 수 없으므로 지어내지 않는다.
-[판정] 기댓값을 미리 낼 수 없다. 아래 항목의 실측값을 기록한다.
-       고정소수점 연산 차이를 고려하여 판정한다.
-1) 입력 : 시험 벡터 주입
-   예상 출력 : (실측 기록)</t>
+[산출 근거] PCM 버퍼 24 칸을 먼저 대기 몰드로 모두 채운 뒤, 채널당 프레임 수를 간격으로 자극 데이터를 얹는다. NofM 개수(16)가 전달 가능 채널 수보다 작으면 16 개를 모두 싣고 색인을 0 으로 되돌리고, 아니면 전달 가능한 만큼만 싣고 색인을 이어간다.
+[판정] 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
+1) 입력 : 채널당 프레임 1, 전달 가능 채널 24, 임시 버퍼 0x40000+i
+   예상 출력 : 앞 8 칸 = 0x40000 0x40001 0x40002 0x40003 0x40004 0x40005 0x40006 0x40007 ... (대기 몰드 0x25555 로 채운 뒤 1 칸 간격으로 얹음), 다음 전송 색인 0
+2) 입력 : 채널당 프레임 3, 전달 가능 채널 8, 임시 버퍼 0x40000+i
+   예상 출력 : 앞 8 칸 = 0x40000 0x25555 0x25555 0x40001 0x25555 0x25555 0x40002 0x25555 ... (대기 몰드 0x25555 로 채운 뒤 3 칸 간격으로 얹음), 다음 전송 색인 8</t>
         </is>
       </c>
     </row>
@@ -5252,7 +5283,7 @@
         </is>
       </c>
     </row>
-    <row r="118" ht="112.5" customHeight="1">
+    <row r="118" ht="125" customHeight="1">
       <c r="B118" s="8" t="inlineStr"/>
       <c r="C118" s="8" t="inlineStr"/>
       <c r="D118" s="9" t="inlineStr">
@@ -5276,6 +5307,114 @@
         </is>
       </c>
       <c r="H118" s="9" t="inlineStr">
+        <is>
+          <t>- 대상 유닛이 호출되는 지점에 디버깅용 중단점을 적용한다.
+- 입력 버퍼와 출력 버퍼를 함께 조회할 수 있도록 창을 준비한다.
+- addr_stimulationTempBuff 를 시험 값으로 채운다.
+- g_pcmFrameNum_per_channel 을 1 과 2 로 바꿔 가며 수행한다.</t>
+        </is>
+      </c>
+      <c r="I118" s="9" t="inlineStr">
+        <is>
+          <t>- 시험 맵을 고정한 상태에서만 이 기댓값이 성립한다.
+- 앞단 유닛의 결과를 입력으로 쓰므로 그 유닛을 먼저 시험한다.</t>
+        </is>
+      </c>
+      <c r="J118" s="9" t="inlineStr">
+        <is>
+          <t>- 임시 버퍼를 0x40000+i 로 채운다.
+- 채널당 프레임 수를 1 로 두고 호출해 PCM 버퍼 24 칸을 조회한다.
+- 2 로 바꿔 다시 수행한다.</t>
+        </is>
+      </c>
+      <c r="K118" s="9" t="inlineStr">
+        <is>
+          <t>- 실시간 자극 비트스트림 생성 구현
+[산출 근거] 맵 데이터와 공유 메모리를 시험용 상수로 고정하면 출력이 결정된다. 아래 시험 맵을 쓴다. 자극 기법이 만든 임시 버퍼를 PCM 기록 버퍼로 옮긴다. 임시 버퍼를 고정하면 결정적이다.
+[판정] 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
+1) 입력 : 임시 버퍼 0x40000+i, 채널당 프레임 1
+   예상 출력 : 24 칸에 자극이 한 칸 간격으로 실린다
+2) 입력 : 같은 입력, 채널당 프레임 2
+   예상 출력 : 두 칸 간격으로 실리고 사이는 대기 몰드 0x25555 로 남는다</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="100" customHeight="1">
+      <c r="B119" s="8" t="inlineStr"/>
+      <c r="C119" s="8" t="inlineStr"/>
+      <c r="D119" s="9" t="inlineStr">
+        <is>
+          <t>SW-FW-UnitTest-CFX-ID-94</t>
+        </is>
+      </c>
+      <c r="E119" s="9" t="inlineStr">
+        <is>
+          <t>특정 명령 비트스트림 생성</t>
+        </is>
+      </c>
+      <c r="F119" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G119" s="9" t="inlineStr">
+        <is>
+          <t>SU-ID-CFX-094</t>
+        </is>
+      </c>
+      <c r="H119" s="9" t="inlineStr">
+        <is>
+          <t>- 대상 유닛이 호출되는 지점에 디버깅용 중단점을 적용한다.
+- 입력 버퍼와 출력 버퍼를 함께 조회할 수 있도록 창을 준비한다.
+- 공유 메모리 PCM_specificBuffer 24 칸에 시험 값을 쓴다.</t>
+        </is>
+      </c>
+      <c r="I119" s="9" t="inlineStr">
+        <is>
+          <t>- 시험 맵을 고정한 상태에서만 이 기댓값이 성립한다.
+- 앞단 유닛의 결과를 입력으로 쓰므로 그 유닛을 먼저 시험한다.</t>
+        </is>
+      </c>
+      <c r="J119" s="9" t="inlineStr">
+        <is>
+          <t>- 특정 명령 버퍼를 0x60000+i 로 채운다.
+- 원 함수를 호출하고 PCM 기록 버퍼 24 칸을 조회한다.</t>
+        </is>
+      </c>
+      <c r="K119" s="9" t="inlineStr">
+        <is>
+          <t>- 특정 명령 비트스트림 생성 구현
+[산출 근거] 맵 데이터와 공유 메모리를 시험용 상수로 고정하면 출력이 결정된다. 아래 시험 맵을 쓴다. 공유 메모리의 특정 명령 버퍼 내용을 PCM 기록 버퍼로 그대로 옮긴다. 값을 바꾸지 않는 복사다.
+[판정] 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
+1) 입력 : 특정 명령 버퍼[i] = 0x60000 + i (i = 0..23)
+   예상 출력 : PCM 기록 버퍼 24 칸이 같은 값이어야 한다 (그대로 복사)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="100" customHeight="1">
+      <c r="B120" s="8" t="inlineStr"/>
+      <c r="C120" s="8" t="inlineStr"/>
+      <c r="D120" s="9" t="inlineStr">
+        <is>
+          <t>SW-FW-UnitTest-CFX-ID-95</t>
+        </is>
+      </c>
+      <c r="E120" s="9" t="inlineStr">
+        <is>
+          <t>대기 비트스트림 생성</t>
+        </is>
+      </c>
+      <c r="F120" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G120" s="9" t="inlineStr">
+        <is>
+          <t>SU-ID-CFX-095</t>
+        </is>
+      </c>
+      <c r="H120" s="9" t="inlineStr">
         <is>
           <t>- 빌드 설정에 TDC_UNIT_TEST 를 정의한다.
 - src/1__cfx/test/tdc_unit_test_cfx.c 를 빌드에 넣는다.
@@ -5285,54 +5424,55 @@
 - PCM 기록 버퍼(HEAR_ADDR_FIFO_PCM_WRITING)를 조회할 수 있게 창을 준비한다.</t>
         </is>
       </c>
-      <c r="I118" s="9" t="inlineStr">
-        <is>
-          <t>- 이 유닛의 출력은 DSP 라이브러리 또는 HEAR 함수체인 결과에 의존한다.
-- 기댓값을 미리 낼 수 없으므로 실측값을 기록한다.
-- 고정소수점 연산 차이를 고려하여 판정한다.</t>
-        </is>
-      </c>
-      <c r="J118" s="9" t="inlineStr">
-        <is>
-          <t>- 호출 후 PCM 기록 버퍼 24 칸을 조회해 자극용 헤더, 전극 번호, 자극 레벨을 기록한다.
-- 채널당 프레임 수를 1 과 2 로 바꿔 가며 각각 기록한다.</t>
-        </is>
-      </c>
-      <c r="K118" s="9" t="inlineStr">
-        <is>
-          <t>- 실시간 자극 비트스트림 생성 구현
-[산출 근거] 실시간 자극 데이터를 비트스트림으로 만든다. 자극 기법 결과에 의존한다. 기댓값을 미리 낼 수 없으므로 지어내지 않는다.
-[판정] 기댓값을 미리 낼 수 없다. 아래 항목의 실측값을 기록한다.
-       고정소수점 연산 차이를 고려하여 판정한다.
-1) 입력 : 시험 벡터 주입
-   예상 출력 : (실측 기록)</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="112.5" customHeight="1">
-      <c r="B119" s="8" t="inlineStr"/>
-      <c r="C119" s="8" t="inlineStr"/>
-      <c r="D119" s="9" t="inlineStr">
-        <is>
-          <t>SW-FW-UnitTest-CFX-ID-94</t>
-        </is>
-      </c>
-      <c r="E119" s="9" t="inlineStr">
-        <is>
-          <t>특정 명령 비트스트림 생성</t>
-        </is>
-      </c>
-      <c r="F119" s="8" t="inlineStr">
+      <c r="I120" s="9" t="inlineStr">
+        <is>
+          <t>- 결과 배열에서 값 -999 는 구분자다. 그 다음 값이 유닛 번호다.
+- 시험은 전역 상태를 바꾼다. 시험 후에는 장치를 재기동한다.
+- 시험 코드는 평시 빌드에서 제외되므로 정상 동작에 영향을 주지 않는다.
+- 버퍼 기록 방향이 감소 방향이다. 시작 주소에서 아래로 24 칸을 본다.</t>
+        </is>
+      </c>
+      <c r="J120" s="9" t="inlineStr">
+        <is>
+          <t>- 버퍼를 미리 다른 값(예: 0x12345)으로 채워 둔다.
+- 원 함수를 한 번 호출한다.
+- 기록 버퍼 시작 주소부터 감소 방향으로 24 칸을 조회한다.</t>
+        </is>
+      </c>
+      <c r="K120" s="9" t="inlineStr">
+        <is>
+          <t>- 대기 비트스트림 생성 구현
+[산출 근거] PCM 기록 버퍼 시작 주소부터 감소 방향으로 24 칸을 같은 값으로 채운다. 채우는 값은 0x25555 다.
+[판정] 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
+1) 입력 : 버퍼를 0x12345 로 채운 뒤 호출
+   예상 출력 : 24 칸 모두 0x25555</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="100" customHeight="1">
+      <c r="B121" s="8" t="inlineStr"/>
+      <c r="C121" s="8" t="inlineStr"/>
+      <c r="D121" s="9" t="inlineStr">
+        <is>
+          <t>SW-FW-UnitTest-CFX-ID-96</t>
+        </is>
+      </c>
+      <c r="E121" s="9" t="inlineStr">
+        <is>
+          <t>연결 검사용 비트스트림 생성</t>
+        </is>
+      </c>
+      <c r="F121" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G119" s="9" t="inlineStr">
-        <is>
-          <t>SU-ID-CFX-094</t>
-        </is>
-      </c>
-      <c r="H119" s="9" t="inlineStr">
+      <c r="G121" s="9" t="inlineStr">
+        <is>
+          <t>SU-ID-CFX-096</t>
+        </is>
+      </c>
+      <c r="H121" s="9" t="inlineStr">
         <is>
           <t>- 빌드 설정에 TDC_UNIT_TEST 를 정의한다.
 - src/1__cfx/test/tdc_unit_test_cfx.c 를 빌드에 넣는다.
@@ -5342,54 +5482,55 @@
 - PCM 기록 버퍼(HEAR_ADDR_FIFO_PCM_WRITING)를 조회할 수 있게 창을 준비한다.</t>
         </is>
       </c>
-      <c r="I119" s="9" t="inlineStr">
-        <is>
-          <t>- 이 유닛의 출력은 DSP 라이브러리 또는 HEAR 함수체인 결과에 의존한다.
-- 기댓값을 미리 낼 수 없으므로 실측값을 기록한다.
-- 고정소수점 연산 차이를 고려하여 판정한다.</t>
-        </is>
-      </c>
-      <c r="J119" s="9" t="inlineStr">
-        <is>
-          <t>- 특정 명령 버퍼에 알려진 값을 넣고 호출한다.
-- PCM 기록 버퍼 24 칸이 그 값과 같은지 조회해 기록한다.</t>
-        </is>
-      </c>
-      <c r="K119" s="9" t="inlineStr">
-        <is>
-          <t>- 특정 명령 비트스트림 생성 구현
-[산출 근거] 공유 메모리의 특정 명령 버퍼 내용을 그대로 내보낸다. 버퍼 내용에 의존한다. 기댓값을 미리 낼 수 없으므로 지어내지 않는다.
-[판정] 기댓값을 미리 낼 수 없다. 아래 항목의 실측값을 기록한다.
-       고정소수점 연산 차이를 고려하여 판정한다.
-1) 입력 : 시험 벡터 주입
-   예상 출력 : (실측 기록)</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="100" customHeight="1">
-      <c r="B120" s="8" t="inlineStr"/>
-      <c r="C120" s="8" t="inlineStr"/>
-      <c r="D120" s="9" t="inlineStr">
-        <is>
-          <t>SW-FW-UnitTest-CFX-ID-95</t>
-        </is>
-      </c>
-      <c r="E120" s="9" t="inlineStr">
-        <is>
-          <t>대기 비트스트림 생성</t>
-        </is>
-      </c>
-      <c r="F120" s="8" t="inlineStr">
+      <c r="I121" s="9" t="inlineStr">
+        <is>
+          <t>- 결과 배열에서 값 -999 는 구분자다. 그 다음 값이 유닛 번호다.
+- 시험은 전역 상태를 바꾼다. 시험 후에는 장치를 재기동한다.
+- 시험 코드는 평시 빌드에서 제외되므로 정상 동작에 영향을 주지 않는다.
+- 버퍼 기록 방향이 감소 방향이다. 시작 주소에서 아래로 24 칸을 본다.</t>
+        </is>
+      </c>
+      <c r="J121" s="9" t="inlineStr">
+        <is>
+          <t>- 버퍼를 미리 다른 값(예: 0x12345)으로 채워 둔다.
+- 원 함수를 한 번 호출한다.
+- 기록 버퍼 시작 주소부터 감소 방향으로 24 칸을 조회한다.</t>
+        </is>
+      </c>
+      <c r="K121" s="9" t="inlineStr">
+        <is>
+          <t>- 연결 검사용 비트스트림 생성 구현
+[산출 근거] PCM 기록 버퍼 시작 주소부터 감소 방향으로 24 칸을 같은 값으로 채운다. 채우는 값은 0x35555 다.
+[판정] 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
+1) 입력 : 버퍼를 0x12345 로 채운 뒤 호출
+   예상 출력 : 24 칸 모두 0x35555</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="100" customHeight="1">
+      <c r="B122" s="8" t="inlineStr"/>
+      <c r="C122" s="8" t="inlineStr"/>
+      <c r="D122" s="9" t="inlineStr">
+        <is>
+          <t>SW-FW-UnitTest-CFX-ID-97</t>
+        </is>
+      </c>
+      <c r="E122" s="9" t="inlineStr">
+        <is>
+          <t>영 채움 생성</t>
+        </is>
+      </c>
+      <c r="F122" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="G120" s="9" t="inlineStr">
-        <is>
-          <t>SU-ID-CFX-095</t>
-        </is>
-      </c>
-      <c r="H120" s="9" t="inlineStr">
+      <c r="G122" s="9" t="inlineStr">
+        <is>
+          <t>SU-ID-CFX-097</t>
+        </is>
+      </c>
+      <c r="H122" s="9" t="inlineStr">
         <is>
           <t>- 빌드 설정에 TDC_UNIT_TEST 를 정의한다.
 - src/1__cfx/test/tdc_unit_test_cfx.c 를 빌드에 넣는다.
@@ -5399,122 +5540,6 @@
 - PCM 기록 버퍼(HEAR_ADDR_FIFO_PCM_WRITING)를 조회할 수 있게 창을 준비한다.</t>
         </is>
       </c>
-      <c r="I120" s="9" t="inlineStr">
-        <is>
-          <t>- 결과 배열에서 값 -999 는 구분자다. 그 다음 값이 유닛 번호다.
-- 시험은 전역 상태를 바꾼다. 시험 후에는 장치를 재기동한다.
-- 시험 코드는 평시 빌드에서 제외되므로 정상 동작에 영향을 주지 않는다.
-- 버퍼 기록 방향이 감소 방향이다. 시작 주소에서 아래로 24 칸을 본다.</t>
-        </is>
-      </c>
-      <c r="J120" s="9" t="inlineStr">
-        <is>
-          <t>- 버퍼를 미리 다른 값(예: 0x12345)으로 채워 둔다.
-- 원 함수를 한 번 호출한다.
-- 기록 버퍼 시작 주소부터 감소 방향으로 24 칸을 조회한다.</t>
-        </is>
-      </c>
-      <c r="K120" s="9" t="inlineStr">
-        <is>
-          <t>- 대기 비트스트림 생성 구현
-[산출 근거] PCM 기록 버퍼 시작 주소부터 감소 방향으로 24 칸을 같은 값으로 채운다. 채우는 값은 0x25555 다.
-[판정] 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
-1) 입력 : 버퍼를 0x12345 로 채운 뒤 호출
-   예상 출력 : 24 칸 모두 0x25555</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="100" customHeight="1">
-      <c r="B121" s="8" t="inlineStr"/>
-      <c r="C121" s="8" t="inlineStr"/>
-      <c r="D121" s="9" t="inlineStr">
-        <is>
-          <t>SW-FW-UnitTest-CFX-ID-96</t>
-        </is>
-      </c>
-      <c r="E121" s="9" t="inlineStr">
-        <is>
-          <t>연결 검사용 비트스트림 생성</t>
-        </is>
-      </c>
-      <c r="F121" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G121" s="9" t="inlineStr">
-        <is>
-          <t>SU-ID-CFX-096</t>
-        </is>
-      </c>
-      <c r="H121" s="9" t="inlineStr">
-        <is>
-          <t>- 빌드 설정에 TDC_UNIT_TEST 를 정의한다.
-- src/1__cfx/test/tdc_unit_test_cfx.c 를 빌드에 넣는다.
-- 기존 소스는 수정하지 않는다. 매크로가 없으면 이 파일은 빈 번역 단위가 된다.
-- 디버거에서 tdc_ut_run_all() 을 호출한다.
-- tdc_ut_done 에 1 이 대입되는 지점에 중단점을 걸고 tdc_ut_result 를 조회한다.
-- PCM 기록 버퍼(HEAR_ADDR_FIFO_PCM_WRITING)를 조회할 수 있게 창을 준비한다.</t>
-        </is>
-      </c>
-      <c r="I121" s="9" t="inlineStr">
-        <is>
-          <t>- 결과 배열에서 값 -999 는 구분자다. 그 다음 값이 유닛 번호다.
-- 시험은 전역 상태를 바꾼다. 시험 후에는 장치를 재기동한다.
-- 시험 코드는 평시 빌드에서 제외되므로 정상 동작에 영향을 주지 않는다.
-- 버퍼 기록 방향이 감소 방향이다. 시작 주소에서 아래로 24 칸을 본다.</t>
-        </is>
-      </c>
-      <c r="J121" s="9" t="inlineStr">
-        <is>
-          <t>- 버퍼를 미리 다른 값(예: 0x12345)으로 채워 둔다.
-- 원 함수를 한 번 호출한다.
-- 기록 버퍼 시작 주소부터 감소 방향으로 24 칸을 조회한다.</t>
-        </is>
-      </c>
-      <c r="K121" s="9" t="inlineStr">
-        <is>
-          <t>- 연결 검사용 비트스트림 생성 구현
-[산출 근거] PCM 기록 버퍼 시작 주소부터 감소 방향으로 24 칸을 같은 값으로 채운다. 채우는 값은 0x35555 다.
-[판정] 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
-1) 입력 : 버퍼를 0x12345 로 채운 뒤 호출
-   예상 출력 : 24 칸 모두 0x35555</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="100" customHeight="1">
-      <c r="B122" s="8" t="inlineStr"/>
-      <c r="C122" s="8" t="inlineStr"/>
-      <c r="D122" s="9" t="inlineStr">
-        <is>
-          <t>SW-FW-UnitTest-CFX-ID-97</t>
-        </is>
-      </c>
-      <c r="E122" s="9" t="inlineStr">
-        <is>
-          <t>영 채움 생성</t>
-        </is>
-      </c>
-      <c r="F122" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G122" s="9" t="inlineStr">
-        <is>
-          <t>SU-ID-CFX-097</t>
-        </is>
-      </c>
-      <c r="H122" s="9" t="inlineStr">
-        <is>
-          <t>- 빌드 설정에 TDC_UNIT_TEST 를 정의한다.
-- src/1__cfx/test/tdc_unit_test_cfx.c 를 빌드에 넣는다.
-- 기존 소스는 수정하지 않는다. 매크로가 없으면 이 파일은 빈 번역 단위가 된다.
-- 디버거에서 tdc_ut_run_all() 을 호출한다.
-- tdc_ut_done 에 1 이 대입되는 지점에 중단점을 걸고 tdc_ut_result 를 조회한다.
-- PCM 기록 버퍼(HEAR_ADDR_FIFO_PCM_WRITING)를 조회할 수 있게 창을 준비한다.</t>
-        </is>
-      </c>
       <c r="I122" s="9" t="inlineStr">
         <is>
           <t>- 결과 배열에서 값 -999 는 구분자다. 그 다음 값이 유닛 번호다.
@@ -5672,7 +5697,7 @@
         </is>
       </c>
     </row>
-    <row r="126" ht="112.5" customHeight="1">
+    <row r="126" ht="100" customHeight="1">
       <c r="B126" s="8" t="inlineStr"/>
       <c r="C126" s="8" t="inlineStr"/>
       <c r="D126" s="9" t="inlineStr">
@@ -5697,35 +5722,31 @@
       </c>
       <c r="H126" s="9" t="inlineStr">
         <is>
-          <t>- 빌드 설정에 TDC_UNIT_TEST 를 정의한다.
-- src/1__cfx/test/tdc_unit_test_cfx.c 를 빌드에 넣는다.
-- 기존 소스는 수정하지 않는다. 매크로가 없으면 이 파일은 빈 번역 단위가 된다.
-- 디버거에서 tdc_ut_run_all() 을 호출한다.
-- tdc_ut_done 에 1 이 대입되는 지점에 중단점을 걸고 tdc_ut_result 를 조회한다.
-- PCM 기록 버퍼(HEAR_ADDR_FIFO_PCM_WRITING)를 조회할 수 있게 창을 준비한다.</t>
+          <t>- 대상 유닛이 호출되는 지점에 디버깅용 중단점을 적용한다.
+- 입력 버퍼와 출력 버퍼를 함께 조회할 수 있도록 창을 준비한다.
+- g_pcmFrameNum_per_channel 을 1 로 둔다.
+- 공유 메모리 backtelControlRegister 를 지정한 값으로 둔다.</t>
         </is>
       </c>
       <c r="I126" s="9" t="inlineStr">
         <is>
-          <t>- 이 유닛의 출력은 DSP 라이브러리 또는 HEAR 함수체인 결과에 의존한다.
-- 기댓값을 미리 낼 수 없으므로 실측값을 기록한다.
-- 고정소수점 연산 차이를 고려하여 판정한다.</t>
+          <t>- 시험 맵을 고정한 상태에서만 이 기댓값이 성립한다.
+- 앞단 유닛의 결과를 입력으로 쓰므로 그 유닛을 먼저 시험한다.</t>
         </is>
       </c>
       <c r="J126" s="9" t="inlineStr">
         <is>
           <t>- 채널당 프레임 수를 1 로 두고 호출한다.
-- PCM 기록 버퍼를 조회해 검사 프레임 구성과 자극 자리 배치를 기록한다.</t>
+- PCM 기록 버퍼 24 칸을 조회해 검사 프레임 자리와 자극 자리를 기록한다.</t>
         </is>
       </c>
       <c r="K126" s="9" t="inlineStr">
         <is>
           <t>- 채널별 검사 프레임 생성 구현
-[산출 근거] 채널당 1 프레임 구성으로 검사 프레임을 만든다. 검사 회로 설정에 의존한다. 기댓값을 미리 낼 수 없으므로 지어내지 않는다.
-[판정] 기댓값을 미리 낼 수 없다. 아래 항목의 실측값을 기록한다.
-       고정소수점 연산 차이를 고려하여 판정한다.
-1) 입력 : 시험 벡터 주입
-   예상 출력 : (실측 기록)</t>
+[산출 근거] 맵 데이터와 공유 메모리를 시험용 상수로 고정하면 출력이 결정된다. 아래 시험 맵을 쓴다. 채널당 1 프레임 구성으로 검사 프레임을 만든다. 검사 회로 설정과 자극 자리 배치가 결정적이다.
+[판정] 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
+1) 입력 : 채널당 프레임 1, 검사 제어 레지스터 0
+   예상 출력 : 첫 칸에 검사 설정 몰드가, 나머지에 대기 몰드 0x25555 가 실린다</t>
         </is>
       </c>
     </row>
@@ -10731,7 +10752,7 @@
         </is>
       </c>
     </row>
-    <row r="239" ht="112.5" customHeight="1">
+    <row r="239" ht="100" customHeight="1">
       <c r="B239" s="8" t="inlineStr"/>
       <c r="C239" s="8" t="inlineStr"/>
       <c r="D239" s="9" t="inlineStr">
@@ -10757,29 +10778,34 @@
       <c r="H239" s="9" t="inlineStr">
         <is>
           <t>- 대상 유닛이 호출되는 지점에 디버깅용 중단점을 적용한다.
-- 입력 버퍼와 출력 버퍼를 함께 조회할 수 있도록 창을 준비한다.</t>
+- 입력 버퍼와 출력 버퍼를 함께 조회할 수 있도록 창을 준비한다.
+- 출력단 보정 설정(DAC offset)과 맵의 T/C 레벨을 지정한 값으로 둔다.
+시험 맵 (앞 4 전극만 다르게 두고 나머지는 같은 값)
+  T 레벨  : 10, 20, 30, 40, 나머지 10
+  C 레벨  : 100, 150, 200, 250, 나머지 100
+  xMin    : 100, 200, 300, 400, 나머지 100
+  xMax    : 10000, 20000, 30000, 40000, 나머지 10000</t>
         </is>
       </c>
       <c r="I239" s="9" t="inlineStr">
         <is>
-          <t>- 이 유닛의 출력은 DSP 라이브러리 또는 HEAR 함수체인 결과에 의존한다.
-- 기댓값을 미리 낼 수 없으므로 실측값을 기록한다.
-- 고정소수점 연산 차이를 고려하여 판정한다.</t>
+          <t>- 시험 맵을 고정한 상태에서만 이 기댓값이 성립한다.
+- 앞단 유닛의 결과를 입력으로 쓰므로 그 유닛을 먼저 시험한다.</t>
         </is>
       </c>
       <c r="J239" s="9" t="inlineStr">
         <is>
-          <t>- 호출 후 255 단계로 환산된 T 레벨과 C 레벨 배열을 조회해 기록한다.</t>
+          <t>- 펄스 폭과 T/C 레벨을 시험 값으로 두고 호출한다.
+- 환산된 T_level_255 와 C_level_255 배열을 조회해 기록한다.</t>
         </is>
       </c>
       <c r="K239" s="9" t="inlineStr">
         <is>
           <t>- 자극 범위 설정 구현
-[산출 근거] 출력단 보정 설정과 맵 데이터에 의존한다. 기댓값을 미리 낼 수 없으므로 지어내지 않는다.
-[판정] 기댓값을 미리 낼 수 없다. 아래 항목의 실측값을 기록한다.
-       고정소수점 연산 차이를 고려하여 판정한다.
-1) 입력 : 시험 벡터 주입
-   예상 출력 : (실측 기록)</t>
+[산출 근거] 맵 데이터와 공유 메모리를 시험용 상수로 고정하면 출력이 결정된다. 아래 시험 맵을 쓴다. 펄스 폭과 T/C 레벨(uA)로 255 단계 환산값을 만든다. 출력단 보정 설정과 맵 데이터를 고정하면 결정적이다.
+[판정] 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
+1) 입력 : 펄스 폭 25, T 레벨 10 20 30 40, C 레벨 100 150 200 250 (uA)
+   예상 출력 : 255 단계로 환산된 값. 출력단 보정 기울기 설정에 따라 시프트 폭이 갈린다</t>
         </is>
       </c>
     </row>

--- a/docs/참고/인허가/사운드1/[04] SUVC-FW-SND1 소프트웨어 유닛 검증 기준서.xlsx
+++ b/docs/참고/인허가/사운드1/[04] SUVC-FW-SND1 소프트웨어 유닛 검증 기준서.xlsx
@@ -10752,7 +10752,7 @@
         </is>
       </c>
     </row>
-    <row r="239" ht="100" customHeight="1">
+    <row r="239" ht="175" customHeight="1">
       <c r="B239" s="8" t="inlineStr"/>
       <c r="C239" s="8" t="inlineStr"/>
       <c r="D239" s="9" t="inlineStr">
@@ -10779,7 +10779,8 @@
         <is>
           <t>- 대상 유닛이 호출되는 지점에 디버깅용 중단점을 적용한다.
 - 입력 버퍼와 출력 버퍼를 함께 조회할 수 있도록 창을 준비한다.
-- 출력단 보정 설정(DAC offset)과 맵의 T/C 레벨을 지정한 값으로 둔다.
+- 기울기 설정(DAC_offsetSlope_register)을 A 또는 B 로 둔다.
+- 맵의 T/C 레벨과 펄스 폭을 시험 값으로 둔다.
 시험 맵 (앞 4 전극만 다르게 두고 나머지는 같은 값)
   T 레벨  : 10, 20, 30, 40, 나머지 10
   C 레벨  : 100, 150, 200, 250, 나머지 100
@@ -10795,21 +10796,29 @@
       </c>
       <c r="J239" s="9" t="inlineStr">
         <is>
-          <t>- 펄스 폭과 T/C 레벨을 시험 값으로 두고 호출한다.
-- 환산된 T_level_255 와 C_level_255 배열을 조회해 기록한다.</t>
+          <t>- 기울기 A 로 두고 시험 맵(T 최소 10 uA)으로 호출한다.
+- DAC_offset_uA 와 DAC_offsetLevel_register 를 조회한다.
+- T 최소를 400 uA 로 올려 다시 호출해 포화가 걸리는지 본다.
+- 기울기 B 로 바꿔 같은 두 경우를 반복한다.</t>
         </is>
       </c>
       <c r="K239" s="9" t="inlineStr">
         <is>
           <t>- 자극 범위 설정 구현
-[산출 근거] 맵 데이터와 공유 메모리를 시험용 상수로 고정하면 출력이 결정된다. 아래 시험 맵을 쓴다. 펄스 폭과 T/C 레벨(uA)로 255 단계 환산값을 만든다. 출력단 보정 설정과 맵 데이터를 고정하면 결정적이다.
+[산출 근거] 맵 데이터와 공유 메모리를 시험용 상수로 고정하면 출력이 결정된다. 아래 시험 맵을 쓴다. 펄스 폭과 T/C 레벨(uA)로 255 단계 환산값을 만들고, 그 과정에서 출력단 보정값(DAC_offset_uA)과 보정 레지스터 단계를 함께 정한다. 활성 보드 ISD_Ver_is_112 기준으로 기울기 A 는 295 uA, B 는 592 uA 에서 포화한다.
 [판정] 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
-1) 입력 : 펄스 폭 25, T 레벨 10 20 30 40, C 레벨 100 150 200 250 (uA)
-   예상 출력 : 255 단계로 환산된 값. 출력단 보정 기울기 설정에 따라 시프트 폭이 갈린다</t>
-        </is>
-      </c>
-    </row>
-    <row r="240" ht="100" customHeight="1">
+1) 입력 : 기울기 A, 최소 자극 전류 10 uA (시험 맵의 T 최소값)
+   예상 출력 : DAC_offset_uA = 10, 보정 레지스터 단계 = 4  (포화 없음)
+2) 입력 : 기울기 A, 최소 자극 전류 400 uA
+   예상 출력 : DAC_offset_uA = 295 [포화], 보정 레지스터 단계 = 129
+3) 입력 : 기울기 B, 최소 자극 전류 400 uA
+   예상 출력 : DAC_offset_uA = 400, 보정 레지스터 단계 = 87  (B 는 592 에서 포화하므로 아직 아님)
+4) 입력 : 기울기 B, 최소 자극 전류 1000 uA
+   예상 출력 : DAC_offset_uA = 592 [포화], 보정 레지스터 단계 = 129</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="350" customHeight="1">
       <c r="B240" s="8" t="inlineStr"/>
       <c r="C240" s="8" t="inlineStr"/>
       <c r="D240" s="9" t="inlineStr">
@@ -10838,30 +10847,54 @@
 - src/2__cm3/Cortex-M3-src/test/tdc_unit_test_cm3.c 를 빌드에 넣는다.
 - 기존 소스는 수정하지 않는다. 매크로가 없으면 이 파일은 빈 번역 단위가 된다.
 - 디버거에서 tdc_ut_cm3_run_all() 을 호출한다.
-- tdc_ut_cm3_done 에 1 이 대입되는 지점에 중단점을 걸고 tdc_ut_cm3_result 를 조회한다.</t>
+- tdc_ut_cm3_done 에 1 이 대입되는 지점에 중단점을 걸고 tdc_ut_cm3_result 를 조회한다.
+- 시험 전에 setting_stimulationRange 를 지정한 조건으로 먼저 부른다.
+- 기울기 설정(DAC_offsetSlope_register)과 최소 자극 전류를 지정한 값으로 둔다.</t>
         </is>
       </c>
       <c r="I240" s="9" t="inlineStr">
         <is>
           <t>- 결과 배열에서 값 -999 는 구분자다. 그 다음 값이 유닛 번호다.
 - 시험은 전역 상태를 바꾼다. 시험 후에는 장치를 재기동한다.
-- 시험 코드는 평시 빌드에서 제외되므로 정상 동작에 영향을 주지 않는다.</t>
+- 시험 코드는 평시 빌드에서 제외되므로 정상 동작에 영향을 주지 않는다.
+- 이 유닛만 단독으로 부르면 직전 설정값이 그대로 나온다. 첫 케이스는 아무 것도 부르지 않은 초기 상태를 본다.
+- 포화값은 보드 버전에 따라 다르다. 활성 버전은 ISD_Ver_is_112 다 (processorDirective.h:21).</t>
         </is>
       </c>
       <c r="J240" s="9" t="inlineStr">
         <is>
-          <t>- 하네스가 원 함수를 한 번 호출한다.
-- 구분자 -999 와 유닛 번호 111 다음에 결과 1 개가 이어진다.
-- 그 값이 소스의 DAC_offset_uA 정의값과 같은지 확인한다.</t>
+          <t>- 재기동 직후 이 유닛만 불러 초기값을 조회한다.
+- 기울기 A 로 두고 최소 자극 전류를 10, 295, 400, 592, 1000 으로 바꿔 가며 setting_stimulationRange 를 부른 뒤 이 유닛으로 읽는다.
+- 기울기 B 로 바꿔 같은 다섯 값을 반복한다.</t>
         </is>
       </c>
       <c r="K240" s="9" t="inlineStr">
         <is>
           <t>- 출력단 보정 값 읽기 구현
-[산출 근거] 상수 DAC_offset_uA 를 그대로 반환한다.
+[산출 근거] **상수가 아니다.** DAC_offset_uA 는 static 변수이고 setting_stimulationRange 가 조건에 따라 설정한다. 이 유닛은 그 값을 읽어 온다. 최소 자극 전류가 포화값 이상이면 포화값으로 잘린다. 활성 보드 ISD_Ver_is_112 기준으로 기울기 A 는 295 uA, B 는 592 uA 에서 포화한다. 레지스터 단계는 기울기 역수(A 14435, B 7185)를 곱해 15 비트 내린 값이다.
 [판정] 아래 입력에 대해 예상 출력과 일치해야 한다. (고정소수점 연산 고려)
-1) 입력 : 인자 없음
-   예상 출력 : 소스의 DAC_offset_uA 정의값과 같아야 한다</t>
+1) 입력 : setting_stimulationRange 를 한 번도 부르지 않은 초기 상태
+   예상 출력 : 0  (static int 초기값)
+2) 입력 : 기울기 설정 A, 최소 자극 전류 10 uA
+   예상 출력 : 10 uA  (레지스터 단계 4)
+3) 입력 : 기울기 설정 A, 최소 자극 전류 295 uA
+   예상 출력 : 295 uA  (레지스터 단계 129)
+4) 입력 : 기울기 설정 A, 최소 자극 전류 400 uA
+   예상 출력 : 295 uA [포화]  (레지스터 단계 129)
+5) 입력 : 기울기 설정 A, 최소 자극 전류 592 uA
+   예상 출력 : 295 uA [포화]  (레지스터 단계 129)
+6) 입력 : 기울기 설정 A, 최소 자극 전류 1000 uA
+   예상 출력 : 295 uA [포화]  (레지스터 단계 129)
+7) 입력 : 기울기 설정 B, 최소 자극 전류 10 uA
+   예상 출력 : 10 uA  (레지스터 단계 2)
+8) 입력 : 기울기 설정 B, 최소 자극 전류 295 uA
+   예상 출력 : 295 uA  (레지스터 단계 64)
+9) 입력 : 기울기 설정 B, 최소 자극 전류 400 uA
+   예상 출력 : 400 uA  (레지스터 단계 87)
+10) 입력 : 기울기 설정 B, 최소 자극 전류 592 uA
+   예상 출력 : 592 uA  (레지스터 단계 129)
+11) 입력 : 기울기 설정 B, 최소 자극 전류 1000 uA
+   예상 출력 : 592 uA [포화]  (레지스터 단계 129)</t>
         </is>
       </c>
     </row>
